--- a/tame_output/ON/bt/strategyON_20240827.xlsx
+++ b/tame_output/ON/bt/strategyON_20240827.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.5%</t>
+          <t>423.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-169.0%</t>
+          <t>-166.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-4.9%</t>
         </is>
       </c>
     </row>
@@ -46378,10 +46378,10 @@
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.235941476466455</v>
+        <v>-4.258062181598728</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.995563420451878</v>
+        <v>0.9867151383989687</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4961693277674253</v>
@@ -46401,10 +46401,10 @@
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.263721874367808</v>
+        <v>-4.285842579500081</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9959484630598758</v>
+        <v>0.9871001810069668</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4683889298660722</v>
@@ -46424,10 +46424,10 @@
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.382102547097946</v>
+        <v>-4.404223252230219</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7869519139684737</v>
+        <v>0.7781036319155648</v>
       </c>
       <c r="F1951" t="n">
         <v>0.401171077715096</v>
@@ -46447,10 +46447,10 @@
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.490716625541277</v>
+        <v>-4.51283733067355</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.863655943310347</v>
+        <v>0.8548076612574378</v>
       </c>
       <c r="F1952" t="n">
         <v>0.401171077715096</v>
@@ -46470,10 +46470,10 @@
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.455307587293134</v>
+        <v>-4.477428292425407</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.892332584711927</v>
+        <v>0.883484302659018</v>
       </c>
       <c r="F1953" t="n">
         <v>0.401171077715096</v>
@@ -46493,10 +46493,10 @@
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.416923924734983</v>
+        <v>-4.439044629867256</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9051054910775562</v>
+        <v>0.8962572090246472</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4395547402732472</v>
@@ -46516,10 +46516,10 @@
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.239807594699817</v>
+        <v>-4.26192829983209</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9726810519369247</v>
+        <v>0.9638327698840155</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4395547402732472</v>
@@ -46539,10 +46539,10 @@
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.284899839533363</v>
+        <v>-4.307020544665636</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9553275457654193</v>
+        <v>0.9464792637125103</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3776586971038574</v>
@@ -46562,10 +46562,10 @@
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.105524418294595</v>
+        <v>-4.127645123426868</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.020864689567341</v>
+        <v>1.012016407514432</v>
       </c>
       <c r="F1957" t="n">
         <v>0.534435455274576</v>
@@ -46585,10 +46585,10 @@
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.150538631815202</v>
+        <v>-4.172659336947474</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9836664594906879</v>
+        <v>0.9748181774377791</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5040865599599714</v>
@@ -46608,10 +46608,10 @@
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.417543142087637</v>
+        <v>-4.439663847219909</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8825562177206596</v>
+        <v>0.8737079356677508</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3097235219170228</v>
@@ -46631,10 +46631,10 @@
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.51874092352481</v>
+        <v>-4.540861628657082</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8412810270422919</v>
+        <v>0.8324327449893834</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2413147083717037</v>
@@ -46654,10 +46654,10 @@
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.512229956910497</v>
+        <v>-4.534350662042769</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8414853752423337</v>
+        <v>0.8326370931894251</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2413147083717037</v>
@@ -46677,10 +46677,10 @@
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.4931918292032</v>
+        <v>-4.515312534335472</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8456253455334977</v>
+        <v>0.8367770634805889</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1831310970405091</v>
@@ -46700,10 +46700,10 @@
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.54570763147802</v>
+        <v>-4.567828336610292</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9439134262577598</v>
+        <v>0.935065144204851</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1831310970405091</v>
@@ -46723,10 +46723,10 @@
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.559574392811938</v>
+        <v>-4.58169509794421</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9392000507103262</v>
+        <v>0.9303517686574174</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1452731803066862</v>
@@ -46746,10 +46746,10 @@
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.514770221272008</v>
+        <v>-4.53689092640428</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9631302497232241</v>
+        <v>0.9542819676703154</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1452731803066862</v>
@@ -46769,10 +46769,10 @@
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.367027251037006</v>
+        <v>-4.389147956169277</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9201776590944246</v>
+        <v>0.9113293770415158</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3130805375415693</v>
@@ -46792,10 +46792,10 @@
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.450848472311704</v>
+        <v>-4.472969177443976</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8894427921160262</v>
+        <v>0.8805945100631174</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3130805375415693</v>
@@ -46815,10 +46815,10 @@
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.44469576625892</v>
+        <v>-4.466816471391192</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8925662229287983</v>
+        <v>0.8837179408758895</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3192332435943536</v>
@@ -46838,10 +46838,10 @@
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.461505064409422</v>
+        <v>-4.483625769541693</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8849229804087078</v>
+        <v>0.876074698355799</v>
       </c>
       <c r="F1969" t="n">
         <v>0.302423945443852</v>
@@ -46861,10 +46861,10 @@
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.399207065633299</v>
+        <v>-4.421327770765571</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9761777337159776</v>
+        <v>0.9673294516630688</v>
       </c>
       <c r="F1970" t="n">
         <v>0.347718209718294</v>
@@ -46884,10 +46884,10 @@
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.197416867968141</v>
+        <v>-4.219537573100413</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8591858144961679</v>
+        <v>0.8503375324432592</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5457364018874484</v>
@@ -46907,10 +46907,10 @@
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.248303580654336</v>
+        <v>-4.270424285786608</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9091213617438652</v>
+        <v>0.9002730796909564</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4948496892012539</v>
@@ -46930,10 +46930,10 @@
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.161692838004529</v>
+        <v>-4.183813543136801</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9583933949198316</v>
+        <v>0.9495451128669228</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5734754204064122</v>
@@ -46953,10 +46953,10 @@
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.221902136009814</v>
+        <v>-4.244022841142086</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9328456565423893</v>
+        <v>0.9239973744894805</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5132661224011277</v>
@@ -46976,10 +46976,10 @@
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.145480089577887</v>
+        <v>-4.167600794710159</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9619060931550885</v>
+        <v>0.9530578111021799</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5132661224011277</v>
@@ -46999,10 +46999,10 @@
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.101106957939319</v>
+        <v>-4.12322766307159</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9795182132459521</v>
+        <v>0.9706699311930436</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5576392540396963</v>
@@ -47022,10 +47022,10 @@
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.123587308798204</v>
+        <v>-4.145708013930475</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9649198670409889</v>
+        <v>0.9560715849880801</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5576392540396963</v>
@@ -47045,10 +47045,10 @@
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.075931578237148</v>
+        <v>-4.09805228336942</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9903639162932159</v>
+        <v>0.9815156342403071</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6052949846007519</v>
@@ -47068,10 +47068,10 @@
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.975413419738393</v>
+        <v>-3.997534124870665</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.035463553067443</v>
+        <v>1.026615271014534</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7058131430995065</v>
@@ -47091,10 +47091,10 @@
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.95950809030604</v>
+        <v>-3.981628795438312</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.028580357316256</v>
+        <v>1.019732075263347</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6267004823902675</v>
@@ -47114,10 +47114,10 @@
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.914669688697642</v>
+        <v>-3.936790393829914</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.050613420570244</v>
+        <v>1.041765138517335</v>
       </c>
       <c r="F1981" t="n">
         <v>0.631243915335137</v>
@@ -47137,10 +47137,10 @@
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.934168144939651</v>
+        <v>-3.956288850071922</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.046974977704518</v>
+        <v>1.03812669565161</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5831592740552327</v>
@@ -47160,10 +47160,10 @@
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.88996530785375</v>
+        <v>-3.912086012986022</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.070535715066716</v>
+        <v>1.061687433013807</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6273621111411332</v>
@@ -47183,10 +47183,10 @@
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.897524973690797</v>
+        <v>-3.919645678823069</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.065921849201144</v>
+        <v>1.057073567148236</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6821655151509525</v>
@@ -47206,10 +47206,10 @@
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.739233556151525</v>
+        <v>-3.761354261283797</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.180486181399893</v>
+        <v>1.171637899346984</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6821655151509525</v>
@@ -47229,10 +47229,10 @@
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.531591552517049</v>
+        <v>-3.553712257649321</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.261983687447936</v>
+        <v>1.253135405395028</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8898075187854286</v>
@@ -47252,10 +47252,10 @@
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.480559459794521</v>
+        <v>-3.502680164926792</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.277344752775218</v>
+        <v>1.268496470722309</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9408396115079566</v>
@@ -47275,10 +47275,10 @@
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.415335278667315</v>
+        <v>-3.437455983799587</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.320621829318805</v>
+        <v>1.311773547265896</v>
       </c>
       <c r="F1988" t="n">
         <v>1.006063792635162</v>
@@ -47298,10 +47298,10 @@
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.377908258596181</v>
+        <v>-3.400028963728453</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.331553609646539</v>
+        <v>1.32270532759363</v>
       </c>
       <c r="F1989" t="n">
         <v>1.011315330664344</v>
@@ -47321,10 +47321,10 @@
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.398019914630889</v>
+        <v>-3.420140619763161</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.324765739563896</v>
+        <v>1.315917457510987</v>
       </c>
       <c r="F1990" t="n">
         <v>1.022342675661763</v>
@@ -47344,10 +47344,10 @@
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.369606651531006</v>
+        <v>-3.391727356663278</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.49668881582506</v>
+        <v>1.487840533772151</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9633671129153341</v>
@@ -47367,10 +47367,10 @@
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.294824390505993</v>
+        <v>-3.316945095638265</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.646714629452882</v>
+        <v>1.637866347399973</v>
       </c>
       <c r="F1992" t="n">
         <v>1.038149373940347</v>
@@ -47390,10 +47390,10 @@
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.268740306242185</v>
+        <v>-3.290861011374457</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.648856239172265</v>
+        <v>1.640007957119356</v>
       </c>
       <c r="F1993" t="n">
         <v>1.038149373940347</v>
@@ -47413,10 +47413,10 @@
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.180862393133065</v>
+        <v>-3.202983098265336</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.682200599999692</v>
+        <v>1.673352317946784</v>
       </c>
       <c r="F1994" t="n">
         <v>1.154075016363698</v>
@@ -47436,10 +47436,10 @@
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.171969931739781</v>
+        <v>-3.194090636872053</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.703311990283797</v>
+        <v>1.694463708230888</v>
       </c>
       <c r="F1995" t="n">
         <v>1.154075016363698</v>
@@ -47459,10 +47459,10 @@
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.340446048709659</v>
+        <v>-3.362566753841931</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.62777659090043</v>
+        <v>1.618928308847521</v>
       </c>
       <c r="F1996" t="n">
         <v>1.126127180647117</v>
@@ -47482,10 +47482,10 @@
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.894189856080219</v>
+        <v>-2.916310561212491</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.787548765140068</v>
+        <v>1.778700483087159</v>
       </c>
       <c r="F1997" t="n">
         <v>1.031408510977484</v>
@@ -47505,10 +47505,10 @@
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.871468752397067</v>
+        <v>-2.893589457529338</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.787301229110233</v>
+        <v>1.778452947057324</v>
       </c>
       <c r="F1998" t="n">
         <v>1.031408510977484</v>
@@ -47528,10 +47528,10 @@
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.000670565691109</v>
+        <v>-3.022791270823381</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.894526629643785</v>
+        <v>1.885678347590876</v>
       </c>
       <c r="F1999" t="n">
         <v>0.902206697683442</v>
@@ -47551,10 +47551,10 @@
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.026544964165135</v>
+        <v>-3.048665669297407</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.921254692747821</v>
+        <v>1.912406410694913</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9471183063951831</v>
@@ -47574,10 +47574,10 @@
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.019490273949961</v>
+        <v>-3.041610979082233</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.920751924823436</v>
+        <v>1.911903642770527</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9541729966103569</v>
@@ -47597,10 +47597,10 @@
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.992539049623473</v>
+        <v>-3.014659754755745</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.941538568198773</v>
+        <v>1.932690286145864</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9690533426380761</v>
@@ -47620,10 +47620,10 @@
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.128492057679789</v>
+        <v>-3.150612762812061</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.071260497121206</v>
+        <v>2.062412215068298</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9690533426380761</v>
@@ -47643,10 +47643,10 @@
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.150900175484662</v>
+        <v>-3.173020880616933</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.05441394490225</v>
+        <v>2.045565662849341</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9690533426380761</v>
@@ -47666,10 +47666,10 @@
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.179124411062262</v>
+        <v>-3.201245116194534</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.045178250220848</v>
+        <v>2.036329968167939</v>
       </c>
       <c r="F2005" t="n">
         <v>0.9870300950893847</v>
@@ -47689,10 +47689,10 @@
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.188565336950792</v>
+        <v>-3.210686042083064</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.097655597587283</v>
+        <v>2.088807315534374</v>
       </c>
       <c r="F2006" t="n">
         <v>1.109457212632776</v>
@@ -47712,10 +47712,10 @@
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.240838944286433</v>
+        <v>-3.262959649418705</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.079637249198327</v>
+        <v>2.070788967145418</v>
       </c>
       <c r="F2007" t="n">
         <v>1.057183605297135</v>
@@ -47735,10 +47735,10 @@
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.317168921887339</v>
+        <v>-3.339289627019611</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.04721707105174</v>
+        <v>2.038368788998831</v>
       </c>
       <c r="F2008" t="n">
         <v>1.057183605297135</v>
@@ -47758,10 +47758,10 @@
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.519422642211692</v>
+        <v>-3.541543347343964</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.961135812524861</v>
+        <v>1.952287530471952</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8549298849727813</v>
@@ -47781,10 +47781,10 @@
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.680991067738947</v>
+        <v>-3.703111772871219</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.894942452524111</v>
+        <v>1.886094170471202</v>
       </c>
       <c r="F2010" t="n">
         <v>0.728146961174902</v>
@@ -47804,10 +47804,10 @@
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.789291729609067</v>
+        <v>-3.811412434741339</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.864695594641982</v>
+        <v>1.855847312589073</v>
       </c>
       <c r="F2011" t="n">
         <v>0.728146961174902</v>
@@ -47827,10 +47827,10 @@
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.882439200912434</v>
+        <v>-3.904559906044705</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.819441802903575</v>
+        <v>1.810593520850666</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6053177498923692</v>
@@ -47850,10 +47850,10 @@
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.910339988021907</v>
+        <v>-3.932460693154178</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.806805529186788</v>
+        <v>1.797957247133879</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5707208257494344</v>
@@ -47873,10 +47873,10 @@
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.0328660907248</v>
+        <v>-4.054986795857072</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.754559532082829</v>
+        <v>1.745711250029921</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4481947230465405</v>
@@ -47896,10 +47896,10 @@
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.263380586910389</v>
+        <v>-4.285501292042661</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.729059693199098</v>
+        <v>1.720211411146189</v>
       </c>
       <c r="F2015" t="n">
         <v>0.2176802268609518</v>
@@ -47919,10 +47919,10 @@
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.612125672134833</v>
+        <v>-4.634246377267105</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.729873378111167</v>
+        <v>1.721025096058258</v>
       </c>
       <c r="F2016" t="n">
         <v>0.108932272942054</v>
@@ -47942,10 +47942,10 @@
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.766112089910973</v>
+        <v>-4.788232795043245</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.737259080146351</v>
+        <v>1.728410798093442</v>
       </c>
       <c r="F2017" t="n">
         <v>0.108932272942054</v>
@@ -47965,10 +47965,10 @@
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.715590186083308</v>
+        <v>-4.737710891215579</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.743519043797538</v>
+        <v>1.734670761744629</v>
       </c>
       <c r="F2018" t="n">
         <v>0.108932272942054</v>
@@ -47988,10 +47988,10 @@
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.968065340091032</v>
+        <v>-4.990186045223304</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.654399471249862</v>
+        <v>1.645551189196953</v>
       </c>
       <c r="F2019" t="n">
         <v>0.108932272942054</v>
@@ -48011,10 +48011,10 @@
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.260961096570444</v>
+        <v>-5.283081801702716</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.538451703177041</v>
+        <v>1.529603421124132</v>
       </c>
       <c r="F2020" t="n">
         <v>0.108932272942054</v>
@@ -48034,10 +48034,10 @@
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.447625224705252</v>
+        <v>-5.469745929837524</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.467907794150439</v>
+        <v>1.45905951209753</v>
       </c>
       <c r="F2021" t="n">
         <v>0.08219330211749409</v>
@@ -48057,10 +48057,10 @@
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.593645911619214</v>
+        <v>-5.615766616751486</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.404577372121044</v>
+        <v>1.395729090068135</v>
       </c>
       <c r="F2022" t="n">
         <v>0.07311021032363713</v>
@@ -48080,10 +48080,10 @@
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.6853599207288</v>
+        <v>-5.707480625861072</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.530095825176254</v>
+        <v>1.521247543123345</v>
       </c>
       <c r="F2023" t="n">
         <v>0.07311021032363713</v>
@@ -48103,10 +48103,10 @@
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.717011579788769</v>
+        <v>-5.739132284921041</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.51228179951608</v>
+        <v>1.503433517463171</v>
       </c>
       <c r="F2024" t="n">
         <v>0.06794175307919692</v>
@@ -48126,10 +48126,10 @@
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.798946398057653</v>
+        <v>-5.821067103189924</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.489737289777018</v>
+        <v>1.480889007724109</v>
       </c>
       <c r="F2025" t="n">
         <v>0.05800700749211674</v>
@@ -48149,10 +48149,10 @@
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.90092252030606</v>
+        <v>-5.923043225438332</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.457872479333557</v>
+        <v>1.449024197280649</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.04396911475629084</v>
@@ -48172,10 +48172,10 @@
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.790916236828838</v>
+        <v>-5.81303694196111</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.494027879968622</v>
+        <v>1.485179597915713</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.02076454283901563</v>
@@ -48195,10 +48195,10 @@
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.647856661087912</v>
+        <v>-5.669977366220184</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.555501720986966</v>
+        <v>1.546653438934057</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.01275111624903635</v>
@@ -48218,10 +48218,10 @@
         <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.346409935616075</v>
+        <v>-5.368530640748347</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.683341294058237</v>
+        <v>1.674493012005328</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2886956092228009</v>
@@ -48241,10 +48241,10 @@
         <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.371000179851259</v>
+        <v>-5.393120884983531</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.674476374116874</v>
+        <v>1.665628092063965</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2886956092228009</v>
@@ -48264,10 +48264,10 @@
         <v>3.82407577475088</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.319961803844738</v>
+        <v>-5.34208250897701</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.695734628899238</v>
+        <v>1.686886346846329</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2886956092228009</v>
@@ -48287,10 +48287,10 @@
         <v>3.843113873625026</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.278822508978108</v>
+        <v>-5.300943214110379</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.731228445720036</v>
+        <v>1.722380163667127</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3298349040894317</v>
@@ -48310,10 +48310,10 @@
         <v>3.65929786974896</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.182187596959468</v>
+        <v>-5.204308302091739</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.586066406651426</v>
+        <v>1.577218124598518</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4264698161080717</v>
@@ -48333,10 +48333,10 @@
         <v>3.662799913822925</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.31276833149031</v>
+        <v>-5.334889036622582</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.537336156913053</v>
+        <v>1.528487874860144</v>
       </c>
       <c r="F2034" t="n">
         <v>0.2958890815772292</v>
@@ -48356,10 +48356,10 @@
         <v>3.647226732899007</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.148271997299348</v>
+        <v>-5.17039270243162</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.58756150966552</v>
+        <v>1.578713227612612</v>
       </c>
       <c r="F2035" t="n">
         <v>0.460385415768191</v>
@@ -48379,10 +48379,10 @@
         <v>3.646414443335437</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.17564192998378</v>
+        <v>-5.197762635116052</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.575801247028177</v>
+        <v>1.566952964975269</v>
       </c>
       <c r="F2036" t="n">
         <v>0.460385415768191</v>
@@ -48402,10 +48402,10 @@
         <v>3.656283222460509</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.18602712487367</v>
+        <v>-5.208147830005942</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.581515948197294</v>
+        <v>1.572667666144385</v>
       </c>
       <c r="F2037" t="n">
         <v>0.4500002208783017</v>
@@ -48425,10 +48425,10 @@
         <v>3.727120228236934</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.204615283595895</v>
+        <v>-5.226735988728167</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.644917690484829</v>
+        <v>1.636069408431921</v>
       </c>
       <c r="F2038" t="n">
         <v>0.4314120621560764</v>
@@ -48448,10 +48448,10 @@
         <v>3.723989239055233</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.204913830291931</v>
+        <v>-5.227034535424202</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.641667282624713</v>
+        <v>1.632819000571805</v>
       </c>
       <c r="F2039" t="n">
         <v>0.4311135154600405</v>
@@ -48471,10 +48471,10 @@
         <v>3.728520133994624</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.104090696601503</v>
+        <v>-5.126211401733775</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.686527431040276</v>
+        <v>1.677679148987367</v>
       </c>
       <c r="F2040" t="n">
         <v>0.4435777309443943</v>
@@ -48494,10 +48494,10 @@
         <v>3.728649387473168</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.913309335849096</v>
+        <v>-4.935430040981368</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.762969228819782</v>
+        <v>1.754120946766873</v>
       </c>
       <c r="F2041" t="n">
         <v>0.6343590916968016</v>
@@ -48517,10 +48517,10 @@
         <v>3.708486233210764</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.894792481807276</v>
+        <v>-4.916913186939547</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.750212816174107</v>
+        <v>1.741364534121198</v>
       </c>
       <c r="F2042" t="n">
         <v>0.6472892211220098</v>
@@ -48540,10 +48540,10 @@
         <v>3.743453169822823</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.839461893905513</v>
+        <v>-4.861582599037785</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.80731198794687</v>
+        <v>1.798463705893961</v>
       </c>
       <c r="F2043" t="n">
         <v>0.702619809023772</v>
@@ -48563,10 +48563,10 @@
         <v>3.73713973772426</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.82740776699255</v>
+        <v>-4.849528472124822</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.805820206613493</v>
+        <v>1.796971924560584</v>
       </c>
       <c r="F2044" t="n">
         <v>0.7146739359367348</v>
@@ -48586,10 +48586,10 @@
         <v>3.739020367908396</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.868562886560771</v>
+        <v>-4.890683591693043</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.791238788970341</v>
+        <v>1.782390506917432</v>
       </c>
       <c r="F2045" t="n">
         <v>0.6735188163685139</v>
@@ -48609,10 +48609,10 @@
         <v>3.751871393786279</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.765682297032178</v>
+        <v>-4.78780300216445</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.84524205065966</v>
+        <v>1.836393768606751</v>
       </c>
       <c r="F2046" t="n">
         <v>0.7763994058971068</v>
@@ -48632,10 +48632,10 @@
         <v>3.772074063959873</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.997282690201679</v>
+        <v>-5.019403395333951</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.772804563565454</v>
+        <v>1.763956281512545</v>
       </c>
       <c r="F2047" t="n">
         <v>0.7763994058971068</v>
@@ -48655,10 +48655,10 @@
         <v>3.772074063959873</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.015355198493291</v>
+        <v>-5.037475903625563</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.765575560248809</v>
+        <v>1.756727278195901</v>
       </c>
       <c r="F2048" t="n">
         <v>0.7763994058971068</v>
@@ -48678,10 +48678,10 @@
         <v>3.73232597755334</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.190462031069735</v>
+        <v>-5.212582736202007</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.655784740811698</v>
+        <v>1.646936458758789</v>
       </c>
       <c r="F2049" t="n">
         <v>0.7763994058971068</v>
@@ -48701,10 +48701,10 @@
         <v>3.73934859655028</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.15917601052928</v>
+        <v>-5.181296715661552</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.67532176802482</v>
+        <v>1.666473485971911</v>
       </c>
       <c r="F2050" t="n">
         <v>0.8076854264375621</v>
@@ -48724,10 +48724,10 @@
         <v>3.838519596123184</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.006150618415996</v>
+        <v>-5.028271323548267</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.835702924443039</v>
+        <v>1.82685464239013</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9607108185508463</v>
@@ -48747,10 +48747,10 @@
         <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.034457932289266</v>
+        <v>-5.056578637421538</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.011846223802022</v>
+        <v>2.002997941749113</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9607108185508463</v>
@@ -48770,10 +48770,10 @@
         <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.201051157402788</v>
+        <v>-5.22317186253506</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.914611885110696</v>
+        <v>1.905763603057787</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7941175934373239</v>
@@ -48793,10 +48793,10 @@
         <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.027986778020488</v>
+        <v>-5.05010748315276</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.987514039525334</v>
+        <v>1.978665757472425</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7941175934373239</v>
@@ -48816,10 +48816,10 @@
         <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.998740797564792</v>
+        <v>-5.020861502697064</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.996830486831107</v>
+        <v>1.987982204778199</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7941175934373239</v>
@@ -48839,10 +48839,10 @@
         <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.105666345442643</v>
+        <v>-5.127787050574915</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.951353506837602</v>
+        <v>1.942505224784693</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6871920455594726</v>
@@ -48862,10 +48862,10 @@
         <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.250684903949892</v>
+        <v>-5.272805609082163</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.894774885577937</v>
+        <v>1.885926603525028</v>
       </c>
       <c r="F2057" t="n">
         <v>0.542173487052224</v>
@@ -48885,10 +48885,10 @@
         <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.369026669734609</v>
+        <v>-5.391147374866881</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.947369418521803</v>
+        <v>1.938521136468894</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5528595256151141</v>
@@ -48908,10 +48908,10 @@
         <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.420437092055317</v>
+        <v>-5.442557797187589</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.924590946719458</v>
+        <v>1.91574266466655</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5528595256151141</v>
@@ -48931,10 +48931,10 @@
         <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.499856543263069</v>
+        <v>-5.52197724839534</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.892726294310647</v>
+        <v>1.883878012257739</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5528595256151141</v>
@@ -48954,10 +48954,10 @@
         <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.595319541180286</v>
+        <v>-5.617440246312558</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.854534988701804</v>
+        <v>1.845686706648895</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5528595256151141</v>
@@ -48977,10 +48977,10 @@
         <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.63533953922407</v>
+        <v>-5.657460244356342</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.836623386046901</v>
+        <v>1.827775103993992</v>
       </c>
       <c r="F2062" t="n">
         <v>0.5128395275713302</v>
@@ -49000,10 +49000,10 @@
         <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.690708701356264</v>
+        <v>-5.712829406488535</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.82020953894175</v>
+        <v>1.811361256888841</v>
       </c>
       <c r="F2063" t="n">
         <v>0.5128395275713302</v>
@@ -49023,10 +49023,10 @@
         <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.736146481187091</v>
+        <v>-5.758267186319363</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.801572790352352</v>
+        <v>1.792724508299443</v>
       </c>
       <c r="F2064" t="n">
         <v>0.4699945368931706</v>
@@ -49046,10 +49046,10 @@
         <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.652921024339427</v>
+        <v>-5.675041729471698</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.854737365941737</v>
+        <v>1.845889083888828</v>
       </c>
       <c r="F2065" t="n">
         <v>0.4699945368931706</v>
@@ -49069,10 +49069,10 @@
         <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.476630799734119</v>
+        <v>-5.498751504866391</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.908954156308587</v>
+        <v>1.900105874255679</v>
       </c>
       <c r="F2066" t="n">
         <v>0.4699945368931706</v>
@@ -49092,10 +49092,10 @@
         <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.293419136601024</v>
+        <v>-5.315539841733296</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.984669771025871</v>
+        <v>1.975821488972962</v>
       </c>
       <c r="F2067" t="n">
         <v>0.4699945368931706</v>
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.779096486576056</v>
+        <v>3.743613838209839</v>
       </c>
       <c r="C2068" t="n">
         <v>4.068185035827917</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.213478188374805</v>
+        <v>-5.213478594249516</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.982437336164248</v>
+        <v>1.982437173814364</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5499354851193897</v>
+        <v>0.5720557843769503</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.398146326899552</v>
+        <v>4.411418506454088</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240827.xlsx
+++ b/tame_output/ON/bt/strategyON_20240827.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.2%</t>
+          <t>423.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-682.9%</t>
+          <t>-685.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-178.0%</t>
+          <t>-179.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-281.6%</t>
+          <t>-280.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.8%</t>
+          <t>-169.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-6.7%</t>
         </is>
       </c>
     </row>
@@ -46378,10 +46378,10 @@
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.258062181598728</v>
+        <v>-4.235941476466455</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9867151383989687</v>
+        <v>0.995563420451878</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4961693277674253</v>
@@ -46401,10 +46401,10 @@
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.285842579500081</v>
+        <v>-4.263721874367808</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9871001810069668</v>
+        <v>0.9959484630598758</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4683889298660722</v>
@@ -46424,10 +46424,10 @@
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.404223252230219</v>
+        <v>-4.382102547097946</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7781036319155648</v>
+        <v>0.7869519139684737</v>
       </c>
       <c r="F1951" t="n">
         <v>0.401171077715096</v>
@@ -46447,10 +46447,10 @@
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.51283733067355</v>
+        <v>-4.490716625541277</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8548076612574378</v>
+        <v>0.863655943310347</v>
       </c>
       <c r="F1952" t="n">
         <v>0.401171077715096</v>
@@ -46470,10 +46470,10 @@
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.477428292425407</v>
+        <v>-4.455307587293134</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.883484302659018</v>
+        <v>0.892332584711927</v>
       </c>
       <c r="F1953" t="n">
         <v>0.401171077715096</v>
@@ -46493,10 +46493,10 @@
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.439044629867256</v>
+        <v>-4.416923924734983</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8962572090246472</v>
+        <v>0.9051054910775562</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4395547402732472</v>
@@ -46516,10 +46516,10 @@
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.26192829983209</v>
+        <v>-4.239807594699817</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9638327698840155</v>
+        <v>0.9726810519369247</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4395547402732472</v>
@@ -46539,10 +46539,10 @@
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.307020544665636</v>
+        <v>-4.284899839533363</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9464792637125103</v>
+        <v>0.9553275457654193</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3776586971038574</v>
@@ -46562,10 +46562,10 @@
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.127645123426868</v>
+        <v>-4.105524418294595</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.012016407514432</v>
+        <v>1.020864689567341</v>
       </c>
       <c r="F1957" t="n">
         <v>0.534435455274576</v>
@@ -46585,10 +46585,10 @@
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.172659336947474</v>
+        <v>-4.150538631815202</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9748181774377791</v>
+        <v>0.9836664594906879</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5040865599599714</v>
@@ -46608,10 +46608,10 @@
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.439663847219909</v>
+        <v>-4.417543142087637</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8737079356677508</v>
+        <v>0.8825562177206596</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3097235219170228</v>
@@ -46631,10 +46631,10 @@
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.540861628657082</v>
+        <v>-4.51874092352481</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8324327449893834</v>
+        <v>0.8412810270422919</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2413147083717037</v>
@@ -46654,10 +46654,10 @@
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.534350662042769</v>
+        <v>-4.512229956910497</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8326370931894251</v>
+        <v>0.8414853752423337</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2413147083717037</v>
@@ -46677,10 +46677,10 @@
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.515312534335472</v>
+        <v>-4.4931918292032</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8367770634805889</v>
+        <v>0.8456253455334977</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1831310970405091</v>
@@ -46700,10 +46700,10 @@
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.567828336610292</v>
+        <v>-4.54570763147802</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.935065144204851</v>
+        <v>0.9439134262577598</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1831310970405091</v>
@@ -46723,10 +46723,10 @@
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.58169509794421</v>
+        <v>-4.559574392811938</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9303517686574174</v>
+        <v>0.9392000507103262</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1452731803066862</v>
@@ -46746,10 +46746,10 @@
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.53689092640428</v>
+        <v>-4.514770221272008</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9542819676703154</v>
+        <v>0.9631302497232241</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1452731803066862</v>
@@ -46769,10 +46769,10 @@
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.389147956169277</v>
+        <v>-4.367027251037006</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9113293770415158</v>
+        <v>0.9201776590944246</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3130805375415693</v>
@@ -46792,10 +46792,10 @@
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.472969177443976</v>
+        <v>-4.450848472311704</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8805945100631174</v>
+        <v>0.8894427921160262</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3130805375415693</v>
@@ -46815,10 +46815,10 @@
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.466816471391192</v>
+        <v>-4.44469576625892</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8837179408758895</v>
+        <v>0.8925662229287983</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3192332435943536</v>
@@ -46838,10 +46838,10 @@
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.483625769541693</v>
+        <v>-4.461505064409422</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.876074698355799</v>
+        <v>0.8849229804087078</v>
       </c>
       <c r="F1969" t="n">
         <v>0.302423945443852</v>
@@ -46861,10 +46861,10 @@
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.421327770765571</v>
+        <v>-4.399207065633299</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9673294516630688</v>
+        <v>0.9761777337159776</v>
       </c>
       <c r="F1970" t="n">
         <v>0.347718209718294</v>
@@ -46884,10 +46884,10 @@
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.219537573100413</v>
+        <v>-4.197416867968141</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8503375324432592</v>
+        <v>0.8591858144961679</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5457364018874484</v>
@@ -46907,10 +46907,10 @@
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.270424285786608</v>
+        <v>-4.248303580654336</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9002730796909564</v>
+        <v>0.9091213617438652</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4948496892012539</v>
@@ -46930,10 +46930,10 @@
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.183813543136801</v>
+        <v>-4.161692838004529</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9495451128669228</v>
+        <v>0.9583933949198316</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5734754204064122</v>
@@ -46953,10 +46953,10 @@
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.244022841142086</v>
+        <v>-4.221902136009814</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9239973744894805</v>
+        <v>0.9328456565423893</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5132661224011277</v>
@@ -46976,10 +46976,10 @@
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.167600794710159</v>
+        <v>-4.145480089577887</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9530578111021799</v>
+        <v>0.9619060931550885</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5132661224011277</v>
@@ -46999,10 +46999,10 @@
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.12322766307159</v>
+        <v>-4.101106957939319</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9706699311930436</v>
+        <v>0.9795182132459521</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5576392540396963</v>
@@ -47022,10 +47022,10 @@
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.145708013930475</v>
+        <v>-4.123587308798204</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9560715849880801</v>
+        <v>0.9649198670409889</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5576392540396963</v>
@@ -47045,10 +47045,10 @@
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.09805228336942</v>
+        <v>-4.075931578237148</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9815156342403071</v>
+        <v>0.9903639162932159</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6052949846007519</v>
@@ -47068,10 +47068,10 @@
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.997534124870665</v>
+        <v>-3.975413419738393</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.026615271014534</v>
+        <v>1.035463553067443</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7058131430995065</v>
@@ -47091,10 +47091,10 @@
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.981628795438312</v>
+        <v>-3.95950809030604</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.019732075263347</v>
+        <v>1.028580357316256</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6267004823902675</v>
@@ -47114,10 +47114,10 @@
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.936790393829914</v>
+        <v>-3.914669688697642</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.041765138517335</v>
+        <v>1.050613420570244</v>
       </c>
       <c r="F1981" t="n">
         <v>0.631243915335137</v>
@@ -47137,10 +47137,10 @@
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.956288850071922</v>
+        <v>-3.934168144939651</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.03812669565161</v>
+        <v>1.046974977704518</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5831592740552327</v>
@@ -47160,10 +47160,10 @@
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.912086012986022</v>
+        <v>-3.88996530785375</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.061687433013807</v>
+        <v>1.070535715066716</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6273621111411332</v>
@@ -47183,10 +47183,10 @@
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.919645678823069</v>
+        <v>-3.897524973690797</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.057073567148236</v>
+        <v>1.065921849201144</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6821655151509525</v>
@@ -47206,10 +47206,10 @@
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.761354261283797</v>
+        <v>-3.739233556151525</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.171637899346984</v>
+        <v>1.180486181399893</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6821655151509525</v>
@@ -47229,10 +47229,10 @@
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.553712257649321</v>
+        <v>-3.531591552517049</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.253135405395028</v>
+        <v>1.261983687447936</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8898075187854286</v>
@@ -47252,10 +47252,10 @@
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.502680164926792</v>
+        <v>-3.480559459794521</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.268496470722309</v>
+        <v>1.277344752775218</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9408396115079566</v>
@@ -47275,10 +47275,10 @@
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.437455983799587</v>
+        <v>-3.415335278667315</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.311773547265896</v>
+        <v>1.320621829318805</v>
       </c>
       <c r="F1988" t="n">
         <v>1.006063792635162</v>
@@ -47298,10 +47298,10 @@
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.400028963728453</v>
+        <v>-3.377908258596181</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.32270532759363</v>
+        <v>1.331553609646539</v>
       </c>
       <c r="F1989" t="n">
         <v>1.011315330664344</v>
@@ -47321,10 +47321,10 @@
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.420140619763161</v>
+        <v>-3.398019914630889</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.315917457510987</v>
+        <v>1.324765739563896</v>
       </c>
       <c r="F1990" t="n">
         <v>1.022342675661763</v>
@@ -47344,10 +47344,10 @@
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.391727356663278</v>
+        <v>-3.369606651531006</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.487840533772151</v>
+        <v>1.49668881582506</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9633671129153341</v>
@@ -47367,10 +47367,10 @@
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.316945095638265</v>
+        <v>-3.294824390505993</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.637866347399973</v>
+        <v>1.646714629452882</v>
       </c>
       <c r="F1992" t="n">
         <v>1.038149373940347</v>
@@ -47390,10 +47390,10 @@
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.290861011374457</v>
+        <v>-3.268740306242185</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.640007957119356</v>
+        <v>1.648856239172265</v>
       </c>
       <c r="F1993" t="n">
         <v>1.038149373940347</v>
@@ -47413,10 +47413,10 @@
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.202983098265336</v>
+        <v>-3.180862393133065</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.673352317946784</v>
+        <v>1.682200599999692</v>
       </c>
       <c r="F1994" t="n">
         <v>1.154075016363698</v>
@@ -47436,10 +47436,10 @@
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.194090636872053</v>
+        <v>-3.171969931739781</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.694463708230888</v>
+        <v>1.703311990283797</v>
       </c>
       <c r="F1995" t="n">
         <v>1.154075016363698</v>
@@ -47459,10 +47459,10 @@
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.362566753841931</v>
+        <v>-3.340446048709659</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.618928308847521</v>
+        <v>1.62777659090043</v>
       </c>
       <c r="F1996" t="n">
         <v>1.126127180647117</v>
@@ -47482,10 +47482,10 @@
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.916310561212491</v>
+        <v>-2.894189856080219</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.778700483087159</v>
+        <v>1.787548765140068</v>
       </c>
       <c r="F1997" t="n">
         <v>1.031408510977484</v>
@@ -47505,10 +47505,10 @@
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.893589457529338</v>
+        <v>-2.871468752397067</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.778452947057324</v>
+        <v>1.787301229110233</v>
       </c>
       <c r="F1998" t="n">
         <v>1.031408510977484</v>
@@ -47528,10 +47528,10 @@
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.022791270823381</v>
+        <v>-3.000670565691109</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.885678347590876</v>
+        <v>1.894526629643785</v>
       </c>
       <c r="F1999" t="n">
         <v>0.902206697683442</v>
@@ -47551,10 +47551,10 @@
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.048665669297407</v>
+        <v>-3.026544964165135</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.912406410694913</v>
+        <v>1.921254692747821</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9471183063951831</v>
@@ -47574,10 +47574,10 @@
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.041610979082233</v>
+        <v>-3.019490273949961</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.911903642770527</v>
+        <v>1.920751924823436</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9541729966103569</v>
@@ -47597,10 +47597,10 @@
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.014659754755745</v>
+        <v>-2.992539049623473</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.932690286145864</v>
+        <v>1.941538568198773</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9690533426380761</v>
@@ -47620,10 +47620,10 @@
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.150612762812061</v>
+        <v>-3.128492057679789</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.062412215068298</v>
+        <v>2.071260497121206</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9690533426380761</v>
@@ -47643,10 +47643,10 @@
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.173020880616933</v>
+        <v>-3.150900175484662</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.045565662849341</v>
+        <v>2.05441394490225</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9690533426380761</v>
@@ -47666,10 +47666,10 @@
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.201245116194534</v>
+        <v>-3.179124411062262</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.036329968167939</v>
+        <v>2.045178250220848</v>
       </c>
       <c r="F2005" t="n">
         <v>0.9870300950893847</v>
@@ -47689,10 +47689,10 @@
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.210686042083064</v>
+        <v>-3.188565336950792</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.088807315534374</v>
+        <v>2.097655597587283</v>
       </c>
       <c r="F2006" t="n">
         <v>1.109457212632776</v>
@@ -47712,10 +47712,10 @@
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.262959649418705</v>
+        <v>-3.240838944286433</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.070788967145418</v>
+        <v>2.079637249198327</v>
       </c>
       <c r="F2007" t="n">
         <v>1.057183605297135</v>
@@ -47735,10 +47735,10 @@
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.339289627019611</v>
+        <v>-3.317168921887339</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.038368788998831</v>
+        <v>2.04721707105174</v>
       </c>
       <c r="F2008" t="n">
         <v>1.057183605297135</v>
@@ -47758,10 +47758,10 @@
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.541543347343964</v>
+        <v>-3.519422642211692</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.952287530471952</v>
+        <v>1.961135812524861</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8549298849727813</v>
@@ -47781,10 +47781,10 @@
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.703111772871219</v>
+        <v>-3.680991067738947</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.886094170471202</v>
+        <v>1.894942452524111</v>
       </c>
       <c r="F2010" t="n">
         <v>0.728146961174902</v>
@@ -47804,10 +47804,10 @@
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.811412434741339</v>
+        <v>-3.789291729609067</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.855847312589073</v>
+        <v>1.864695594641982</v>
       </c>
       <c r="F2011" t="n">
         <v>0.728146961174902</v>
@@ -47827,10 +47827,10 @@
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.904559906044705</v>
+        <v>-3.882439200912434</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.810593520850666</v>
+        <v>1.819441802903575</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6053177498923692</v>
@@ -47850,10 +47850,10 @@
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.932460693154178</v>
+        <v>-3.910339988021907</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.797957247133879</v>
+        <v>1.806805529186788</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5707208257494344</v>
@@ -47873,10 +47873,10 @@
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.054986795857072</v>
+        <v>-4.0328660907248</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.745711250029921</v>
+        <v>1.754559532082829</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4481947230465405</v>
@@ -47896,10 +47896,10 @@
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.285501292042661</v>
+        <v>-4.263380586910389</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.720211411146189</v>
+        <v>1.729059693199098</v>
       </c>
       <c r="F2015" t="n">
         <v>0.2176802268609518</v>
@@ -47919,10 +47919,10 @@
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.634246377267105</v>
+        <v>-4.612125672134833</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.721025096058258</v>
+        <v>1.729873378111167</v>
       </c>
       <c r="F2016" t="n">
         <v>0.108932272942054</v>
@@ -47942,10 +47942,10 @@
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.788232795043245</v>
+        <v>-4.766112089910973</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.728410798093442</v>
+        <v>1.737259080146351</v>
       </c>
       <c r="F2017" t="n">
         <v>0.108932272942054</v>
@@ -47965,10 +47965,10 @@
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.737710891215579</v>
+        <v>-4.715590186083308</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.734670761744629</v>
+        <v>1.743519043797538</v>
       </c>
       <c r="F2018" t="n">
         <v>0.108932272942054</v>
@@ -47988,10 +47988,10 @@
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.990186045223304</v>
+        <v>-4.968065340091032</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.645551189196953</v>
+        <v>1.654399471249862</v>
       </c>
       <c r="F2019" t="n">
         <v>0.108932272942054</v>
@@ -48011,10 +48011,10 @@
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.283081801702716</v>
+        <v>-5.260961096570444</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.529603421124132</v>
+        <v>1.538451703177041</v>
       </c>
       <c r="F2020" t="n">
         <v>0.108932272942054</v>
@@ -48034,10 +48034,10 @@
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.469745929837524</v>
+        <v>-5.447625224705252</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.45905951209753</v>
+        <v>1.467907794150439</v>
       </c>
       <c r="F2021" t="n">
         <v>0.08219330211749409</v>
@@ -48057,10 +48057,10 @@
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.615766616751486</v>
+        <v>-5.593645911619214</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.395729090068135</v>
+        <v>1.404577372121044</v>
       </c>
       <c r="F2022" t="n">
         <v>0.07311021032363713</v>
@@ -48080,10 +48080,10 @@
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.707480625861072</v>
+        <v>-5.6853599207288</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.521247543123345</v>
+        <v>1.530095825176254</v>
       </c>
       <c r="F2023" t="n">
         <v>0.07311021032363713</v>
@@ -48103,10 +48103,10 @@
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.739132284921041</v>
+        <v>-5.717011579788769</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.503433517463171</v>
+        <v>1.51228179951608</v>
       </c>
       <c r="F2024" t="n">
         <v>0.06794175307919692</v>
@@ -48126,10 +48126,10 @@
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.821067103189924</v>
+        <v>-5.798946398057653</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.480889007724109</v>
+        <v>1.489737289777018</v>
       </c>
       <c r="F2025" t="n">
         <v>0.05800700749211674</v>
@@ -48149,10 +48149,10 @@
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.923043225438332</v>
+        <v>-5.90092252030606</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.449024197280649</v>
+        <v>1.457872479333557</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.04396911475629084</v>
@@ -48172,10 +48172,10 @@
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.81303694196111</v>
+        <v>-5.790916236828838</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.485179597915713</v>
+        <v>1.494027879968622</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.02076454283901563</v>
@@ -48195,10 +48195,10 @@
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.669977366220184</v>
+        <v>-5.647856661087912</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.546653438934057</v>
+        <v>1.555501720986966</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.01275111624903635</v>
@@ -48218,10 +48218,10 @@
         <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.368530640748347</v>
+        <v>-5.346409935616075</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.674493012005328</v>
+        <v>1.683341294058237</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2886956092228009</v>
@@ -48241,10 +48241,10 @@
         <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.393120884983531</v>
+        <v>-5.371000179851259</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.665628092063965</v>
+        <v>1.674476374116874</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2886956092228009</v>
@@ -48264,10 +48264,10 @@
         <v>3.82407577475088</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.34208250897701</v>
+        <v>-5.319961803844738</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.686886346846329</v>
+        <v>1.695734628899238</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2886956092228009</v>
@@ -48287,10 +48287,10 @@
         <v>3.843113873625026</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.300943214110379</v>
+        <v>-5.278822508978108</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.722380163667127</v>
+        <v>1.731228445720036</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3298349040894317</v>
@@ -48310,10 +48310,10 @@
         <v>3.65929786974896</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.204308302091739</v>
+        <v>-5.182187596959468</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.577218124598518</v>
+        <v>1.586066406651426</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4264698161080717</v>
@@ -48333,10 +48333,10 @@
         <v>3.662799913822925</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.334889036622582</v>
+        <v>-5.31276833149031</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.528487874860144</v>
+        <v>1.537336156913053</v>
       </c>
       <c r="F2034" t="n">
         <v>0.2958890815772292</v>
@@ -48356,10 +48356,10 @@
         <v>3.647226732899007</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.17039270243162</v>
+        <v>-5.148271997299348</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.578713227612612</v>
+        <v>1.58756150966552</v>
       </c>
       <c r="F2035" t="n">
         <v>0.460385415768191</v>
@@ -48379,10 +48379,10 @@
         <v>3.646414443335437</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.197762635116052</v>
+        <v>-5.17564192998378</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.566952964975269</v>
+        <v>1.575801247028177</v>
       </c>
       <c r="F2036" t="n">
         <v>0.460385415768191</v>
@@ -48402,10 +48402,10 @@
         <v>3.656283222460509</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.208147830005942</v>
+        <v>-5.18602712487367</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.572667666144385</v>
+        <v>1.581515948197294</v>
       </c>
       <c r="F2037" t="n">
         <v>0.4500002208783017</v>
@@ -48425,10 +48425,10 @@
         <v>3.727120228236934</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.226735988728167</v>
+        <v>-5.204615283595895</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.636069408431921</v>
+        <v>1.644917690484829</v>
       </c>
       <c r="F2038" t="n">
         <v>0.4314120621560764</v>
@@ -48448,10 +48448,10 @@
         <v>3.723989239055233</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.227034535424202</v>
+        <v>-5.204913830291931</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.632819000571805</v>
+        <v>1.641667282624713</v>
       </c>
       <c r="F2039" t="n">
         <v>0.4311135154600405</v>
@@ -48471,10 +48471,10 @@
         <v>3.728520133994624</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.126211401733775</v>
+        <v>-5.104090696601503</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.677679148987367</v>
+        <v>1.686527431040276</v>
       </c>
       <c r="F2040" t="n">
         <v>0.4435777309443943</v>
@@ -48494,10 +48494,10 @@
         <v>3.728649387473168</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.935430040981368</v>
+        <v>-4.913309335849096</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.754120946766873</v>
+        <v>1.762969228819782</v>
       </c>
       <c r="F2041" t="n">
         <v>0.6343590916968016</v>
@@ -48517,10 +48517,10 @@
         <v>3.708486233210764</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.916913186939547</v>
+        <v>-4.894792481807276</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.741364534121198</v>
+        <v>1.750212816174107</v>
       </c>
       <c r="F2042" t="n">
         <v>0.6472892211220098</v>
@@ -48540,10 +48540,10 @@
         <v>3.743453169822823</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.861582599037785</v>
+        <v>-4.839461893905513</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.798463705893961</v>
+        <v>1.80731198794687</v>
       </c>
       <c r="F2043" t="n">
         <v>0.702619809023772</v>
@@ -48563,10 +48563,10 @@
         <v>3.73713973772426</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.849528472124822</v>
+        <v>-4.82740776699255</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.796971924560584</v>
+        <v>1.805820206613493</v>
       </c>
       <c r="F2044" t="n">
         <v>0.7146739359367348</v>
@@ -48586,10 +48586,10 @@
         <v>3.739020367908396</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.890683591693043</v>
+        <v>-4.868562886560771</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.782390506917432</v>
+        <v>1.791238788970341</v>
       </c>
       <c r="F2045" t="n">
         <v>0.6735188163685139</v>
@@ -48609,10 +48609,10 @@
         <v>3.751871393786279</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.78780300216445</v>
+        <v>-4.765682297032178</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.836393768606751</v>
+        <v>1.84524205065966</v>
       </c>
       <c r="F2046" t="n">
         <v>0.7763994058971068</v>
@@ -48632,10 +48632,10 @@
         <v>3.772074063959873</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.019403395333951</v>
+        <v>-4.997282690201679</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.763956281512545</v>
+        <v>1.772804563565454</v>
       </c>
       <c r="F2047" t="n">
         <v>0.7763994058971068</v>
@@ -48655,10 +48655,10 @@
         <v>3.772074063959873</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.037475903625563</v>
+        <v>-5.015355198493291</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.756727278195901</v>
+        <v>1.765575560248809</v>
       </c>
       <c r="F2048" t="n">
         <v>0.7763994058971068</v>
@@ -48678,10 +48678,10 @@
         <v>3.73232597755334</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.212582736202007</v>
+        <v>-5.190462031069735</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.646936458758789</v>
+        <v>1.655784740811698</v>
       </c>
       <c r="F2049" t="n">
         <v>0.7763994058971068</v>
@@ -48701,10 +48701,10 @@
         <v>3.73934859655028</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.181296715661552</v>
+        <v>-5.15917601052928</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.666473485971911</v>
+        <v>1.67532176802482</v>
       </c>
       <c r="F2050" t="n">
         <v>0.8076854264375621</v>
@@ -48724,10 +48724,10 @@
         <v>3.838519596123184</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.028271323548267</v>
+        <v>-5.006150618415996</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.82685464239013</v>
+        <v>1.835702924443039</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9607108185508463</v>
@@ -48747,10 +48747,10 @@
         <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.056578637421538</v>
+        <v>-5.052798187417715</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.002997941749113</v>
+        <v>2.004510121750643</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9607108185508463</v>
@@ -48770,10 +48770,10 @@
         <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.22317186253506</v>
+        <v>-5.219391412531238</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.905763603057787</v>
+        <v>1.907275783059316</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7941175934373239</v>
@@ -48793,10 +48793,10 @@
         <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.05010748315276</v>
+        <v>-5.046327033148938</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.978665757472425</v>
+        <v>1.980177937473954</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7941175934373239</v>
@@ -48816,10 +48816,10 @@
         <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.020861502697064</v>
+        <v>-5.017081052693241</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.987982204778199</v>
+        <v>1.989494384779728</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7941175934373239</v>
@@ -48839,10 +48839,10 @@
         <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.127787050574915</v>
+        <v>-5.124006600571092</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.942505224784693</v>
+        <v>1.944017404786222</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6871920455594726</v>
@@ -48862,10 +48862,10 @@
         <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.272805609082163</v>
+        <v>-5.269025159078341</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.885926603525028</v>
+        <v>1.887438783526557</v>
       </c>
       <c r="F2057" t="n">
         <v>0.542173487052224</v>
@@ -48885,10 +48885,10 @@
         <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.391147374866881</v>
+        <v>-5.387366924863058</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.938521136468894</v>
+        <v>1.940033316470423</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5528595256151141</v>
@@ -48908,10 +48908,10 @@
         <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.442557797187589</v>
+        <v>-5.438777347183766</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.91574266466655</v>
+        <v>1.917254844668078</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5528595256151141</v>
@@ -48931,10 +48931,10 @@
         <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.52197724839534</v>
+        <v>-5.518196798391518</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.883878012257739</v>
+        <v>1.885390192259267</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5528595256151141</v>
@@ -48954,10 +48954,10 @@
         <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.617440246312558</v>
+        <v>-5.613659796308736</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.845686706648895</v>
+        <v>1.847198886650424</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5528595256151141</v>
@@ -48977,10 +48977,10 @@
         <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.657460244356342</v>
+        <v>-5.653679794352519</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.827775103993992</v>
+        <v>1.829287283995521</v>
       </c>
       <c r="F2062" t="n">
         <v>0.5128395275713302</v>
@@ -49000,10 +49000,10 @@
         <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.712829406488535</v>
+        <v>-5.709048956484713</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.811361256888841</v>
+        <v>1.81287343689037</v>
       </c>
       <c r="F2063" t="n">
         <v>0.5128395275713302</v>
@@ -49023,10 +49023,10 @@
         <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.758267186319363</v>
+        <v>-5.75448673631554</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.792724508299443</v>
+        <v>1.794236688300972</v>
       </c>
       <c r="F2064" t="n">
         <v>0.4699945368931706</v>
@@ -49046,10 +49046,10 @@
         <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.675041729471698</v>
+        <v>-5.671261279467876</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.845889083888828</v>
+        <v>1.847401263890357</v>
       </c>
       <c r="F2065" t="n">
         <v>0.4699945368931706</v>
@@ -49069,10 +49069,10 @@
         <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.498751504866391</v>
+        <v>-5.494971054862568</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.900105874255679</v>
+        <v>1.901618054257208</v>
       </c>
       <c r="F2066" t="n">
         <v>0.4699945368931706</v>
@@ -49092,10 +49092,10 @@
         <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.315539841733296</v>
+        <v>-5.311759391729473</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.975821488972962</v>
+        <v>1.977333668974491</v>
       </c>
       <c r="F2067" t="n">
         <v>0.4699945368931706</v>
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.743613838209839</v>
+        <v>3.851682932805489</v>
       </c>
       <c r="C2068" t="n">
         <v>4.068185035827917</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.213478594249516</v>
+        <v>-5.240037944715622</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.982437173814364</v>
+        <v>1.971813433627921</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5720557843769503</v>
+        <v>0.5417159839070211</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.411418506454088</v>
+        <v>4.393214626172131</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240827.xlsx
+++ b/tame_output/ON/bt/strategyON_20240827.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.6%</t>
+          <t>423.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-685.6%</t>
+          <t>-683.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-179.0%</t>
+          <t>-178.3%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-280.1%</t>
+          <t>-281.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -48747,10 +48747,10 @@
         <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.052798187417715</v>
+        <v>-5.034457932289266</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.004510121750643</v>
+        <v>2.011846223802022</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9607108185508463</v>
@@ -48770,10 +48770,10 @@
         <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.219391412531238</v>
+        <v>-5.201051157402788</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.907275783059316</v>
+        <v>1.914611885110696</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7941175934373239</v>
@@ -48793,10 +48793,10 @@
         <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.046327033148938</v>
+        <v>-5.027986778020488</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.980177937473954</v>
+        <v>1.987514039525334</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7941175934373239</v>
@@ -48816,10 +48816,10 @@
         <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.017081052693241</v>
+        <v>-4.998740797564792</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.989494384779728</v>
+        <v>1.996830486831107</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7941175934373239</v>
@@ -48839,10 +48839,10 @@
         <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.124006600571092</v>
+        <v>-5.105666345442643</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.944017404786222</v>
+        <v>1.951353506837602</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6871920455594726</v>
@@ -48862,10 +48862,10 @@
         <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.269025159078341</v>
+        <v>-5.250684903949892</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.887438783526557</v>
+        <v>1.894774885577937</v>
       </c>
       <c r="F2057" t="n">
         <v>0.542173487052224</v>
@@ -48885,10 +48885,10 @@
         <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.387366924863058</v>
+        <v>-5.369026669734609</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.940033316470423</v>
+        <v>1.947369418521803</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5528595256151141</v>
@@ -48908,10 +48908,10 @@
         <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.438777347183766</v>
+        <v>-5.420437092055317</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.917254844668078</v>
+        <v>1.924590946719458</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5528595256151141</v>
@@ -48931,10 +48931,10 @@
         <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.518196798391518</v>
+        <v>-5.499856543263069</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.885390192259267</v>
+        <v>1.892726294310647</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5528595256151141</v>
@@ -48954,10 +48954,10 @@
         <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.613659796308736</v>
+        <v>-5.595319541180286</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.847198886650424</v>
+        <v>1.854534988701804</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5528595256151141</v>
@@ -48977,10 +48977,10 @@
         <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.653679794352519</v>
+        <v>-5.63533953922407</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.829287283995521</v>
+        <v>1.836623386046901</v>
       </c>
       <c r="F2062" t="n">
         <v>0.5128395275713302</v>
@@ -49000,10 +49000,10 @@
         <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.709048956484713</v>
+        <v>-5.690708701356264</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.81287343689037</v>
+        <v>1.82020953894175</v>
       </c>
       <c r="F2063" t="n">
         <v>0.5128395275713302</v>
@@ -49023,10 +49023,10 @@
         <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.75448673631554</v>
+        <v>-5.736146481187091</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.794236688300972</v>
+        <v>1.801572790352352</v>
       </c>
       <c r="F2064" t="n">
         <v>0.4699945368931706</v>
@@ -49046,10 +49046,10 @@
         <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.671261279467876</v>
+        <v>-5.652921024339427</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.847401263890357</v>
+        <v>1.854737365941737</v>
       </c>
       <c r="F2065" t="n">
         <v>0.4699945368931706</v>
@@ -49069,10 +49069,10 @@
         <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.494971054862568</v>
+        <v>-5.476630799734119</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.901618054257208</v>
+        <v>1.908954156308587</v>
       </c>
       <c r="F2066" t="n">
         <v>0.4699945368931706</v>
@@ -49092,10 +49092,10 @@
         <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.311759391729473</v>
+        <v>-5.293419136601024</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.977333668974491</v>
+        <v>1.984669771025871</v>
       </c>
       <c r="F2067" t="n">
         <v>0.4699945368931706</v>
@@ -49109,16 +49109,16 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.851682932805489</v>
+        <v>3.750151309940325</v>
       </c>
       <c r="C2068" t="n">
         <v>4.068185035827917</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.240037944715622</v>
+        <v>-5.221697689587173</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.971813433627921</v>
+        <v>1.979149535679301</v>
       </c>
       <c r="F2068" t="n">
         <v>0.5417159839070211</v>

--- a/tame_output/ON/bt/strategyON_20240827.xlsx
+++ b/tame_output/ON/bt/strategyON_20240827.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>57.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>110.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.2%</t>
+          <t>423.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-683.7%</t>
+          <t>-687.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-178.3%</t>
+          <t>-179.9%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-281.6%</t>
+          <t>-280.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-25.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2068"/>
+  <dimension ref="A1:G2069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382325</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812098</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987899</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.873530691357055</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.864816705103577</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.857856093008484</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.872318447389627</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.866850567848822</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.864348661859399</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.872049640096724</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.867830348443774</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.86995466236379</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.862696737347493</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.866295860868141</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.879623366922695</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.878643844538992</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.883338645593309</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.864532904377105</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.866275981001982</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.870205294836802</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.870883878754142</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.867881949974136</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.86946098698475</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.885355169786573</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.886501014226875</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
         <v>2.896589116788315</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942107</v>
       </c>
       <c r="C1933" t="n">
         <v>2.882626608189741</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.897915777423949</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.805559976746391</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.724821838231692</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.715258546863584</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.852289383555786</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.856856615547574</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.832598644308781</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111299</v>
       </c>
       <c r="C1941" t="n">
         <v>2.761136957710231</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.771309344142363</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.766255614716223</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.758031390160749</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.74828581656043</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.235941476466455</v>
+        <v>-4.258062181598728</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.995563420451878</v>
+        <v>0.9867151383989687</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4961693277674253</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498868</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.263721874367808</v>
+        <v>-4.285842579500081</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9959484630598758</v>
+        <v>0.9871001810069668</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4683889298660722</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.382102547097946</v>
+        <v>-4.404223252230219</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7869519139684737</v>
+        <v>0.7781036319155648</v>
       </c>
       <c r="F1951" t="n">
         <v>0.401171077715096</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.490716625541277</v>
+        <v>-4.51283733067355</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.863655943310347</v>
+        <v>0.8548076612574378</v>
       </c>
       <c r="F1952" t="n">
         <v>0.401171077715096</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.455307587293134</v>
+        <v>-4.477428292425407</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.892332584711927</v>
+        <v>0.883484302659018</v>
       </c>
       <c r="F1953" t="n">
         <v>0.401171077715096</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.416923924734983</v>
+        <v>-4.439044629867256</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9051054910775562</v>
+        <v>0.8962572090246472</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4395547402732472</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.239807594699817</v>
+        <v>-4.26192829983209</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9726810519369247</v>
+        <v>0.9638327698840155</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4395547402732472</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.284899839533363</v>
+        <v>-4.307020544665636</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9553275457654193</v>
+        <v>0.9464792637125103</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3776586971038574</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.105524418294595</v>
+        <v>-4.127645123426868</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.020864689567341</v>
+        <v>1.012016407514432</v>
       </c>
       <c r="F1957" t="n">
         <v>0.534435455274576</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982232</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.150538631815202</v>
+        <v>-4.172659336947474</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9836664594906879</v>
+        <v>0.9748181774377791</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5040865599599714</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.417543142087637</v>
+        <v>-4.439663847219909</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8825562177206596</v>
+        <v>0.8737079356677508</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3097235219170228</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760817</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.51874092352481</v>
+        <v>-4.540861628657082</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8412810270422919</v>
+        <v>0.8324327449893834</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2413147083717037</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815462</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.512229956910497</v>
+        <v>-4.534350662042769</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8414853752423337</v>
+        <v>0.8326370931894251</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2413147083717037</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.4931918292032</v>
+        <v>-4.515312534335472</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8456253455334977</v>
+        <v>0.8367770634805889</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1831310970405091</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131256</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.54570763147802</v>
+        <v>-4.567828336610292</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9439134262577598</v>
+        <v>0.935065144204851</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1831310970405091</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.559574392811938</v>
+        <v>-4.58169509794421</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9392000507103262</v>
+        <v>0.9303517686574174</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1452731803066862</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789127</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.514770221272008</v>
+        <v>-4.53689092640428</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9631302497232241</v>
+        <v>0.9542819676703154</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1452731803066862</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519913</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.367027251037006</v>
+        <v>-4.389147956169277</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9201776590944246</v>
+        <v>0.9113293770415158</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3130805375415693</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181174</v>
       </c>
       <c r="C1967" t="n">
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.450848472311704</v>
+        <v>-4.472969177443976</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8894427921160262</v>
+        <v>0.8805945100631174</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3130805375415693</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394733</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.44469576625892</v>
+        <v>-4.466816471391192</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8925662229287983</v>
+        <v>0.8837179408758895</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3192332435943536</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890617</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.461505064409422</v>
+        <v>-4.483625769541693</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8849229804087078</v>
+        <v>0.876074698355799</v>
       </c>
       <c r="F1969" t="n">
         <v>0.302423945443852</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.86736263679843</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.399207065633299</v>
+        <v>-4.421327770765571</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9761777337159776</v>
+        <v>0.9673294516630688</v>
       </c>
       <c r="F1970" t="n">
         <v>0.347718209718294</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992195</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.197416867968141</v>
+        <v>-4.219537573100413</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8591858144961679</v>
+        <v>0.8503375324432592</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5457364018874484</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.248303580654336</v>
+        <v>-4.270424285786608</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9091213617438652</v>
+        <v>0.9002730796909564</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4948496892012539</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.161692838004529</v>
+        <v>-4.183813543136801</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9583933949198316</v>
+        <v>0.9495451128669228</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5734754204064122</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.221902136009814</v>
+        <v>-4.244022841142086</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9328456565423893</v>
+        <v>0.9239973744894805</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5132661224011277</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.145480089577887</v>
+        <v>-4.167600794710159</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9619060931550885</v>
+        <v>0.9530578111021799</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5132661224011277</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.101106957939319</v>
+        <v>-4.12322766307159</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9795182132459521</v>
+        <v>0.9706699311930436</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5576392540396963</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.123587308798204</v>
+        <v>-4.145708013930475</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9649198670409889</v>
+        <v>0.9560715849880801</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5576392540396963</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.075931578237148</v>
+        <v>-4.09805228336942</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9903639162932159</v>
+        <v>0.9815156342403071</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6052949846007519</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.975413419738393</v>
+        <v>-3.997534124870665</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.035463553067443</v>
+        <v>1.026615271014534</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7058131430995065</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.95950809030604</v>
+        <v>-3.981628795438312</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.028580357316256</v>
+        <v>1.019732075263347</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6267004823902675</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932772</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.914669688697642</v>
+        <v>-3.936790393829914</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.050613420570244</v>
+        <v>1.041765138517335</v>
       </c>
       <c r="F1981" t="n">
         <v>0.631243915335137</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917054</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.934168144939651</v>
+        <v>-3.956288850071922</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.046974977704518</v>
+        <v>1.03812669565161</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5831592740552327</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405962</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.88996530785375</v>
+        <v>-3.912086012986022</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.070535715066716</v>
+        <v>1.061687433013807</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6273621111411332</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83819962926564</v>
+        <v>3.838199629265647</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.897524973690797</v>
+        <v>-3.919645678823069</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.065921849201144</v>
+        <v>1.057073567148236</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6821655151509525</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284881</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.739233556151525</v>
+        <v>-3.761354261283797</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.180486181399893</v>
+        <v>1.171637899346984</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6821655151509525</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.865338681321025</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.531591552517049</v>
+        <v>-3.553712257649321</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.261983687447936</v>
+        <v>1.253135405395028</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8898075187854286</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.480559459794521</v>
+        <v>-3.502680164926792</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.277344752775218</v>
+        <v>1.268496470722309</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9408396115079566</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404855</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.415335278667315</v>
+        <v>-3.437455983799587</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.320621829318805</v>
+        <v>1.311773547265896</v>
       </c>
       <c r="F1988" t="n">
         <v>1.006063792635162</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.377908258596181</v>
+        <v>-3.400028963728453</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.331553609646539</v>
+        <v>1.32270532759363</v>
       </c>
       <c r="F1989" t="n">
         <v>1.011315330664344</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.398019914630889</v>
+        <v>-3.420140619763161</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.324765739563896</v>
+        <v>1.315917457510987</v>
       </c>
       <c r="F1990" t="n">
         <v>1.022342675661763</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.369606651531006</v>
+        <v>-3.391727356663278</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.49668881582506</v>
+        <v>1.487840533772151</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9633671129153341</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.294824390505993</v>
+        <v>-3.316945095638265</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.646714629452882</v>
+        <v>1.637866347399973</v>
       </c>
       <c r="F1992" t="n">
         <v>1.038149373940347</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.268740306242185</v>
+        <v>-3.290861011374457</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.648856239172265</v>
+        <v>1.640007957119356</v>
       </c>
       <c r="F1993" t="n">
         <v>1.038149373940347</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.180862393133065</v>
+        <v>-3.202983098265336</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.682200599999692</v>
+        <v>1.673352317946784</v>
       </c>
       <c r="F1994" t="n">
         <v>1.154075016363698</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.171969931739781</v>
+        <v>-3.194090636872053</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.703311990283797</v>
+        <v>1.694463708230888</v>
       </c>
       <c r="F1995" t="n">
         <v>1.154075016363698</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.340446048709659</v>
+        <v>-3.362566753841931</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.62777659090043</v>
+        <v>1.618928308847521</v>
       </c>
       <c r="F1996" t="n">
         <v>1.126127180647117</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.79557406678271</v>
       </c>
       <c r="C1997" t="n">
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.894189856080219</v>
+        <v>-2.916310561212491</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.787548765140068</v>
+        <v>1.778700483087159</v>
       </c>
       <c r="F1997" t="n">
         <v>1.031408510977484</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.871468752397067</v>
+        <v>-2.893589457529338</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.787301229110233</v>
+        <v>1.778452947057324</v>
       </c>
       <c r="F1998" t="n">
         <v>1.031408510977484</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.000670565691109</v>
+        <v>-3.022791270823381</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.894526629643785</v>
+        <v>1.885678347590876</v>
       </c>
       <c r="F1999" t="n">
         <v>0.902206697683442</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.026544964165135</v>
+        <v>-3.048665669297407</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.921254692747821</v>
+        <v>1.912406410694913</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9471183063951831</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799967</v>
       </c>
       <c r="C2001" t="n">
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.019490273949961</v>
+        <v>-3.041610979082233</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.920751924823436</v>
+        <v>1.911903642770527</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9541729966103569</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331118</v>
       </c>
       <c r="C2002" t="n">
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.992539049623473</v>
+        <v>-3.014659754755745</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.941538568198773</v>
+        <v>1.932690286145864</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9690533426380761</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.128492057679789</v>
+        <v>-3.150612762812061</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.071260497121206</v>
+        <v>2.062412215068298</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9690533426380761</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714428</v>
       </c>
       <c r="C2004" t="n">
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.150900175484662</v>
+        <v>-3.173020880616933</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.05441394490225</v>
+        <v>2.045565662849341</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9690533426380761</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.179124411062262</v>
+        <v>-3.201245116194534</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.045178250220848</v>
+        <v>2.036329968167939</v>
       </c>
       <c r="F2005" t="n">
         <v>0.9870300950893847</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.188565336950792</v>
+        <v>-3.210686042083064</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.097655597587283</v>
+        <v>2.088807315534374</v>
       </c>
       <c r="F2006" t="n">
         <v>1.109457212632776</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.240838944286433</v>
+        <v>-3.262959649418705</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.079637249198327</v>
+        <v>2.070788967145418</v>
       </c>
       <c r="F2007" t="n">
         <v>1.057183605297135</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.317168921887339</v>
+        <v>-3.339289627019611</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.04721707105174</v>
+        <v>2.038368788998831</v>
       </c>
       <c r="F2008" t="n">
         <v>1.057183605297135</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887749</v>
       </c>
       <c r="C2009" t="n">
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.519422642211692</v>
+        <v>-3.541543347343964</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.961135812524861</v>
+        <v>1.952287530471952</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8549298849727813</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.680991067738947</v>
+        <v>-3.703111772871219</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.894942452524111</v>
+        <v>1.886094170471202</v>
       </c>
       <c r="F2010" t="n">
         <v>0.728146961174902</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.789291729609067</v>
+        <v>-3.811412434741339</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.864695594641982</v>
+        <v>1.855847312589073</v>
       </c>
       <c r="F2011" t="n">
         <v>0.728146961174902</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.882439200912434</v>
+        <v>-3.904559906044705</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.819441802903575</v>
+        <v>1.810593520850666</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6053177498923692</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006978</v>
       </c>
       <c r="C2013" t="n">
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.910339988021907</v>
+        <v>-3.932460693154178</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.806805529186788</v>
+        <v>1.797957247133879</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5707208257494344</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.68489577878739</v>
       </c>
       <c r="C2014" t="n">
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.0328660907248</v>
+        <v>-4.054986795857072</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.754559532082829</v>
+        <v>1.745711250029921</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4481947230465405</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.61934808158594</v>
       </c>
       <c r="C2015" t="n">
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.263380586910389</v>
+        <v>-4.285501292042661</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.729059693199098</v>
+        <v>1.720211411146189</v>
       </c>
       <c r="F2015" t="n">
         <v>0.2176802268609518</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814667</v>
       </c>
       <c r="C2016" t="n">
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.612125672134833</v>
+        <v>-4.634246377267105</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.729873378111167</v>
+        <v>1.721025096058258</v>
       </c>
       <c r="F2016" t="n">
         <v>0.108932272942054</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237091</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.766112089910973</v>
+        <v>-4.788232795043245</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.737259080146351</v>
+        <v>1.728410798093442</v>
       </c>
       <c r="F2017" t="n">
         <v>0.108932272942054</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.715590186083308</v>
+        <v>-4.737710891215579</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.743519043797538</v>
+        <v>1.734670761744629</v>
       </c>
       <c r="F2018" t="n">
         <v>0.108932272942054</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609756</v>
       </c>
       <c r="C2019" t="n">
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.968065340091032</v>
+        <v>-4.990186045223304</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.654399471249862</v>
+        <v>1.645551189196953</v>
       </c>
       <c r="F2019" t="n">
         <v>0.108932272942054</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.67402853597316</v>
       </c>
       <c r="C2020" t="n">
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.260961096570444</v>
+        <v>-5.283081801702716</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.538451703177041</v>
+        <v>1.529603421124132</v>
       </c>
       <c r="F2020" t="n">
         <v>0.108932272942054</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.447625224705252</v>
+        <v>-5.469745929837524</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.467907794150439</v>
+        <v>1.45905951209753</v>
       </c>
       <c r="F2021" t="n">
         <v>0.08219330211749409</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.593645911619214</v>
+        <v>-5.615766616751486</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.404577372121044</v>
+        <v>1.395729090068135</v>
       </c>
       <c r="F2022" t="n">
         <v>0.07311021032363713</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830331</v>
       </c>
       <c r="C2023" t="n">
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.6853599207288</v>
+        <v>-5.707480625861072</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.530095825176254</v>
+        <v>1.521247543123345</v>
       </c>
       <c r="F2023" t="n">
         <v>0.07311021032363713</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071553</v>
       </c>
       <c r="C2024" t="n">
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.717011579788769</v>
+        <v>-5.739132284921041</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.51228179951608</v>
+        <v>1.503433517463171</v>
       </c>
       <c r="F2024" t="n">
         <v>0.06794175307919692</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.798946398057653</v>
+        <v>-5.821067103189924</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.489737289777018</v>
+        <v>1.480889007724109</v>
       </c>
       <c r="F2025" t="n">
         <v>0.05800700749211674</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.90092252030606</v>
+        <v>-5.923043225438332</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.457872479333557</v>
+        <v>1.449024197280649</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.04396911475629084</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.790916236828838</v>
+        <v>-5.81303694196111</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.494027879968622</v>
+        <v>1.485179597915713</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.02076454283901563</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818524</v>
       </c>
       <c r="C2028" t="n">
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.647856661087912</v>
+        <v>-5.669977366220184</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.555501720986966</v>
+        <v>1.546653438934057</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.01275111624903635</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
         <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.346409935616075</v>
+        <v>-5.368530640748347</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.683341294058237</v>
+        <v>1.674493012005328</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2886956092228009</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679627</v>
       </c>
       <c r="C2030" t="n">
         <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.371000179851259</v>
+        <v>-5.393120884983531</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.674476374116874</v>
+        <v>1.665628092063965</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2886956092228009</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.82407577475088</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.319961803844738</v>
+        <v>-5.34208250897701</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.695734628899238</v>
+        <v>1.686886346846329</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2886956092228009</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.843113873625026</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.278822508978108</v>
+        <v>-5.300943214110379</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.731228445720036</v>
+        <v>1.722380163667127</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3298349040894317</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
         <v>3.65929786974896</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.182187596959468</v>
+        <v>-5.204308302091739</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.586066406651426</v>
+        <v>1.577218124598518</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4264698161080717</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.662799913822925</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.31276833149031</v>
+        <v>-5.334889036622582</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.537336156913053</v>
+        <v>1.528487874860144</v>
       </c>
       <c r="F2034" t="n">
         <v>0.2958890815772292</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833454</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.647226732899007</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.148271997299348</v>
+        <v>-5.17039270243162</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.58756150966552</v>
+        <v>1.578713227612612</v>
       </c>
       <c r="F2035" t="n">
         <v>0.460385415768191</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.82103066007763</v>
       </c>
       <c r="C2036" t="n">
         <v>3.646414443335437</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.17564192998378</v>
+        <v>-5.197762635116052</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.575801247028177</v>
+        <v>1.566952964975269</v>
       </c>
       <c r="F2036" t="n">
         <v>0.460385415768191</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147906</v>
+        <v>3.832307024147911</v>
       </c>
       <c r="C2037" t="n">
         <v>3.656283222460509</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.18602712487367</v>
+        <v>-5.208147830005942</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.581515948197294</v>
+        <v>1.572667666144385</v>
       </c>
       <c r="F2037" t="n">
         <v>0.4500002208783017</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.727120228236934</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.204615283595895</v>
+        <v>-5.226735988728167</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.644917690484829</v>
+        <v>1.636069408431921</v>
       </c>
       <c r="F2038" t="n">
         <v>0.4314120621560764</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.723989239055233</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.204913830291931</v>
+        <v>-5.227034535424202</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.641667282624713</v>
+        <v>1.632819000571805</v>
       </c>
       <c r="F2039" t="n">
         <v>0.4311135154600405</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.728520133994624</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.104090696601503</v>
+        <v>-5.126211401733775</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.686527431040276</v>
+        <v>1.677679148987367</v>
       </c>
       <c r="F2040" t="n">
         <v>0.4435777309443943</v>
@@ -48488,16 +48488,16 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.728649387473168</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.913309335849096</v>
+        <v>-4.935430040981368</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.762969228819782</v>
+        <v>1.754120946766873</v>
       </c>
       <c r="F2041" t="n">
         <v>0.6343590916968016</v>
@@ -48511,16 +48511,16 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.77523303390608</v>
       </c>
       <c r="C2042" t="n">
         <v>3.708486233210764</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.894792481807276</v>
+        <v>-4.916913186939547</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.750212816174107</v>
+        <v>1.741364534121198</v>
       </c>
       <c r="F2042" t="n">
         <v>0.6472892211220098</v>
@@ -48534,16 +48534,16 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
         <v>3.743453169822823</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.839461893905513</v>
+        <v>-4.861582599037785</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.80731198794687</v>
+        <v>1.798463705893961</v>
       </c>
       <c r="F2043" t="n">
         <v>0.702619809023772</v>
@@ -48557,16 +48557,16 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.73713973772426</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.82740776699255</v>
+        <v>-4.849528472124822</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.805820206613493</v>
+        <v>1.796971924560584</v>
       </c>
       <c r="F2044" t="n">
         <v>0.7146739359367348</v>
@@ -48580,16 +48580,16 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
         <v>3.739020367908396</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.868562886560771</v>
+        <v>-4.890683591693043</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.791238788970341</v>
+        <v>1.782390506917432</v>
       </c>
       <c r="F2045" t="n">
         <v>0.6735188163685139</v>
@@ -48603,16 +48603,16 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.751871393786279</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.765682297032178</v>
+        <v>-4.78780300216445</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.84524205065966</v>
+        <v>1.836393768606751</v>
       </c>
       <c r="F2046" t="n">
         <v>0.7763994058971068</v>
@@ -48626,16 +48626,16 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760311</v>
+        <v>3.646857607760316</v>
       </c>
       <c r="C2047" t="n">
         <v>3.772074063959873</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.997282690201679</v>
+        <v>-5.019403395333951</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.772804563565454</v>
+        <v>1.763956281512545</v>
       </c>
       <c r="F2047" t="n">
         <v>0.7763994058971068</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781702</v>
+        <v>3.666767386781706</v>
       </c>
       <c r="C2048" t="n">
         <v>3.772074063959873</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.015355198493291</v>
+        <v>-5.037475903625563</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.765575560248809</v>
+        <v>1.756727278195901</v>
       </c>
       <c r="F2048" t="n">
         <v>0.7763994058971068</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082831</v>
+        <v>3.670068888082835</v>
       </c>
       <c r="C2049" t="n">
         <v>3.73232597755334</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.190462031069735</v>
+        <v>-5.212582736202007</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.655784740811698</v>
+        <v>1.646936458758789</v>
       </c>
       <c r="F2049" t="n">
         <v>0.7763994058971068</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
         <v>3.73934859655028</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.15917601052928</v>
+        <v>-5.181296715661552</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.67532176802482</v>
+        <v>1.666473485971911</v>
       </c>
       <c r="F2050" t="n">
         <v>0.8076854264375621</v>
@@ -48718,16 +48718,16 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73059065867782</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
         <v>3.838519596123184</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.006150618415996</v>
+        <v>-5.028271323548267</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.835702924443039</v>
+        <v>1.82685464239013</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9607108185508463</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073879</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
         <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.034457932289266</v>
+        <v>-5.074447701655659</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.011846223802022</v>
+        <v>1.995850316055465</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9607108185508463</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903164</v>
+        <v>3.69913580090317</v>
       </c>
       <c r="C2053" t="n">
         <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.201051157402788</v>
+        <v>-5.241040926769181</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.914611885110696</v>
+        <v>1.898615977364138</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7941175934373239</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568379</v>
+        <v>3.708202704568383</v>
       </c>
       <c r="C2054" t="n">
         <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.027986778020488</v>
+        <v>-5.067976547386881</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.987514039525334</v>
+        <v>1.971518131778776</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7941175934373239</v>
@@ -48810,16 +48810,16 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682205</v>
       </c>
       <c r="C2055" t="n">
         <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.998740797564792</v>
+        <v>-5.038730566931185</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.996830486831107</v>
+        <v>1.98083457908455</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7941175934373239</v>
@@ -48833,16 +48833,16 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699424827539108</v>
       </c>
       <c r="C2056" t="n">
         <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.105666345442643</v>
+        <v>-5.145656114809036</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.951353506837602</v>
+        <v>1.935357599091045</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6871920455594726</v>
@@ -48856,16 +48856,16 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983734</v>
+        <v>3.689962785983738</v>
       </c>
       <c r="C2057" t="n">
         <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.250684903949892</v>
+        <v>-5.290674673316285</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.894774885577937</v>
+        <v>1.878778977831379</v>
       </c>
       <c r="F2057" t="n">
         <v>0.542173487052224</v>
@@ -48879,16 +48879,16 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969745</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.369026669734609</v>
+        <v>-5.409016439101002</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.947369418521803</v>
+        <v>1.931373510775245</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5528595256151141</v>
@@ -48902,16 +48902,16 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073535</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
         <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.420437092055317</v>
+        <v>-5.46042686142171</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.924590946719458</v>
+        <v>1.908595038972901</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5528595256151141</v>
@@ -48925,16 +48925,16 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720062</v>
+        <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
         <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.499856543263069</v>
+        <v>-5.539846312629462</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.892726294310647</v>
+        <v>1.87673038656409</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5528595256151141</v>
@@ -48948,16 +48948,16 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581129</v>
+        <v>3.736825137581133</v>
       </c>
       <c r="C2061" t="n">
         <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.595319541180286</v>
+        <v>-5.635309310546679</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.854534988701804</v>
+        <v>1.838539080955246</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5528595256151141</v>
@@ -48971,16 +48971,16 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500731</v>
+        <v>3.715393145500735</v>
       </c>
       <c r="C2062" t="n">
         <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.63533953922407</v>
+        <v>-5.675329308590463</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.836623386046901</v>
+        <v>1.820627478300343</v>
       </c>
       <c r="F2062" t="n">
         <v>0.5128395275713302</v>
@@ -48994,16 +48994,16 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636267</v>
+        <v>3.73610959863627</v>
       </c>
       <c r="C2063" t="n">
         <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.690708701356264</v>
+        <v>-5.730698470722657</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.82020953894175</v>
+        <v>1.804213631195192</v>
       </c>
       <c r="F2063" t="n">
         <v>0.5128395275713302</v>
@@ -49017,16 +49017,16 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73684305539601</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
         <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.736146481187091</v>
+        <v>-5.776136250553484</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.801572790352352</v>
+        <v>1.785576882605795</v>
       </c>
       <c r="F2064" t="n">
         <v>0.4699945368931706</v>
@@ -49040,16 +49040,16 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396419</v>
+        <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
         <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.652921024339427</v>
+        <v>-5.69291079370582</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.854737365941737</v>
+        <v>1.838741458195179</v>
       </c>
       <c r="F2065" t="n">
         <v>0.4699945368931706</v>
@@ -49063,16 +49063,16 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299173</v>
+        <v>3.794507029299177</v>
       </c>
       <c r="C2066" t="n">
         <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.476630799734119</v>
+        <v>-5.516620569100512</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.908954156308587</v>
+        <v>1.89295824856203</v>
       </c>
       <c r="F2066" t="n">
         <v>0.4699945368931706</v>
@@ -49086,16 +49086,16 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.794725278590407</v>
       </c>
       <c r="C2067" t="n">
         <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.293419136601024</v>
+        <v>-5.333408905967417</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.984669771025871</v>
+        <v>1.968673863279314</v>
       </c>
       <c r="F2067" t="n">
         <v>0.4699945368931706</v>
@@ -49109,22 +49109,45 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.750151309940325</v>
+        <v>3.776866743146285</v>
       </c>
       <c r="C2068" t="n">
         <v>4.068185035827917</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.221697689587173</v>
+        <v>-5.261687458953566</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.979149535679301</v>
+        <v>1.963153627932744</v>
       </c>
       <c r="F2068" t="n">
         <v>0.5417159839070211</v>
       </c>
       <c r="G2068" t="n">
         <v>4.393214626172131</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" s="2" t="n">
+        <v>45531</v>
+      </c>
+      <c r="B2069" t="n">
+        <v>3.853043335174236</v>
+      </c>
+      <c r="C2069" t="n">
+        <v>4.216470477531841</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>-5.261687458953566</v>
+      </c>
+      <c r="E2069" t="n">
+        <v>1.963153627932744</v>
+      </c>
+      <c r="F2069" t="n">
+        <v>0.5417159839070211</v>
+      </c>
+      <c r="G2069" t="n">
+        <v>4.209534274518209</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240827.xlsx
+++ b/tame_output/ON/bt/strategyON_20240827.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -763,12 +763,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>110.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>125.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.6%</t>
+          <t>423.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-687.7%</t>
+          <t>-682.5%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-179.9%</t>
+          <t>-180.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-280.1%</t>
+          <t>-299.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-169.8%</t>
+          <t>-160.6%</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-24.6%</t>
         </is>
       </c>
     </row>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495497</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.873530691357055</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.864816705103577</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.857856093008484</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.872318447389627</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.866850567848822</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.864348661859399</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.872049640096724</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.867830348443774</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.86995466236379</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.862696737347493</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.866295860868141</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.879623366922695</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.878643844538992</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.883338645593309</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.864532904377105</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.866275981001982</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.870205294836802</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.870883878754142</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.867881949974136</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.86946098698475</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539951</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.885355169786573</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.886501014226875</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577001</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.896589116788315</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942107</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.882626608189741</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.897915777423949</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.805559976746391</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.724821838231692</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.715258546863584</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.852289383555786</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.856856615547574</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.832598644308781</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111299</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.761136957710231</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.771309344142363</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.766255614716223</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316051</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.758031390160749</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803196</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.74828581656043</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798541</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.258062181598728</v>
+        <v>-4.235941476466455</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9867151383989687</v>
+        <v>0.995563420451878</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4961693277674253</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498868</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.285842579500081</v>
+        <v>-4.263721874367808</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9871001810069668</v>
+        <v>0.9959484630598758</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4683889298660722</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.404223252230219</v>
+        <v>-4.382102547097946</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7781036319155648</v>
+        <v>0.7869519139684737</v>
       </c>
       <c r="F1951" t="n">
         <v>0.401171077715096</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.51283733067355</v>
+        <v>-4.490716625541277</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8548076612574378</v>
+        <v>0.863655943310347</v>
       </c>
       <c r="F1952" t="n">
         <v>0.401171077715096</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.477428292425407</v>
+        <v>-4.455307587293134</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.883484302659018</v>
+        <v>0.892332584711927</v>
       </c>
       <c r="F1953" t="n">
         <v>0.401171077715096</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913429</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.439044629867256</v>
+        <v>-4.416923924734983</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8962572090246472</v>
+        <v>0.9051054910775562</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4395547402732472</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.26192829983209</v>
+        <v>-4.239807594699817</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9638327698840155</v>
+        <v>0.9726810519369247</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4395547402732472</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793906</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.307020544665636</v>
+        <v>-4.284899839533363</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9464792637125103</v>
+        <v>0.9553275457654193</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3776586971038574</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.127645123426868</v>
+        <v>-4.105524418294595</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.012016407514432</v>
+        <v>1.020864689567341</v>
       </c>
       <c r="F1957" t="n">
         <v>0.534435455274576</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982232</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.172659336947474</v>
+        <v>-4.150538631815202</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9748181774377791</v>
+        <v>0.9836664594906879</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5040865599599714</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509541</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.439663847219909</v>
+        <v>-4.417543142087637</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8737079356677508</v>
+        <v>0.8825562177206596</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3097235219170228</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760817</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.540861628657082</v>
+        <v>-4.51874092352481</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8324327449893834</v>
+        <v>0.8412810270422919</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2413147083717037</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815462</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.534350662042769</v>
+        <v>-4.512229956910497</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8326370931894251</v>
+        <v>0.8414853752423337</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2413147083717037</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.515312534335472</v>
+        <v>-4.4931918292032</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8367770634805889</v>
+        <v>0.8456253455334977</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1831310970405091</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131256</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.567828336610292</v>
+        <v>-4.54570763147802</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.935065144204851</v>
+        <v>0.9439134262577598</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1831310970405091</v>
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.58169509794421</v>
+        <v>-4.642610727410941</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9303517686574174</v>
+        <v>0.9059855168707251</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1452731803066862</v>
+        <v>0.1745918746528304</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.850550140332861</v>
+        <v>2.868141356940547</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789127</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.53689092640428</v>
+        <v>-4.597806555871011</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9542819676703154</v>
+        <v>0.9299157158836231</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1452731803066862</v>
+        <v>0.1745918746528304</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.856558670729787</v>
+        <v>2.874149887337473</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519913</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.389147956169277</v>
+        <v>-4.450063585636008</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9113293770415158</v>
+        <v>0.8869631252548236</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3130805375415693</v>
+        <v>0.3423992318877136</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.855193306347916</v>
+        <v>2.872784522955603</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181174</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.472969177443976</v>
+        <v>-4.533884806910707</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8805945100631174</v>
+        <v>0.8562282582764251</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3130805375415693</v>
+        <v>0.3423992318877136</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.857986927879397</v>
+        <v>2.875578144487084</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394733</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.466816471391192</v>
+        <v>-4.527732100857922</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8837179408758895</v>
+        <v>0.8593516890891972</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3192332435943536</v>
+        <v>0.3485519379404979</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.862340899902726</v>
+        <v>2.879932116510413</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890617</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.483625769541693</v>
+        <v>-4.544541399008424</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.876074698355799</v>
+        <v>0.8517084465691067</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.302423945443852</v>
+        <v>0.3317426397899962</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.851335797752535</v>
+        <v>2.868927014360222</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86736263679843</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.421327770765571</v>
+        <v>-4.482243400232302</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9673294516630688</v>
+        <v>0.9429631998763766</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.347718209718294</v>
+        <v>0.3770369040644383</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.944847910114021</v>
+        <v>2.962439126721708</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992195</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.219537573100413</v>
+        <v>-4.280453202567144</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8503375324432592</v>
+        <v>0.8259712806565669</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5457364018874484</v>
+        <v>0.5750550962335927</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.865950827129641</v>
+        <v>2.883542043737328</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852429</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.270424285786608</v>
+        <v>-4.331339915253339</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9002730796909564</v>
+        <v>0.8759068279042641</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4948496892012539</v>
+        <v>0.5241683835473983</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.905709031840099</v>
+        <v>2.923300248447786</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.183813543136801</v>
+        <v>-4.244729172603532</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9495451128669228</v>
+        <v>0.9251788610802305</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5734754204064122</v>
+        <v>0.6027941147525565</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.967512206679238</v>
+        <v>2.985103423286925</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.244022841142086</v>
+        <v>-4.304938470608817</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9239973744894805</v>
+        <v>0.8996311227027882</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5132661224011277</v>
+        <v>0.542584816747272</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.929922608700739</v>
+        <v>2.947513825308426</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.167600794710159</v>
+        <v>-4.22851642417689</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9530578111021799</v>
+        <v>0.9286915593154874</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5132661224011277</v>
+        <v>0.542584816747272</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.928414226740668</v>
+        <v>2.946005443348354</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316251</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.12322766307159</v>
+        <v>-4.184143292538321</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9706699311930436</v>
+        <v>0.9463036794063511</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5576392540396963</v>
+        <v>0.5869579483858406</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.954900973159245</v>
+        <v>2.972492189766931</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.145708013930475</v>
+        <v>-4.206623643397206</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9560715849880801</v>
+        <v>0.9317053332013878</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5576392540396963</v>
+        <v>0.5869579483858406</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.949294767297836</v>
+        <v>2.966885983905522</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190328</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.09805228336942</v>
+        <v>-4.15896791283615</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9815156342403071</v>
+        <v>0.9571493824536148</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6052949846007519</v>
+        <v>0.6346136789468962</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.984269962662274</v>
+        <v>3.00186117926996</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056962</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.997534124870665</v>
+        <v>-4.058449754337396</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.026615271014534</v>
+        <v>1.002249019227841</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7058131430995065</v>
+        <v>0.7351318374456508</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.049473231136251</v>
+        <v>3.067064447743938</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557297</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.981628795438312</v>
+        <v>-4.042544424905043</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.019732075263347</v>
+        <v>0.9953658234766547</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6267004823902675</v>
+        <v>0.6560191767364119</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.98876030718658</v>
+        <v>3.006351523794267</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932772</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.936790393829914</v>
+        <v>-3.997706023296645</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.041765138517335</v>
+        <v>1.017398886730642</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.631243915335137</v>
+        <v>0.6605626096812813</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.99558406956413</v>
+        <v>3.013175286171817</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917054</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.956288850071922</v>
+        <v>-4.017204479538654</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.03812669565161</v>
+        <v>1.013760443864917</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5831592740552327</v>
+        <v>0.612477968401377</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.970894224427266</v>
+        <v>2.988485441034952</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405962</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.912086012986022</v>
+        <v>-3.973001642452753</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.061687433013807</v>
+        <v>1.037321181227114</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6273621111411332</v>
+        <v>0.6566808054872775</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.003295529206643</v>
+        <v>3.02088674581433</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265647</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.919645678823069</v>
+        <v>-3.9805613082898</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.057073567148236</v>
+        <v>1.032707315361543</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6821655151509525</v>
+        <v>0.7114842094970968</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.034587572081782</v>
+        <v>3.052178788689469</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284881</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.761354261283797</v>
+        <v>-3.822269890750528</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.171637899346984</v>
+        <v>1.147271647560292</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6821655151509525</v>
+        <v>0.7114842094970968</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.085835337264822</v>
+        <v>3.103426553872509</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321025</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.553712257649321</v>
+        <v>-3.614627887116052</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.253135405395028</v>
+        <v>1.228769153608335</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8898075187854286</v>
+        <v>0.9191262131315729</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.208861244039761</v>
+        <v>3.226452460647447</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.502680164926792</v>
+        <v>-3.563595794393524</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.268496470722309</v>
+        <v>1.244130218935616</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9408396115079566</v>
+        <v>0.9701583058541009</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.234428727911547</v>
+        <v>3.252019944519234</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404855</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.437455983799587</v>
+        <v>-3.498371613266318</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.311773547265896</v>
+        <v>1.287407295479204</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.006063792635162</v>
+        <v>1.035382486981307</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.290750640680576</v>
+        <v>3.308341857288262</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.400028963728453</v>
+        <v>-3.460944593195185</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.32270532759363</v>
+        <v>1.298339075806938</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.011315330664344</v>
+        <v>1.040634025010488</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.289862535797365</v>
+        <v>3.307453752405052</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.420140619763161</v>
+        <v>-3.481056249229893</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.315917457510987</v>
+        <v>1.291551205724294</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.022342675661763</v>
+        <v>1.051661370007907</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.297735735127057</v>
+        <v>3.315326951734744</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.391727356663278</v>
+        <v>-3.452642986130009</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.487840533772151</v>
+        <v>1.463474281985459</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9633671129153341</v>
+        <v>0.9926858072614786</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.42290816850041</v>
+        <v>3.440499385108097</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.316945095638265</v>
+        <v>-3.377860725104997</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.637866347399973</v>
+        <v>1.613500095613281</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.038149373940347</v>
+        <v>1.067468068286491</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.587890434333235</v>
+        <v>3.605481650940922</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.290861011374457</v>
+        <v>-3.351776640841189</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.640007957119356</v>
+        <v>1.615641705332663</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.038149373940347</v>
+        <v>1.067468068286491</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.579598410347094</v>
+        <v>3.597189626954781</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.202983098265336</v>
+        <v>-3.263898727732068</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.673352317946784</v>
+        <v>1.648986066160091</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.154075016363698</v>
+        <v>1.183393710709842</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.647346991384884</v>
+        <v>3.664938207992571</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.194090636872053</v>
+        <v>-3.255006266338785</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.694463708230888</v>
+        <v>1.670097456444195</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.154075016363698</v>
+        <v>1.183393710709842</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.664901397111676</v>
+        <v>3.682492613719362</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.964311434698041</v>
+        <v>2.935359419630533</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.362566753841931</v>
+        <v>-3.327805061632933</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.618928308847521</v>
+        <v>1.603880970663613</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.126127180647117</v>
+        <v>1.217898987502747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.639987743086311</v>
+        <v>3.666098812132181</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.79557406678271</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.945581131885902</v>
+        <v>2.916629116818395</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.916310561212491</v>
+        <v>-2.881548869003494</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.778700483087159</v>
+        <v>1.76365314490325</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.031408510977484</v>
+        <v>1.123180317833114</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.564426238472393</v>
+        <v>3.590537307518264</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.936245154382807</v>
+        <v>2.907293139315299</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.893589457529338</v>
+        <v>-2.858827765320341</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.778452947057324</v>
+        <v>1.763405608873416</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.031408510977484</v>
+        <v>1.123180317833114</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.555090260969298</v>
+        <v>3.581201330015168</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.095151280233976</v>
+        <v>3.066199265166468</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.022791270823381</v>
+        <v>-2.988029578614384</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.885678347590876</v>
+        <v>1.870631009406968</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.902206697683442</v>
+        <v>0.9939785045390717</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.636475298844041</v>
+        <v>3.662586367889912</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.132229102727623</v>
+        <v>3.103277087660115</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.048665669297407</v>
+        <v>-3.013903977088409</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.912406410694913</v>
+        <v>1.897359072511004</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9471183063951831</v>
+        <v>1.038890113250813</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.700500086564733</v>
+        <v>3.726611155610603</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799967</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.128904458717168</v>
+        <v>3.09995244364966</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.041610979082233</v>
+        <v>-3.006849286873236</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.911903642770527</v>
+        <v>1.896856304586619</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9541729966103569</v>
+        <v>1.045944803465987</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.701408256683382</v>
+        <v>3.727519325729252</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331118</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.138910612361909</v>
+        <v>3.109958597294402</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.014659754755745</v>
+        <v>-2.979898062546748</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.932690286145864</v>
+        <v>1.917642947961955</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9690533426380761</v>
+        <v>1.060825149493706</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.720342617944755</v>
+        <v>3.746453686990626</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.323013744506869</v>
+        <v>3.294061729439361</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.150612762812061</v>
+        <v>-3.115851070603064</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.062412215068298</v>
+        <v>2.047364876884389</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9690533426380761</v>
+        <v>1.060825149493706</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.904445750089715</v>
+        <v>3.930556819135585</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714428</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.315130439409862</v>
+        <v>3.286178424342355</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.173020880616933</v>
+        <v>-3.138259188407936</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.045565662849341</v>
+        <v>2.030518324665433</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9690533426380761</v>
+        <v>1.060825149493706</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.896562444992708</v>
+        <v>3.922673514038578</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.3171844389595</v>
+        <v>3.288232423891992</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.201245116194534</v>
+        <v>-3.166483423985536</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.036329968167939</v>
+        <v>2.02128262998403</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9870300950893847</v>
+        <v>1.078801901945014</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.909402496013131</v>
+        <v>3.935513565059001</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.373438156681347</v>
+        <v>3.344486141613839</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.210686042083064</v>
+        <v>-3.175924349874066</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.088807315534374</v>
+        <v>2.073759977350465</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.109457212632776</v>
+        <v>1.201229019488406</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.039112484261013</v>
+        <v>4.065223553306883</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.376329251226648</v>
+        <v>3.34737723615914</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.262959649418705</v>
+        <v>-3.228197957209708</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.070788967145418</v>
+        <v>2.05574162896151</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.057183605297135</v>
+        <v>1.148955412152764</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.010639414404928</v>
+        <v>4.036750483450799</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.374441064120423</v>
+        <v>3.345489049052915</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.339289627019611</v>
+        <v>-3.304527934810614</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.038368788998831</v>
+        <v>2.023321450814922</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.057183605297135</v>
+        <v>1.148955412152764</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.008751227298704</v>
+        <v>4.034862296344574</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887749</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.369261293723285</v>
+        <v>3.340309278655778</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.541543347343964</v>
+        <v>-3.506781655134967</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.952287530471952</v>
+        <v>1.937240192288043</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8549298849727813</v>
+        <v>0.9467016918284108</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.882219224706954</v>
+        <v>3.908330293752824</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343068</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.367695303933437</v>
+        <v>3.33874328886593</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.703111772871219</v>
+        <v>-3.668350080662222</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.886094170471202</v>
+        <v>1.871046832287294</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.728146961174902</v>
+        <v>0.8199187680305314</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.804583480638379</v>
+        <v>3.830694549684249</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.380768710799356</v>
+        <v>3.351816695731848</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.811412434741339</v>
+        <v>-3.776650742532341</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.855847312589073</v>
+        <v>1.840799974405165</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.728146961174902</v>
+        <v>0.8199187680305314</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.817656887504298</v>
+        <v>3.843767956550168</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378394</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.372773907582296</v>
+        <v>3.343821892514788</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.904559906044705</v>
+        <v>-3.869798213835708</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.810593520850666</v>
+        <v>1.795546182666758</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6053177498923692</v>
+        <v>0.6970895567479987</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.735964557517718</v>
+        <v>3.762075626563588</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006978</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.371297948709298</v>
+        <v>3.34234593364179</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.932460693154178</v>
+        <v>-3.897699000945181</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.797957247133879</v>
+        <v>1.782909908949971</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5707208257494344</v>
+        <v>0.6624926326050639</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.713730444158959</v>
+        <v>3.739841513204829</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.368062392686497</v>
+        <v>3.339110377618989</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.054986795857072</v>
+        <v>-4.020225103648075</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.745711250029921</v>
+        <v>1.730663911846012</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4481947230465405</v>
+        <v>0.53996652990217</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.636979226514421</v>
+        <v>3.663090295560291</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.61934808158594</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.434768352277001</v>
+        <v>3.405816337209493</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.285501292042661</v>
+        <v>-4.250739599833664</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.720211411146189</v>
+        <v>1.70516407296228</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2176802268609518</v>
+        <v>0.3094520337165813</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.565376488393572</v>
+        <v>3.591487557439442</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814667</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.575080071278848</v>
+        <v>3.54612805621134</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.634246377267105</v>
+        <v>-4.599484685058107</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.721025096058258</v>
+        <v>1.70597775787435</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.108932272942054</v>
+        <v>0.2007040797976835</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.64043943504408</v>
+        <v>3.66655050408995</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.644060340424487</v>
+        <v>3.61510832535698</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.788232795043245</v>
+        <v>-4.753471102834248</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.728410798093442</v>
+        <v>1.713363459909533</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.108932272942054</v>
+        <v>0.2007040797976835</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.70941970418972</v>
+        <v>3.73553077323559</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.630111542544608</v>
+        <v>3.601159527477101</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.737710891215579</v>
+        <v>-4.702949199006582</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.734670761744629</v>
+        <v>1.719623423560721</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.108932272942054</v>
+        <v>0.2007040797976835</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.695470906309841</v>
+        <v>3.721581975355711</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.641982031600022</v>
+        <v>3.613030016532515</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.990186045223304</v>
+        <v>-4.955424353014307</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.645551189196953</v>
+        <v>1.630503851013045</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.108932272942054</v>
+        <v>0.2007040797976835</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.707341395365255</v>
+        <v>3.733452464411125</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67402853597316</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.643192566118966</v>
+        <v>3.614240551051458</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.283081801702716</v>
+        <v>-5.248320109493719</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.529603421124132</v>
+        <v>1.514556082940224</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.108932272942054</v>
+        <v>0.2007040797976835</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.708551929884198</v>
+        <v>3.734662998930069</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.647314308346287</v>
+        <v>3.61836229327878</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.469745929837524</v>
+        <v>-5.434984237628527</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.45905951209753</v>
+        <v>1.444012173913622</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.08219330211749409</v>
+        <v>0.1739651089731236</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.696630289616784</v>
+        <v>3.722741358662654</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.642392161082477</v>
+        <v>3.613440146014969</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.615766616751486</v>
+        <v>-5.581004924542489</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.395729090068135</v>
+        <v>1.380681751884226</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.07311021032363713</v>
+        <v>0.1648820171792666</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.686258287276659</v>
+        <v>3.71236935632253</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830331</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.804596217781521</v>
+        <v>3.775644202714013</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.707480625861072</v>
+        <v>-5.672718933652074</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.521247543123345</v>
+        <v>1.506200204939436</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.07311021032363713</v>
+        <v>0.1648820171792666</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.848462343975704</v>
+        <v>3.874573413021574</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071553</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.799442855745335</v>
+        <v>3.770490840677827</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.739132284921041</v>
+        <v>-5.704370592712044</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.503433517463171</v>
+        <v>1.488386179279263</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.06794175307919692</v>
+        <v>0.1597135599348264</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.840207907592853</v>
+        <v>3.866318976638723</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.809672273313826</v>
+        <v>3.780720258246319</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.821067103189924</v>
+        <v>-5.786305410980927</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.480889007724109</v>
+        <v>1.4658416695402</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.05800700749211674</v>
+        <v>0.1497788143477462</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.844476477809097</v>
+        <v>3.870587546854967</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.818597911769729</v>
+        <v>3.789645896702221</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.923043225438332</v>
+        <v>-5.888281533229335</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.449024197280649</v>
+        <v>1.43397685909674</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.04396911475629084</v>
+        <v>0.04780269209933863</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.792216442915954</v>
+        <v>3.818327511961825</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.810750799013904</v>
+        <v>3.781798783946396</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.81303694196111</v>
+        <v>-5.778275249752113</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.485179597915713</v>
+        <v>1.470132259731804</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.02076454283901563</v>
+        <v>0.07100726401661384</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.798292073310495</v>
+        <v>3.824403142356365</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818524</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.815000809735878</v>
+        <v>3.786048794668371</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.669977366220184</v>
+        <v>-5.635215674011187</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.546653438934057</v>
+        <v>1.531606100750149</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.01275111624903635</v>
+        <v>0.07902069060659311</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.807350139986457</v>
+        <v>3.833461209032327</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.822261692618414</v>
+        <v>3.793309677550907</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.368530640748347</v>
+        <v>-5.333768948539349</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.674493012005328</v>
+        <v>1.65944567382142</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2886956092228009</v>
+        <v>0.3804674160784304</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.995479058152095</v>
+        <v>4.021590127197965</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679627</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.823232870371125</v>
+        <v>3.794280855303617</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.393120884983531</v>
+        <v>-5.358359192774533</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.665628092063965</v>
+        <v>1.650580753880057</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2886956092228009</v>
+        <v>0.3804674160784304</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.996450235904805</v>
+        <v>4.022561304950676</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.82407577475088</v>
+        <v>3.795123759683373</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.34208250897701</v>
+        <v>-5.307320816768013</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.686886346846329</v>
+        <v>1.67183900866242</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2886956092228009</v>
+        <v>0.3804674160784304</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.997293140284561</v>
+        <v>4.023404209330431</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.843113873625026</v>
+        <v>3.814161858557518</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.300943214110379</v>
+        <v>-5.266181521901382</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.722380163667127</v>
+        <v>1.707332825483218</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3298349040894317</v>
+        <v>0.4216067109450612</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.041014816078685</v>
+        <v>4.067125885124556</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270048</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.65929786974896</v>
+        <v>3.630345854681453</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.204308302091739</v>
+        <v>-5.169546609882742</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.577218124598518</v>
+        <v>1.562170786414609</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4264698161080717</v>
+        <v>0.5182416229637011</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.915179759413804</v>
+        <v>3.941290828459674</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.662799913822925</v>
+        <v>3.633847898755417</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.334889036622582</v>
+        <v>-5.300127344413585</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.528487874860144</v>
+        <v>1.513440536676236</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2958890815772292</v>
+        <v>0.3876608884328586</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.840333362769262</v>
+        <v>3.866444431815133</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.647226732899007</v>
+        <v>3.6182747178315</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.17039270243162</v>
+        <v>-5.135631010222623</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.578713227612612</v>
+        <v>1.563665889428703</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.460385415768191</v>
+        <v>0.5521572226238205</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.923457982359922</v>
+        <v>3.949569051405792</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.82103066007763</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.646414443335437</v>
+        <v>3.617462428267929</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.197762635116052</v>
+        <v>-5.163000942907055</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.566952964975269</v>
+        <v>1.55190562679136</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.460385415768191</v>
+        <v>0.5521572226238205</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.922645692796352</v>
+        <v>3.948756761842222</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147911</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.656283222460509</v>
+        <v>3.627331207393002</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.208147830005942</v>
+        <v>-5.173386137796944</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.572667666144385</v>
+        <v>1.557620327960477</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4500002208783017</v>
+        <v>0.5417720277339312</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.926283354987491</v>
+        <v>3.95239442403336</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.727120228236934</v>
+        <v>3.698168213169427</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.226735988728167</v>
+        <v>-5.191974296519169</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.636069408431921</v>
+        <v>1.621022070248012</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4314120621560764</v>
+        <v>0.5231838690117059</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.985967465530581</v>
+        <v>4.01207853457645</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.723989239055233</v>
+        <v>3.695037223987725</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.227034535424202</v>
+        <v>-5.192272843215205</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.632819000571805</v>
+        <v>1.617771662387896</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4311135154600405</v>
+        <v>0.52288532231567</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.982657348331258</v>
+        <v>4.008768417377127</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.728520133994624</v>
+        <v>3.699568118927117</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.126211401733775</v>
+        <v>-5.091449709524777</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.677679148987367</v>
+        <v>1.662631810803458</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4435777309443943</v>
+        <v>0.5353495378000238</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.994666772561261</v>
+        <v>4.020777841607131</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.728649387473168</v>
+        <v>3.69969737240566</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.935430040981368</v>
+        <v>-4.900668348772371</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.754120946766873</v>
+        <v>1.739073608582965</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6343590916968016</v>
+        <v>0.7261308985524312</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.109264842491249</v>
+        <v>4.135375911537119</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.77523303390608</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.708486233210764</v>
+        <v>3.679534218143257</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.916913186939547</v>
+        <v>-4.88215149473055</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.741364534121198</v>
+        <v>1.726317195937289</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6472892211220098</v>
+        <v>0.7390610279776394</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.096859765883971</v>
+        <v>4.12297083492984</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.743453169822823</v>
+        <v>3.714501154755315</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.861582599037785</v>
+        <v>-4.826820906828788</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.798463705893961</v>
+        <v>1.783416367710053</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.702619809023772</v>
+        <v>0.7943916158794015</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.165025055237086</v>
+        <v>4.191136124282957</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.73713973772426</v>
+        <v>3.708187722656753</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.849528472124822</v>
+        <v>-4.814766779915825</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.796971924560584</v>
+        <v>1.781924586376676</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7146739359367348</v>
+        <v>0.8064457427923644</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.165944099286301</v>
+        <v>4.192055168332171</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811009</v>
+        <v>3.725010844811007</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.739020367908396</v>
+        <v>3.710068352840889</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.890683591693043</v>
+        <v>-4.855921899484046</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.782390506917432</v>
+        <v>1.767343168733523</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6735188163685139</v>
+        <v>0.7652906232241434</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.143131657729505</v>
+        <v>4.169242726775375</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382918</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.751871393786279</v>
+        <v>3.722919378718771</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.78780300216445</v>
+        <v>-4.753041309955453</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.836393768606751</v>
+        <v>1.821346430422843</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7763994058971068</v>
+        <v>0.8681712127527363</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.217711037324543</v>
+        <v>4.243822106370413</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760316</v>
+        <v>3.646857607760314</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.772074063959873</v>
+        <v>3.743122048892365</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.019403395333951</v>
+        <v>-4.984641703124954</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.763956281512545</v>
+        <v>1.748908943328637</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7763994058971068</v>
+        <v>0.8681712127527363</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.237913707498137</v>
+        <v>4.264024776544007</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781706</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.772074063959873</v>
+        <v>3.743122048892365</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.037475903625563</v>
+        <v>-5.002714211416565</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.756727278195901</v>
+        <v>1.741679940011992</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7763994058971068</v>
+        <v>0.8681712127527363</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.237913707498137</v>
+        <v>4.264024776544007</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082835</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.73232597755334</v>
+        <v>3.703373962485832</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.212582736202007</v>
+        <v>-5.17782104399301</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.646936458758789</v>
+        <v>1.631889120574881</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7763994058971068</v>
+        <v>0.8681712127527363</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.198165621091603</v>
+        <v>4.224276690137474</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.73934859655028</v>
+        <v>3.710396581482772</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.181296715661552</v>
+        <v>-5.146535023452555</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.666473485971911</v>
+        <v>1.651426147788003</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8076854264375621</v>
+        <v>0.8994572332931917</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.223959852412817</v>
+        <v>4.250070921458687</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677823</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.838519596123184</v>
+        <v>3.809567581055676</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.028271323548267</v>
+        <v>-4.99350963133927</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.82685464239013</v>
+        <v>1.811807304206221</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9607108185508463</v>
+        <v>1.052482625406476</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.414946087253692</v>
+        <v>4.441057156299562</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.025985821031476</v>
+        <v>3.997033805963969</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.074447701655659</v>
+        <v>-5.021816945212541</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.995850316055465</v>
+        <v>1.987950603565205</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9607108185508463</v>
+        <v>1.052482625406476</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.602412312161984</v>
+        <v>4.628523381207854</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.995388772385558</v>
+        <v>3.966436757318051</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.241040926769181</v>
+        <v>-5.188410170326063</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.898615977364138</v>
+        <v>1.890716264873878</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7941175934373239</v>
+        <v>0.8858894002929534</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.471859328447953</v>
+        <v>4.497970397493823</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568383</v>
+        <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.999065175047276</v>
+        <v>3.970113159979769</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.067976547386881</v>
+        <v>-5.015345790943763</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.971518131778776</v>
+        <v>1.963618419288516</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7941175934373239</v>
+        <v>0.8858894002929534</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.47553573110967</v>
+        <v>4.501646800155541</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682205</v>
+        <v>3.740601586682203</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.996683230170771</v>
+        <v>3.967731215103264</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.038730566931185</v>
+        <v>-4.986099810488066</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.98083457908455</v>
+        <v>1.97293486659429</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7941175934373239</v>
+        <v>0.8858894002929534</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.473153786233166</v>
+        <v>4.499264855279036</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539108</v>
+        <v>3.699424827539106</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.993976469328406</v>
+        <v>3.965024454260899</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.145656114809036</v>
+        <v>-5.093025358365917</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.935357599091045</v>
+        <v>1.927457886600785</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6871920455594726</v>
+        <v>0.778963852415102</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.40629169666409</v>
+        <v>4.43240276570996</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983738</v>
+        <v>3.689962785983736</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.995405271471641</v>
+        <v>3.966453256404133</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.290674673316285</v>
+        <v>-5.238043916873166</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.878778977831379</v>
+        <v>1.870879265341119</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.542173487052224</v>
+        <v>0.6339452939078535</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.320709363702975</v>
+        <v>4.346820432748846</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969748</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.095336510729394</v>
+        <v>4.066384495661886</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.409016439101002</v>
+        <v>-5.356385682657884</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.931373510775245</v>
+        <v>1.923473798284985</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5528595256151141</v>
+        <v>0.6446313324707436</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.427052226098462</v>
+        <v>4.453163295144332</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073537</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.093122207855332</v>
+        <v>4.064170192787825</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.46042686142171</v>
+        <v>-5.407796104978591</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.908595038972901</v>
+        <v>1.900695326482641</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5528595256151141</v>
+        <v>0.6446313324707436</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.424837923224401</v>
+        <v>4.450948992270271</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.093025335929622</v>
+        <v>4.064073320862114</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.539846312629462</v>
+        <v>-5.487215556186343</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.87673038656409</v>
+        <v>1.86883067407383</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5528595256151141</v>
+        <v>0.6446313324707436</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.424741051298691</v>
+        <v>4.45085212034456</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581133</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.093019229487665</v>
+        <v>4.064067214420158</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.635309310546679</v>
+        <v>-5.582678554103561</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.838539080955246</v>
+        <v>1.830639368464986</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5528595256151141</v>
+        <v>0.6446313324707436</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.424734944856734</v>
+        <v>4.450846013902604</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500735</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.091115626050276</v>
+        <v>4.062163610982768</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.675329308590463</v>
+        <v>-5.622698552147344</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.820627478300343</v>
+        <v>1.812727765810083</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5128395275713302</v>
+        <v>0.6046113344269597</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.398819342593074</v>
+        <v>4.424930411638944</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73610959863627</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.096849443798003</v>
+        <v>4.067897428730495</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.730698470722657</v>
+        <v>-5.678067714279538</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.804213631195192</v>
+        <v>1.796313918704933</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5128395275713302</v>
+        <v>0.6046113344269597</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.404553160340801</v>
+        <v>4.430664229386671</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396013</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.096387807140935</v>
+        <v>4.067435792073427</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.776136250553484</v>
+        <v>-5.723505494110365</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.785576882605795</v>
+        <v>1.777677170115533</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4699945368931706</v>
+        <v>0.5617663437488001</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.378384529276838</v>
+        <v>4.404495598322708</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396422</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.116262199991255</v>
+        <v>4.087310184923746</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.69291079370582</v>
+        <v>-5.640280037262701</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.838741458195179</v>
+        <v>1.830841745704918</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4699945368931706</v>
+        <v>0.5617663437488001</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.398258922127157</v>
+        <v>4.424369991173027</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299177</v>
+        <v>3.794507029299175</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.099962900515982</v>
+        <v>4.071010885448474</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.516620569100512</v>
+        <v>-5.463989812657394</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.89295824856203</v>
+        <v>1.885058536071769</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4699945368931706</v>
+        <v>0.5617663437488001</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.381959622651885</v>
+        <v>4.408070691697755</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590407</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.102393849980028</v>
+        <v>4.073441834912519</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.333408905967417</v>
+        <v>-5.280778149524298</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.968673863279314</v>
+        <v>1.960774150789053</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4699945368931706</v>
+        <v>0.5617663437488001</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.38439057211593</v>
+        <v>4.4105016411618</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776866743146285</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.068185035827917</v>
+        <v>4.039233020760409</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.261687458953566</v>
+        <v>-5.209056702510448</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.963153627932744</v>
+        <v>1.955253915442483</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5417159839070211</v>
+        <v>0.6334877907626507</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.393214626172131</v>
+        <v>4.419325695217999</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.853043335174236</v>
+        <v>3.886133536857576</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.216470477531841</v>
+        <v>4.221340149804842</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.261687458953566</v>
+        <v>-5.209056702510448</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.963153627932744</v>
+        <v>1.955253915442483</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5417159839070211</v>
+        <v>0.6334877907626507</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.209534274518209</v>
+        <v>4.21440394679121</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240827.xlsx
+++ b/tame_output/ON/bt/strategyON_20240827.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>110.5%</t>
+          <t>87.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-81.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.3%</t>
+          <t>126.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-616.8%</t>
+          <t>-639.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.8%</t>
+          <t>415.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-682.5%</t>
+          <t>-725.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-247.1%</t>
+          <t>-256.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-109.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-180.7%</t>
+          <t>-195.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-228.8%</t>
+          <t>-250.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>-65.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-299.9%</t>
+          <t>-134.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-160.6%</t>
+          <t>-192.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-137.6%</t>
+          <t>-151.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-47.8%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.455994000230163</v>
+        <v>-1.677857997786343</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.534166243036052</v>
+        <v>2.44542064401358</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.253873330619843</v>
+        <v>1.032009333063663</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.86924426581377</v>
+        <v>3.736125867280062</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.822062727374816</v>
+        <v>-2.043926724930996</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.38082305148464</v>
+        <v>2.292077452462168</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.88780460347519</v>
+        <v>0.6659406059190102</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.642687328833428</v>
+        <v>3.50956893029972</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.0305535088265</v>
+        <v>-2.252417506382681</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.317765028642734</v>
+        <v>2.229019429620263</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.6793138220235055</v>
+        <v>0.4574498244673257</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.537931149701186</v>
+        <v>3.404812751167478</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.277754693591722</v>
+        <v>-2.499618691147902</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.226983305145214</v>
+        <v>2.138237706122742</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.699467175522318</v>
+        <v>0.4776031779661382</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.558121912209042</v>
+        <v>3.425003513675334</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.770139721615819</v>
+        <v>-2.992003719171999</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.031135685979308</v>
+        <v>1.942390086956836</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.2070821474982212</v>
+        <v>-0.01478185005795857</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.263797287438316</v>
+        <v>3.130678888904608</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.155320112545891</v>
+        <v>-3.377184110102072</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.875606068420142</v>
+        <v>1.78686046939767</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.2070821474982212</v>
+        <v>-0.01478185005795857</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.262339826251179</v>
+        <v>3.129221427717471</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.405190792560473</v>
+        <v>-3.627054790116653</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.777426919868925</v>
+        <v>1.688681320846454</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.2433448673286845</v>
+        <v>0.02148086977250468</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.285866581604073</v>
+        <v>3.152748183070365</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.611702569447494</v>
+        <v>-3.833566567003674</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.690928267770375</v>
+        <v>1.602182668747903</v>
       </c>
       <c r="F1857" t="n">
-        <v>0.036833090441663</v>
+        <v>-0.1850309071145168</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.158065574128118</v>
+        <v>3.02494717559441</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178241</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.931046644527996</v>
+        <v>-4.152910642084176</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.564963564438434</v>
+        <v>1.476217965415962</v>
       </c>
       <c r="F1858" t="n">
-        <v>0.036833090441663</v>
+        <v>-0.1850309071145168</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.159838500828378</v>
+        <v>3.02672010229467</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.31725647580377</v>
+        <v>-4.539120473359952</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.396812519395528</v>
+        <v>1.308066920373056</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.05393984927578033</v>
+        <v>-0.2758038468319601</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.091707624465316</v>
+        <v>2.958589225931608</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.551950469936322</v>
+        <v>-4.773814467492504</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.291219696744598</v>
+        <v>1.202474097722126</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.04760358204652515</v>
+        <v>-0.269467579602705</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.08379415980496</v>
+        <v>2.950675761271252</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.887613117166775</v>
+        <v>-5.109477114722957</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.155535229508382</v>
+        <v>1.06678963048591</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.11553456753543</v>
+        <v>-0.3373985650916098</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.041616160167582</v>
+        <v>2.908497761633874</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.964057447369647</v>
+        <v>-5.185921444925828</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.131445057661475</v>
+        <v>1.042699458639003</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.03508905844176807</v>
+        <v>-0.2569530559979479</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.096371025858021</v>
+        <v>2.963252627324313</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.329184830008393</v>
+        <v>-5.551048827564575</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9846486196118076</v>
+        <v>0.8959030205893352</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3313998427407806</v>
+        <v>-0.5532638402969604</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.917839070284444</v>
+        <v>2.784720671750737</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.737773607189072</v>
+        <v>-5.959637604745254</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8199746527542953</v>
+        <v>0.7312290537318229</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.9618526174776388</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.671447347990797</v>
+        <v>2.538328949457089</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.851534019211937</v>
+        <v>-6.073398016768119</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7696559204166098</v>
+        <v>0.6809103213941374</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.9618526174776388</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.666632780462257</v>
+        <v>2.533514381928549</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.267925893498934</v>
+        <v>-6.489789891055116</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6010932213106881</v>
+        <v>0.5123476222882157</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.9618526174776388</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.664626831071135</v>
+        <v>2.531508432537427</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.629099523315922</v>
+        <v>-6.850963520872104</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4668824600525721</v>
+        <v>0.3781368610300997</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.9618526174776388</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.674885521739814</v>
+        <v>2.541767123206106</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.972358042958941</v>
+        <v>-7.194222040515123</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3256786173410595</v>
+        <v>0.2369330183185876</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.9618526174776388</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.670985086885509</v>
+        <v>2.537866688351801</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.020560860201285</v>
+        <v>-7.242424857757467</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3048024104991232</v>
+        <v>0.2160568114766508</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.9618526174776388</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.669390006940509</v>
+        <v>2.536271608406802</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.317222202011482</v>
+        <v>-7.539086199567664</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1899168497042525</v>
+        <v>0.1011712506817801</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-1.030595753211518</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.631923101429391</v>
+        <v>2.498804702895683</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.503941910320785</v>
+        <v>-7.725805907876967</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1112026618461281</v>
+        <v>0.02245706282365578</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-1.030595753211518</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.627896796894988</v>
+        <v>2.49477839836128</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.886943299063416</v>
+        <v>-8.108807296619597</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.04209999497250827</v>
+        <v>-0.1308455939949802</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-1.030595753211518</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.627794695573404</v>
+        <v>2.494676297039696</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.891429744264805</v>
+        <v>-8.113293741820986</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.04132305708163386</v>
+        <v>-0.1300686561041058</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-1.035082198412906</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.627674344424</v>
+        <v>2.494555945890292</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.250960066768808</v>
+        <v>-8.472824064324987</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1797848827851847</v>
+        <v>-0.2685304818076562</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-1.035082198412906</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.63302464772205</v>
+        <v>2.499906249188343</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.30130913022303</v>
+        <v>-8.523173127779209</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1920084882096957</v>
+        <v>-0.2807540872321677</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8635672643109484</v>
+        <v>-1.085431261867128</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.610731229606695</v>
+        <v>2.477612831072987</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.398928407644426</v>
+        <v>-8.620792405200605</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2280144485564857</v>
+        <v>-0.3167600475789571</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9611865417323451</v>
+        <v>-1.183050539288525</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.555201413775626</v>
+        <v>2.422083015241918</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.452999907152785</v>
+        <v>-8.674863904708964</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2467494920382567</v>
+        <v>-0.3354950910607282</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.015258041240704</v>
+        <v>-1.237122038796884</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.525652070392182</v>
+        <v>2.392533671858474</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.657258082482649</v>
+        <v>-8.879122080038828</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3229395650515601</v>
+        <v>-0.4116851640740316</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.142896985854693</v>
+        <v>-1.364760983410873</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.454581900742431</v>
+        <v>2.321463502208724</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.690910920991122</v>
+        <v>-8.912774918547301</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3319181459705134</v>
+        <v>-0.4206637449929849</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.243310353771731</v>
+        <v>-1.465174351327911</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.398816434476645</v>
+        <v>2.265698035942937</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.82999703560998</v>
+        <v>-9.051861033166158</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3721808903246351</v>
+        <v>-0.4609264893471066</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.382396468390588</v>
+        <v>-1.604260465946767</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.330736467198752</v>
+        <v>2.197618068665044</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.005121452996523</v>
+        <v>-9.226985450552702</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4276754365317355</v>
+        <v>-0.5164210355542069</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.557520885777131</v>
+        <v>-1.779384883333311</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.240217037514342</v>
+        <v>2.107098638980634</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.239573547011013</v>
+        <v>-9.461437544567191</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5286754390391275</v>
+        <v>-0.617421038061599</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.557520885777131</v>
+        <v>-1.779384883333311</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.232997872612747</v>
+        <v>2.099879474079039</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.343948278037459</v>
+        <v>-9.565812275593638</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5770975222236823</v>
+        <v>-0.6658431212461537</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.661895616803577</v>
+        <v>-1.883759614359757</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.163700843222903</v>
+        <v>2.030582444689195</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.506461743736043</v>
+        <v>-9.728325741292222</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6409871186645595</v>
+        <v>-0.729732717687031</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.759529047222264</v>
+        <v>-1.981393044778444</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.106236574810247</v>
+        <v>1.973118176276539</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.632498537104333</v>
+        <v>-9.854362534660511</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6887081073827606</v>
+        <v>-0.777453706405232</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.734277424412522</v>
+        <v>-1.956141421968701</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.124081277125207</v>
+        <v>1.990962878591499</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.575426765208402</v>
+        <v>-9.797290762764581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6618890629379877</v>
+        <v>-0.7506346619604591</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.734277424412522</v>
+        <v>-1.956141421968701</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.128071612811608</v>
+        <v>1.9949532142779</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.717098606932522</v>
+        <v>-9.938962604488701</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7200330265263775</v>
+        <v>-0.8087786255488489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.734277424412522</v>
+        <v>-1.956141421968701</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.126596385912866</v>
+        <v>1.993477987379158</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.667507762507688</v>
+        <v>-9.889371760063867</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6851432785915712</v>
+        <v>-0.7738888776140427</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.684686579987688</v>
+        <v>-1.906550577543868</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.171404302732639</v>
+        <v>2.038285904198931</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.518589428035831</v>
+        <v>-9.74045342559201</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6386270784495118</v>
+        <v>-0.7273726774719833</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.653436989252515</v>
+        <v>-1.875300986808695</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.17710292352706</v>
+        <v>2.043984524993352</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.292744275316419</v>
+        <v>-9.5146082728726</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5387099443255381</v>
+        <v>-0.6274555433480105</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.611510313665351</v>
+        <v>-1.833374311221531</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.211838001915567</v>
+        <v>2.078719603381859</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.168165618978827</v>
+        <v>-9.390029616535008</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4877393372344425</v>
+        <v>-0.5764849362569149</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.611510313665351</v>
+        <v>-1.833374311221531</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.212977146471625</v>
+        <v>2.079858747937918</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.221060907023114</v>
+        <v>-9.442924904579295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.5062636782900496</v>
+        <v>-0.595009277312522</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.606554967576905</v>
+        <v>-1.828418965133085</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.218584128286801</v>
+        <v>2.085465729753093</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.148927731735233</v>
+        <v>-9.370791729291414</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4716767039362608</v>
+        <v>-0.5604223029587327</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.606554967576905</v>
+        <v>-1.828418965133085</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.224317832525437</v>
+        <v>2.091199433991729</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.077561339125586</v>
+        <v>-9.299425336681766</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.452867409286267</v>
+        <v>-0.5416130083087394</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.535188574967257</v>
+        <v>-1.757052572523437</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.257400405697361</v>
+        <v>2.124282007163653</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.984102305140361</v>
+        <v>-9.205966302696542</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.4253672770050847</v>
+        <v>-0.5141128760275571</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.535188574967257</v>
+        <v>-1.757052572523437</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.247516924384453</v>
+        <v>2.114398525850746</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.97344912358693</v>
+        <v>-9.19531312114311</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4229405648830857</v>
+        <v>-0.5116861639055581</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.535188574967257</v>
+        <v>-1.757052572523437</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.24568236388508</v>
+        <v>2.112563965351372</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.875542084910439</v>
+        <v>-9.09740608246662</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3840780643859505</v>
+        <v>-0.4728236634084229</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.467202825106701</v>
+        <v>-1.68906682266288</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.286173498827953</v>
+        <v>2.153055100294245</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.851588543934481</v>
+        <v>-9.073452541490662</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3738281418500735</v>
+        <v>-0.4625737408725459</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.443249284130743</v>
+        <v>-1.665113281686923</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.301214129559021</v>
+        <v>2.168095731025313</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.587528605611684</v>
+        <v>-8.809392603167865</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2814644826827069</v>
+        <v>-0.3702100817051792</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.179189345807947</v>
+        <v>-1.401053343364127</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.446389776390946</v>
+        <v>2.313271377857238</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.880448982106846</v>
+        <v>-8.102312979663028</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.001419666941072428</v>
+        <v>-0.09016526596354524</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.179189345807947</v>
+        <v>-1.401053343364127</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.443602742730645</v>
+        <v>2.310484344196937</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.840264683740656</v>
+        <v>-8.062128681296837</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.01499767629324511</v>
+        <v>-0.0737479227292277</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.139005047441756</v>
+        <v>-1.360869044997936</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.468056945638201</v>
+        <v>2.334938547104493</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.676864812801293</v>
+        <v>-7.898728810357475</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.07972444588974703</v>
+        <v>-0.009021153132725779</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9756051765023934</v>
+        <v>-1.197469174058573</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.565463689422576</v>
+        <v>2.432345290888868</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.443383590571695</v>
+        <v>-7.665247588127876</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1810413636194386</v>
+        <v>0.0922957645969662</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7421239542727949</v>
+        <v>-0.9639879518289747</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.713476851598187</v>
+        <v>2.580358453064479</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.293717199564179</v>
+        <v>-7.515581197120361</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2380157097094857</v>
+        <v>0.1492701106870129</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6492204630302589</v>
+        <v>-0.8710844605864387</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.76632673603075</v>
+        <v>2.633208337497042</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.161441725933293</v>
+        <v>-7.383305723489475</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.1921866851689948</v>
+        <v>0.103441086146522</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5169449893993723</v>
+        <v>-0.7388089869555521</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.746952806216436</v>
+        <v>2.613834407682728</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.005703393373551</v>
+        <v>-7.227567390929733</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2572970788805282</v>
+        <v>0.1685514798580554</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3612066568396307</v>
+        <v>-0.5830706543958105</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.843210866439918</v>
+        <v>2.71009246790621</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.920738726644231</v>
+        <v>-7.142602724200414</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3041892867959151</v>
+        <v>0.2154436877734418</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2762419901103111</v>
+        <v>-0.4981059876664909</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.907096007701168</v>
+        <v>2.77397760916746</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.026328716417336</v>
+        <v>-7.248192713973518</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1339773612874544</v>
+        <v>0.0452317622649816</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3818319798834155</v>
+        <v>-0.6036959774395954</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.715766084238087</v>
+        <v>2.582647685704379</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987904</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.958094131791908</v>
+        <v>-7.179958129348091</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2098155370147117</v>
+        <v>0.1210699379922389</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3634166570108795</v>
+        <v>-0.5852806545670594</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.775359619838695</v>
+        <v>2.642241221304987</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.873530691357055</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.810154090384309</v>
+        <v>-7.032018087940491</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1491126308895838</v>
+        <v>0.06036703186711101</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3430957411023219</v>
+        <v>-0.5649597386585018</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.667673246695662</v>
+        <v>2.534554848161954</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.864816705103577</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.75718456813032</v>
+        <v>-6.979048565686503</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1615864535377014</v>
+        <v>0.07284085451522815</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2901262188483331</v>
+        <v>-0.5119902164045129</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.690740973794577</v>
+        <v>2.557622575260869</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098113</v>
       </c>
       <c r="C1912" t="n">
         <v>2.857856093008484</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.591396372170029</v>
+        <v>-6.813260369726212</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2209411198267244</v>
+        <v>0.1321955208042516</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2901262188483331</v>
+        <v>-0.5119902164045129</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.683780361699484</v>
+        <v>2.550661963165776</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493424</v>
       </c>
       <c r="C1913" t="n">
         <v>2.872318447389627</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.558033165691261</v>
+        <v>-6.779897163247443</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2487487567993751</v>
+        <v>0.1600031577769019</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2901262188483331</v>
+        <v>-0.5119902164045129</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.698242716080627</v>
+        <v>2.565124317546919</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722821</v>
       </c>
       <c r="C1914" t="n">
         <v>2.866850567848822</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.449774028568739</v>
+        <v>-6.671638026124922</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2865845321075788</v>
+        <v>0.1978389330851056</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2901262188483331</v>
+        <v>-0.5119902164045129</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.692774836539822</v>
+        <v>2.559656438006114</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.82805292879205</v>
       </c>
       <c r="C1915" t="n">
         <v>2.864348661859399</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.326482893751608</v>
+        <v>-6.548346891307791</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.333399080045008</v>
+        <v>0.2446534810225347</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1668350840312026</v>
+        <v>-0.3886990815873824</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.764247611440677</v>
+        <v>2.631129212906969</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.872049640096724</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.273786026620317</v>
+        <v>-6.495650024176499</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3621788051348496</v>
+        <v>0.2734332061123768</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1141382168999114</v>
+        <v>-0.3360022144560912</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.803566709956777</v>
+        <v>2.670448311423069</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.867830348443774</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.030020584636873</v>
+        <v>-6.251884582193055</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4554656902752781</v>
+        <v>0.3667200912528048</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1141382168999114</v>
+        <v>-0.3360022144560912</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.799347418303828</v>
+        <v>2.66622901977012</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.86995466236379</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.9402449122604</v>
+        <v>-6.162108909816583</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4935002731458829</v>
+        <v>0.40475467412341</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.05253877198560136</v>
+        <v>-0.2744027695417812</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.83843139917243</v>
+        <v>2.705313000638722</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.862696737347493</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.690394518311326</v>
+        <v>-6.091035878529391</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5861825057092149</v>
+        <v>0.4259259616219886</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.05253877198560136</v>
+        <v>-0.2744027695417812</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.831173474156132</v>
+        <v>2.698055075622424</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.866295860868141</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.514502425843894</v>
+        <v>-5.915143786061959</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6601384662168366</v>
+        <v>0.4998819221296102</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.05253877198560136</v>
+        <v>-0.2744027695417812</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.834772597676781</v>
+        <v>2.701654199143073</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.879623366922695</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.34305596282143</v>
+        <v>-5.743697323039496</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7420445574803756</v>
+        <v>0.5817880133931492</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1189076910368618</v>
+        <v>-0.1029563065193181</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.950967981544812</v>
+        <v>2.817849583011105</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.878643844538992</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.263033675712309</v>
+        <v>-5.663675035930375</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7730739499403207</v>
+        <v>0.6128174058530949</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1989299781459827</v>
+        <v>-0.02293401941019713</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.998001831426582</v>
+        <v>2.864883432892874</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.883338645593309</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.199397933478375</v>
+        <v>-5.60003929369644</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8032230478882121</v>
+        <v>0.6429665038009857</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2625657203799173</v>
+        <v>0.04070172282373741</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.04087807782126</v>
+        <v>2.907759679287552</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.864532904377105</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.10570061526198</v>
+        <v>-5.506341975480045</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8218962339585656</v>
+        <v>0.6616396898713397</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2625657203799173</v>
+        <v>0.04070172282373741</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.022072336605055</v>
+        <v>2.888953938071348</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.866275981001982</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.116203238327269</v>
+        <v>-5.516844598545334</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8194382613573277</v>
+        <v>0.6591817172701013</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2520630973146284</v>
+        <v>0.03019909975844853</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.01751383939076</v>
+        <v>2.884395440857052</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.870205294836802</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.043960670156074</v>
+        <v>-5.444602030374139</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8522646024606257</v>
+        <v>0.6920080583733994</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2520630973146284</v>
+        <v>0.03019909975844853</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.02144315322558</v>
+        <v>2.888324754691872</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.870883878754142</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.026246983278209</v>
+        <v>-5.426888343496274</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8600286611291117</v>
+        <v>0.6997721170418854</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2552444262115452</v>
+        <v>0.03338042865536534</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.02403053448107</v>
+        <v>2.890912135947362</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.867881949974136</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.917442097798482</v>
+        <v>-5.318083458016547</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.900548686540996</v>
+        <v>0.7402921424537698</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2552444262115452</v>
+        <v>0.03338042865536534</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.021028605701063</v>
+        <v>2.887910207167355</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.86946098698475</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.697421299761471</v>
+        <v>-5.098062659979536</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9901360427664143</v>
+        <v>0.8298794986791882</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3964642712795254</v>
+        <v>0.1746002737233456</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.107339549752465</v>
+        <v>2.974221151218758</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.885355169786573</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.564553610698193</v>
+        <v>-4.965194970916259</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.059177301193549</v>
+        <v>0.8989207571063225</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3964642712795254</v>
+        <v>0.1746002737233456</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.123233732554289</v>
+        <v>2.990115334020581</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496266</v>
       </c>
       <c r="C1931" t="n">
         <v>2.886501014226875</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.444380527333695</v>
+        <v>-4.84502188755176</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.10839237897965</v>
+        <v>0.9481358348924238</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5166373546440244</v>
+        <v>0.2947733570878445</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.19648342701329</v>
+        <v>3.063365028479582</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577003</v>
       </c>
       <c r="C1932" t="n">
         <v>2.896589116788315</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.309127166003718</v>
+        <v>-4.709768526221783</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.172581826073081</v>
+        <v>1.012325281985855</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6518907159740015</v>
+        <v>0.4300267184178216</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.287723546372716</v>
+        <v>3.154605147839008</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942109</v>
       </c>
       <c r="C1933" t="n">
         <v>2.882626608189741</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.36900199336141</v>
+        <v>-4.769643353579475</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.13466938653143</v>
+        <v>0.9744128424442036</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5920158886163094</v>
+        <v>0.3701518910601295</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.237836141359527</v>
+        <v>3.104717742825819</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.897915777423949</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.249181762450573</v>
+        <v>-4.649823122668638</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.197886648129973</v>
+        <v>1.037630104042747</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5920158886163094</v>
+        <v>0.3701518910601295</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.253125310593735</v>
+        <v>3.120006912060028</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.805559976746391</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.251651468912379</v>
+        <v>-4.652292829130444</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.104542964867692</v>
+        <v>0.944286420780466</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5895461821545032</v>
+        <v>0.3676821845983234</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.159287686039093</v>
+        <v>3.026169287505385</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>2.724821838231692</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.320021655236389</v>
+        <v>-4.720663015454455</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9964567518233896</v>
+        <v>0.8362002077361632</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.3769578836345383</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.084114966946124</v>
+        <v>2.950996568412416</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>2.715258546863584</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.333809708083436</v>
+        <v>-4.734451068301501</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9813782393164621</v>
+        <v>0.8211216952292359</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.3769578836345383</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.074551675578015</v>
+        <v>2.941433277044307</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
         <v>2.852289383555786</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.389329783976025</v>
+        <v>-4.789971144194091</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.096201045651629</v>
+        <v>0.9359445015644026</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.3769578836345383</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.211582512270217</v>
+        <v>3.078464113736509</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.856856615547574</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.213855524183556</v>
+        <v>-4.614496884401621</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.170957981560404</v>
+        <v>1.010701437473178</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.3769578836345383</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.216149744262005</v>
+        <v>3.083031345728297</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.832598644308781</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.205931149598642</v>
+        <v>-4.606572509816707</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.149869760155577</v>
+        <v>0.9896132160683508</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.3769578836345383</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.191891773023212</v>
+        <v>3.058773374489504</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111301</v>
       </c>
       <c r="C1941" t="n">
         <v>2.761136957710231</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.199652947028793</v>
+        <v>-4.600294307246858</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.080919354584966</v>
+        <v>0.9206628104977401</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6051000837605671</v>
+        <v>0.3832360862043874</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.124197007966571</v>
+        <v>2.991078609432863</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.78434395226417</v>
       </c>
       <c r="C1942" t="n">
         <v>2.771309344142363</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.139800327825069</v>
+        <v>-4.540441688043135</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.115032788698588</v>
+        <v>0.9547762446113619</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6051000837605671</v>
+        <v>0.3832360862043874</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.134369394398703</v>
+        <v>3.001250995864996</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742306</v>
       </c>
       <c r="C1943" t="n">
         <v>2.766255614716223</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.053556864798692</v>
+        <v>-4.454198225016757</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.144476444482999</v>
+        <v>0.9842199003957732</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6051000837605671</v>
+        <v>0.3832360862043874</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.129315664972564</v>
+        <v>2.996197266438856</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316053</v>
       </c>
       <c r="C1944" t="n">
         <v>2.758031390160749</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.098863684197672</v>
+        <v>-4.499505044415737</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.118129492167933</v>
+        <v>0.9578729480807069</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5642899207513363</v>
+        <v>0.3424259231951566</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.096605342611551</v>
+        <v>2.963486944077843</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803198</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.127896788899973</v>
+        <v>-4.528538149118038</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.107068123320114</v>
+        <v>0.9468115792328879</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5642899207513363</v>
+        <v>0.3424259231951566</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.097157215644653</v>
+        <v>2.964038817110945</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809505</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.035086307449113</v>
+        <v>-4.435727667667178</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.073465007791824</v>
+        <v>0.9132084637045974</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6571004022021957</v>
+        <v>0.4352364046460159</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.082116196406534</v>
+        <v>2.948997797872826</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560432</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.079475776778541</v>
+        <v>-4.480117136996606</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.057582695984653</v>
+        <v>0.8973261518974274</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.612710932872768</v>
+        <v>0.3908469353165883</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.057355990733478</v>
+        <v>2.92423759219977</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472743</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.196017381883883</v>
+        <v>-4.596658742101948</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.006041762454239</v>
+        <v>0.8457852183670134</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4961693277674253</v>
+        <v>0.2743053302112455</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.982506736181995</v>
+        <v>2.849388337648287</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.235941476466455</v>
+        <v>-4.636582836684521</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.995563420451878</v>
+        <v>0.8353068763646516</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4961693277674253</v>
+        <v>0.2743053302112455</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.987998032012662</v>
+        <v>2.854879633478955</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.68959784049887</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.263721874367808</v>
+        <v>-4.664363234585873</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9959484630598758</v>
+        <v>0.8356919189726497</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4683889298660722</v>
+        <v>0.2465249323098924</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.98282699504039</v>
+        <v>2.849708596506682</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.64306962170533</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.382102547097946</v>
+        <v>-4.782743907316012</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7869519139684737</v>
+        <v>0.6266953698812476</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.401171077715096</v>
+        <v>0.1793070801589162</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.780852003750458</v>
+        <v>2.64773360521675</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729274</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.490716625541277</v>
+        <v>-4.891357985759343</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.863655943310347</v>
+        <v>0.7033993992231209</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.401171077715096</v>
+        <v>0.1793070801589162</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.901001664469663</v>
+        <v>2.767883265935955</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190773</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.455307587293134</v>
+        <v>-4.8559489475112</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.892332584711927</v>
+        <v>0.7320760406247009</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.401171077715096</v>
+        <v>0.1793070801589162</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.915514690571986</v>
+        <v>2.782396292038278</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913431</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.416923924734983</v>
+        <v>-4.817565284953049</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9051054910775562</v>
+        <v>0.7448489469903301</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4395547402732472</v>
+        <v>0.2176907427170674</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.935964329449245</v>
+        <v>2.802845930915538</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532491</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.239807594699817</v>
+        <v>-4.640448954917883</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9726810519369247</v>
+        <v>0.8124245078496983</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4395547402732472</v>
+        <v>0.2176907427170674</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.932693358294547</v>
+        <v>2.799574959760839</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793908</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.284899839533363</v>
+        <v>-4.685541199751428</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9553275457654193</v>
+        <v>0.7950710016781932</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3776586971038574</v>
+        <v>0.1557946995476776</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.896239124154826</v>
+        <v>2.763120725621119</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.75072937701124</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.105524418294595</v>
+        <v>-4.506165778512661</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.020864689567341</v>
+        <v>0.8606081454801147</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.534435455274576</v>
+        <v>0.3125714577183963</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.984092154363672</v>
+        <v>2.850973755829964</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982234</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.150538631815202</v>
+        <v>-4.551179992033267</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9836664594906879</v>
+        <v>0.8234099154034618</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5040865599599714</v>
+        <v>0.2822225624037917</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.946690272506499</v>
+        <v>2.813571873972791</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.417543142087637</v>
+        <v>-4.818184502305702</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8825562177206596</v>
+        <v>0.7222996736334335</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3097235219170228</v>
+        <v>0.0878595243608431</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.835764012019676</v>
+        <v>2.702645613485968</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760819</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.51874092352481</v>
+        <v>-4.919382283742875</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8412810270422919</v>
+        <v>0.6810244829550658</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2413147083717037</v>
+        <v>0.01945071081552391</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.793922645788986</v>
+        <v>2.660804247255278</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815464</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.512229956910497</v>
+        <v>-4.912871317128563</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8414853752423337</v>
+        <v>0.6812288311551076</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2413147083717037</v>
+        <v>0.01945071081552391</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.791522607343302</v>
+        <v>2.658404208809594</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378109</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.4931918292032</v>
+        <v>-4.893833189421265</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8456253455334977</v>
+        <v>0.6853688014462715</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1831310970405091</v>
+        <v>-0.03873290051567063</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.753137159752831</v>
+        <v>2.620018761219123</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131257</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.54570763147802</v>
+        <v>-4.946348991696086</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9439134262577598</v>
+        <v>0.7836568821705336</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1831310970405091</v>
+        <v>-0.03873290051567063</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.872431561387021</v>
+        <v>2.739313162853313</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067872</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.642610727410941</v>
+        <v>-4.960215753030004</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9059855168707251</v>
+        <v>0.7789435066231001</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1745918746528304</v>
+        <v>-0.07659081724949357</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.868141356940547</v>
+        <v>2.717431741799153</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.597806555871011</v>
+        <v>-4.915411581490074</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9299157158836231</v>
+        <v>0.802873705635998</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1745918746528304</v>
+        <v>-0.07659081724949357</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.874149887337473</v>
+        <v>2.723440272196079</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519915</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.450063585636008</v>
+        <v>-4.767668611255071</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8869631252548236</v>
+        <v>0.7599211150071985</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3423992318877136</v>
+        <v>0.09121653998538959</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.872784522955603</v>
+        <v>2.722074907814208</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181176</v>
       </c>
       <c r="C1967" t="n">
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.533884806910707</v>
+        <v>-4.85148983252977</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8562282582764251</v>
+        <v>0.7291862480288001</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3423992318877136</v>
+        <v>0.09121653998538959</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.875578144487084</v>
+        <v>2.724868529345689</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394735</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.527732100857922</v>
+        <v>-4.845337126476985</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8593516890891972</v>
+        <v>0.7323096788415722</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3485519379404979</v>
+        <v>0.09736924603817387</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.879932116510413</v>
+        <v>2.729222501369018</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890619</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.544541399008424</v>
+        <v>-4.862146424627487</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8517084465691067</v>
+        <v>0.7246664363214816</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3317426397899962</v>
+        <v>0.08055994788767223</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.868927014360222</v>
+        <v>2.718217399218827</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798432</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.482243400232302</v>
+        <v>-4.799848425851365</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9429631998763766</v>
+        <v>0.8159211896287515</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3770369040644383</v>
+        <v>0.1258542121621143</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.962439126721708</v>
+        <v>2.811729511580313</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992197</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.280453202567144</v>
+        <v>-4.598058228186207</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8259712806565669</v>
+        <v>0.6989292704089416</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5750550962335927</v>
+        <v>0.3238724043312687</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.883542043737328</v>
+        <v>2.732832428595933</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.84144481785243</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.331339915253339</v>
+        <v>-4.648944940872402</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8759068279042641</v>
+        <v>0.748864817656639</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5241683835473983</v>
+        <v>0.2729856916450741</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.923300248447786</v>
+        <v>2.772590633306391</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.244729172603532</v>
+        <v>-4.562334198222595</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9251788610802305</v>
+        <v>0.7981368508326054</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6027941147525565</v>
+        <v>0.3516114228502324</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.985103423286925</v>
+        <v>2.83439380814553</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.304938470608817</v>
+        <v>-4.62254349622788</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8996311227027882</v>
+        <v>0.7725891124551632</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.542584816747272</v>
+        <v>0.2914021248449479</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.947513825308426</v>
+        <v>2.796804210167031</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.22851642417689</v>
+        <v>-4.546121449795953</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9286915593154874</v>
+        <v>0.8016495490678623</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.542584816747272</v>
+        <v>0.2914021248449479</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.946005443348354</v>
+        <v>2.79529582820696</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316253</v>
       </c>
       <c r="C1976" t="n">
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.184143292538321</v>
+        <v>-4.501748318157384</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9463036794063511</v>
+        <v>0.819261669158726</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5869579483858406</v>
+        <v>0.3357752564835165</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.972492189766931</v>
+        <v>2.821782574625537</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105971</v>
       </c>
       <c r="C1977" t="n">
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.206623643397206</v>
+        <v>-4.524228669016269</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9317053332013878</v>
+        <v>0.8046633229537625</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5869579483858406</v>
+        <v>0.3357752564835165</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.966885983905522</v>
+        <v>2.816176368764128</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190329</v>
       </c>
       <c r="C1978" t="n">
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.15896791283615</v>
+        <v>-4.476572938455213</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9571493824536148</v>
+        <v>0.8301073722059895</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6346136789468962</v>
+        <v>0.3834309870445721</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.00186117926996</v>
+        <v>2.851151564128566</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569622</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.058449754337396</v>
+        <v>-4.376054779956458</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.002249019227841</v>
+        <v>0.8752070089802162</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7351318374456508</v>
+        <v>0.4839491455433267</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.067064447743938</v>
+        <v>2.916354832602543</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557298</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.042544424905043</v>
+        <v>-4.360149450524106</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9953658234766547</v>
+        <v>0.8683238132290296</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6560191767364119</v>
+        <v>0.4048364848340878</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.006351523794267</v>
+        <v>2.855641908652872</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932774</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.997706023296645</v>
+        <v>-4.315311048915707</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.017398886730642</v>
+        <v>0.8903568764830174</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6605626096812813</v>
+        <v>0.4093799177789573</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.013175286171817</v>
+        <v>2.862465671030423</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917056</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.017204479538654</v>
+        <v>-4.334809505157716</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.013760443864917</v>
+        <v>0.8867184336172922</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.612477968401377</v>
+        <v>0.361295276499053</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.988485441034952</v>
+        <v>2.837775825893558</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405964</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.973001642452753</v>
+        <v>-4.290606668071815</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.037321181227114</v>
+        <v>0.9102791709794895</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6566808054872775</v>
+        <v>0.4054981135849534</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.02088674581433</v>
+        <v>2.870177130672935</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265649</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.9805613082898</v>
+        <v>-4.316930804748654</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.032707315361543</v>
+        <v>0.8981595167780017</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7114842094970968</v>
+        <v>0.4514027950162582</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.052178788689469</v>
+        <v>2.896129940000966</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284883</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.822269890750528</v>
+        <v>-4.158639387209382</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.147271647560292</v>
+        <v>1.01272384897675</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7114842094970968</v>
+        <v>0.4514027950162582</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.103426553872509</v>
+        <v>2.947377705184005</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321027</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.614627887116052</v>
+        <v>-3.950997383574906</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.228769153608335</v>
+        <v>1.094221355024794</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9191262131315729</v>
+        <v>0.6590447986507344</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.226452460647447</v>
+        <v>3.070403611958944</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475143</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.563595794393524</v>
+        <v>-3.899965290852378</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.244130218935616</v>
+        <v>1.109582420352075</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9701583058541009</v>
+        <v>0.7100768913732624</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.252019944519234</v>
+        <v>3.095971095830731</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404857</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.498371613266318</v>
+        <v>-3.834741109725172</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.287407295479204</v>
+        <v>1.152859496895662</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.035382486981307</v>
+        <v>0.775301072500468</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.308341857288262</v>
+        <v>3.152293008599759</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.460944593195185</v>
+        <v>-3.797314089654038</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.298339075806938</v>
+        <v>1.163791277223396</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.040634025010488</v>
+        <v>0.7805526105296496</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.307453752405052</v>
+        <v>3.151404903716549</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992663</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.481056249229893</v>
+        <v>-3.817425745688747</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.291551205724294</v>
+        <v>1.157003407140753</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.051661370007907</v>
+        <v>0.7915799555270688</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.315326951734744</v>
+        <v>3.15927810304624</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.82866144563629</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.452642986130009</v>
+        <v>-3.789012482588863</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.463474281985459</v>
+        <v>1.328926483401917</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9926858072614786</v>
+        <v>0.73260439278064</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.440499385108097</v>
+        <v>3.284450536419594</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957628</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.377860725104997</v>
+        <v>-3.714230221563851</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.613500095613281</v>
+        <v>1.478952297029739</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.067468068286491</v>
+        <v>0.8073866538056527</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.605481650940922</v>
+        <v>3.449432802252419</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.351776640841189</v>
+        <v>-3.688146137300043</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.615641705332663</v>
+        <v>1.481093906749122</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.067468068286491</v>
+        <v>0.8073866538056527</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.597189626954781</v>
+        <v>3.441140778266278</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896933</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.263898727732068</v>
+        <v>-3.600268224190922</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.648986066160091</v>
+        <v>1.514438267576549</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.183393710709842</v>
+        <v>0.9233122962290038</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.664938207992571</v>
+        <v>3.508889359304068</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959861</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.255006266338785</v>
+        <v>-3.591375762797639</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.670097456444195</v>
+        <v>1.535549657860654</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.183393710709842</v>
+        <v>0.9233122962290038</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.682492613719362</v>
+        <v>3.526443765030859</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945369</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.935359419630533</v>
+        <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.327805061632933</v>
+        <v>-3.759851879767516</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.603880970663613</v>
+        <v>1.460014258477287</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.217898987502747</v>
+        <v>0.895364460512423</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.666098812132181</v>
+        <v>3.501530111005494</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782712</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.916629116818395</v>
+        <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.881548869003494</v>
+        <v>-3.313595687138077</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.76365314490325</v>
+        <v>1.619786432716924</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.123180317833114</v>
+        <v>0.8006457908427903</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.590537307518264</v>
+        <v>3.425968606391577</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.78467134563264</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.907293139315299</v>
+        <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.858827765320341</v>
+        <v>-3.290874583454924</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.763405608873416</v>
+        <v>1.61953889668709</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.123180317833114</v>
+        <v>0.8006457908427903</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.581201330015168</v>
+        <v>3.416632628888482</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777677</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.066199265166468</v>
+        <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.988029578614384</v>
+        <v>-3.420076396748966</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.870631009406968</v>
+        <v>1.726764297220642</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9939785045390717</v>
+        <v>0.671443977548748</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.662586367889912</v>
+        <v>3.498017666763225</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644416</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.103277087660115</v>
+        <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.013903977088409</v>
+        <v>-3.445950795222992</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.897359072511004</v>
+        <v>1.753492360324678</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.038890113250813</v>
+        <v>0.7163555862604891</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.726611155610603</v>
+        <v>3.562042454483916</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799969</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.09995244364966</v>
+        <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.006849286873236</v>
+        <v>-3.438896105007819</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.896856304586619</v>
+        <v>1.752989592400293</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.045944803465987</v>
+        <v>0.7234102764756629</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.727519325729252</v>
+        <v>3.562950624602566</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.76667349633112</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.109958597294402</v>
+        <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.979898062546748</v>
+        <v>-3.411944880681331</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.917642947961955</v>
+        <v>1.77377623577563</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.060825149493706</v>
+        <v>0.7382906225033821</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.746453686990626</v>
+        <v>3.581884985863939</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784112</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.294061729439361</v>
+        <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.115851070603064</v>
+        <v>-3.547897888737647</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.047364876884389</v>
+        <v>1.903498164698063</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.060825149493706</v>
+        <v>0.7382906225033821</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.930556819135585</v>
+        <v>3.765988118008899</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714429</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.286178424342355</v>
+        <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.138259188407936</v>
+        <v>-3.570306006542519</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.030518324665433</v>
+        <v>1.886651612479107</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.060825149493706</v>
+        <v>0.7382906225033821</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.922673514038578</v>
+        <v>3.758104812911892</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.288232423891992</v>
+        <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.166483423985536</v>
+        <v>-3.598530242120119</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.02128262998403</v>
+        <v>1.877415917797705</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.078801901945014</v>
+        <v>0.7562673749546907</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.935513565059001</v>
+        <v>3.770944863932314</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.344486141613839</v>
+        <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.175924349874066</v>
+        <v>-3.607971168008649</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.073759977350465</v>
+        <v>1.92989326516414</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.201229019488406</v>
+        <v>0.8786944924980821</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.065223553306883</v>
+        <v>3.900654852180196</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.34737723615914</v>
+        <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.228197957209708</v>
+        <v>-3.660244775344291</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.05574162896151</v>
+        <v>1.911874916775184</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.148955412152764</v>
+        <v>0.8264208851624408</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.036750483450799</v>
+        <v>3.872181782324112</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347706</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.345489049052915</v>
+        <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.304527934810614</v>
+        <v>-3.736574752945196</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.023321450814922</v>
+        <v>1.879454738628597</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.148955412152764</v>
+        <v>0.8264208851624408</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.034862296344574</v>
+        <v>3.870293595217888</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887751</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.340309278655778</v>
+        <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.506781655134967</v>
+        <v>-3.93882847326955</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.937240192288043</v>
+        <v>1.793373480101718</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9467016918284108</v>
+        <v>0.6241671648380873</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.908330293752824</v>
+        <v>3.743761592626138</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.33874328886593</v>
+        <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.668350080662222</v>
+        <v>-4.100396898796805</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.871046832287294</v>
+        <v>1.727180120100968</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8199187680305314</v>
+        <v>0.497384241040208</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.830694549684249</v>
+        <v>3.666125848557563</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.351816695731848</v>
+        <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.776650742532341</v>
+        <v>-4.208697560666924</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.840799974405165</v>
+        <v>1.696933262218839</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8199187680305314</v>
+        <v>0.497384241040208</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.843767956550168</v>
+        <v>3.679199255423481</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378396</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.343821892514788</v>
+        <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.869798213835708</v>
+        <v>-4.301845031970291</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.795546182666758</v>
+        <v>1.651679470480432</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6970895567479987</v>
+        <v>0.3745550297576752</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.762075626563588</v>
+        <v>3.597506925436901</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006979</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.34234593364179</v>
+        <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.897699000945181</v>
+        <v>-4.329745819079764</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.782909908949971</v>
+        <v>1.639043196763645</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6624926326050639</v>
+        <v>0.3399581056147404</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.739841513204829</v>
+        <v>3.575272812078143</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787391</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.339110377618989</v>
+        <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.020225103648075</v>
+        <v>-4.452271921782658</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.730663911846012</v>
+        <v>1.586797199659686</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.53996652990217</v>
+        <v>0.2174320029118465</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.663090295560291</v>
+        <v>3.498521594433605</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585942</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.405816337209493</v>
+        <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.250739599833664</v>
+        <v>-4.682786417968247</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.70516407296228</v>
+        <v>1.561297360775955</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3094520337165813</v>
+        <v>-0.01308249327374222</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.591487557439442</v>
+        <v>3.426918856312756</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814669</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.54612805621134</v>
+        <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.599484685058107</v>
+        <v>-5.03153150319269</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.70597775787435</v>
+        <v>1.562111045688024</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2007040797976835</v>
+        <v>-0.12183044719264</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.66655050408995</v>
+        <v>3.501981802963264</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237099</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.61510832535698</v>
+        <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.753471102834248</v>
+        <v>-5.185517920968831</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.713363459909533</v>
+        <v>1.569496747723208</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2007040797976835</v>
+        <v>-0.12183044719264</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.73553077323559</v>
+        <v>3.570962072108903</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423392</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.601159527477101</v>
+        <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.702949199006582</v>
+        <v>-5.134996017141165</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.719623423560721</v>
+        <v>1.575756711374395</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2007040797976835</v>
+        <v>-0.12183044719264</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.721581975355711</v>
+        <v>3.557013274229024</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609758</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.613030016532515</v>
+        <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.955424353014307</v>
+        <v>-5.387471171148889</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.630503851013045</v>
+        <v>1.486637138826719</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2007040797976835</v>
+        <v>-0.12183044719264</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.733452464411125</v>
+        <v>3.568883763284438</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973162</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.614240551051458</v>
+        <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.248320109493719</v>
+        <v>-5.680366927628302</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.514556082940224</v>
+        <v>1.370689370753898</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2007040797976835</v>
+        <v>-0.12183044719264</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.734662998930069</v>
+        <v>3.570094297803382</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.66350945725195</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.61836229327878</v>
+        <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.434984237628527</v>
+        <v>-5.86703105576311</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.444012173913622</v>
+        <v>1.300145461727296</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1739651089731236</v>
+        <v>-0.1485694180171999</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.722741358662654</v>
+        <v>3.558172657535968</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.613440146014969</v>
+        <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.581004924542489</v>
+        <v>-6.013051742677072</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.380681751884226</v>
+        <v>1.236815039697901</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1648820171792666</v>
+        <v>-0.1576525098110569</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.71236935632253</v>
+        <v>3.547800655195843</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830332</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.775644202714013</v>
+        <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.672718933652074</v>
+        <v>-6.104765751786656</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.506200204939436</v>
+        <v>1.362333492753111</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1648820171792666</v>
+        <v>-0.1576525098110569</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.874573413021574</v>
+        <v>3.710004711894887</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.770490840677827</v>
+        <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.704370592712044</v>
+        <v>-6.136417410846626</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.488386179279263</v>
+        <v>1.344519467092937</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1597135599348264</v>
+        <v>-0.1628209670554971</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.866318976638723</v>
+        <v>3.701750275512037</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.780720258246319</v>
+        <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.786305410980927</v>
+        <v>-6.218352229115509</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.4658416695402</v>
+        <v>1.321974957353875</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1497788143477462</v>
+        <v>-0.1727557126425773</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.870587546854967</v>
+        <v>3.70601884572828</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.789645896702221</v>
+        <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.888281533229335</v>
+        <v>-6.320328351363917</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.43397685909674</v>
+        <v>1.290110146910415</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.04780269209933863</v>
+        <v>-0.2747318348909848</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.818327511961825</v>
+        <v>3.653758810835138</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.781798783946396</v>
+        <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.778275249752113</v>
+        <v>-6.210322067886695</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.470132259731804</v>
+        <v>1.326265547545479</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.07100726401661384</v>
+        <v>-0.2515272629737096</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.824403142356365</v>
+        <v>3.659834441229679</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818526</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.786048794668371</v>
+        <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.635215674011187</v>
+        <v>-6.067262492145769</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.531606100750149</v>
+        <v>1.387739388563823</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.07902069060659311</v>
+        <v>-0.2435138363837304</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.833461209032327</v>
+        <v>3.66889250790564</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051791</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.793309677550907</v>
+        <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.333768948539349</v>
+        <v>-5.765815766673931</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.65944567382142</v>
+        <v>1.515578961635094</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3804674160784304</v>
+        <v>0.0579328890881069</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.021590127197965</v>
+        <v>3.857021426071279</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679629</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.794280855303617</v>
+        <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.358359192774533</v>
+        <v>-5.790406010909115</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.650580753880057</v>
+        <v>1.506714041693732</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3804674160784304</v>
+        <v>0.0579328890881069</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.022561304950676</v>
+        <v>3.857992603823989</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474163</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.795123759683373</v>
+        <v>3.82407577475088</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.307320816768013</v>
+        <v>-5.739367634902595</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.67183900866242</v>
+        <v>1.527972296476095</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3804674160784304</v>
+        <v>0.0579328890881069</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.023404209330431</v>
+        <v>3.858835508203745</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969546</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.814161858557518</v>
+        <v>3.843113873625026</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.266181521901382</v>
+        <v>-5.698228340035964</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.707332825483218</v>
+        <v>1.563466113296893</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4216067109450612</v>
+        <v>0.09907218395473771</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.067125885124556</v>
+        <v>3.902557183997869</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700482</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.630345854681453</v>
+        <v>3.65929786974896</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.169546609882742</v>
+        <v>-5.601593428017324</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.562170786414609</v>
+        <v>1.418304074228284</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5182416229637011</v>
+        <v>0.1957070959733777</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.941290828459674</v>
+        <v>3.776722127332987</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.633847898755417</v>
+        <v>3.662799913822925</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.300127344413585</v>
+        <v>-5.732174162548167</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.513440536676236</v>
+        <v>1.36957382448991</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3876608884328586</v>
+        <v>0.06512636144253514</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.866444431815133</v>
+        <v>3.701875730688446</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.77502886083346</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.6182747178315</v>
+        <v>3.647226732899007</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.135631010222623</v>
+        <v>-5.567677828357205</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.563665889428703</v>
+        <v>1.419799177242378</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5521572226238205</v>
+        <v>0.229622695633497</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.949569051405792</v>
+        <v>3.785000350279105</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077632</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.617462428267929</v>
+        <v>3.646414443335437</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.163000942907055</v>
+        <v>-5.595047761041637</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.55190562679136</v>
+        <v>1.408038914605035</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5521572226238205</v>
+        <v>0.229622695633497</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.948756761842222</v>
+        <v>3.784188060715535</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147913</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.627331207393002</v>
+        <v>3.656283222460509</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.173386137796944</v>
+        <v>-5.605432955931526</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.557620327960477</v>
+        <v>1.413753615774151</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5417720277339312</v>
+        <v>0.2192375007436077</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.95239442403336</v>
+        <v>3.787825722906674</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735284</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.698168213169427</v>
+        <v>3.727120228236934</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.191974296519169</v>
+        <v>-5.624021114653751</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.621022070248012</v>
+        <v>1.477155358061687</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5231838690117059</v>
+        <v>0.2006493420213823</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.01207853457645</v>
+        <v>3.847509833449764</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496557</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.695037223987725</v>
+        <v>3.723989239055233</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.192272843215205</v>
+        <v>-5.624319661349787</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.617771662387896</v>
+        <v>1.473904950201571</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.52288532231567</v>
+        <v>0.2003507953253464</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.008768417377127</v>
+        <v>3.844199716250441</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108859</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.699568118927117</v>
+        <v>3.728520133994624</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.091449709524777</v>
+        <v>-5.52349652765936</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.662631810803458</v>
+        <v>1.518765098617133</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5353495378000238</v>
+        <v>0.2128150108097003</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.020777841607131</v>
+        <v>3.856209140480445</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121468</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.69969737240566</v>
+        <v>3.728649387473168</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.900668348772371</v>
+        <v>-5.332715166906953</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.739073608582965</v>
+        <v>1.595206896396639</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7261308985524312</v>
+        <v>0.4035963715621076</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.135375911537119</v>
+        <v>3.970807210410433</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.679534218143257</v>
+        <v>3.708486233210764</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.88215149473055</v>
+        <v>-5.314198312865132</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.726317195937289</v>
+        <v>1.582450483750964</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7390610279776394</v>
+        <v>0.4165265009873159</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.12297083492984</v>
+        <v>3.958402133803154</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.714501154755315</v>
+        <v>3.743453169822823</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.826820906828788</v>
+        <v>-5.25886772496337</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.783416367710053</v>
+        <v>1.639549655523727</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7943916158794015</v>
+        <v>0.471857088889078</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.191136124282957</v>
+        <v>4.02656742315627</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.708187722656753</v>
+        <v>3.73713973772426</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.814766779915825</v>
+        <v>-5.246813598050407</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.781924586376676</v>
+        <v>1.63805787419035</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8064457427923644</v>
+        <v>0.4839112158020408</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.192055168332171</v>
+        <v>4.027486467205485</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811011</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.710068352840889</v>
+        <v>3.739020367908396</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.855921899484046</v>
+        <v>-5.287968717618628</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.767343168733523</v>
+        <v>1.623476456547198</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7652906232241434</v>
+        <v>0.4427560962338199</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.169242726775375</v>
+        <v>4.004674025648688</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.612322444382921</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.722919378718771</v>
+        <v>3.751871393786279</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.753041309955453</v>
+        <v>-5.185088128090035</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.821346430422843</v>
+        <v>1.677479718236517</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8681712127527363</v>
+        <v>0.5456366857624129</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.243822106370413</v>
+        <v>4.079253405243727</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.743122048892365</v>
+        <v>3.772074063959873</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.984641703124954</v>
+        <v>-5.416688521259536</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.748908943328637</v>
+        <v>1.605042231142311</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8681712127527363</v>
+        <v>0.5456366857624129</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.264024776544007</v>
+        <v>4.099456075417321</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781708</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.743122048892365</v>
+        <v>3.772074063959873</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.002714211416565</v>
+        <v>-5.434761029551147</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.741679940011992</v>
+        <v>1.597813227825667</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8681712127527363</v>
+        <v>0.5456366857624129</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.264024776544007</v>
+        <v>4.099456075417321</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082837</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.703373962485832</v>
+        <v>3.73232597755334</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.17782104399301</v>
+        <v>-5.609867862127592</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.631889120574881</v>
+        <v>1.488022408388555</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8681712127527363</v>
+        <v>0.5456366857624129</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.224276690137474</v>
+        <v>4.059707989010787</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943589</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.710396581482772</v>
+        <v>3.73934859655028</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.146535023452555</v>
+        <v>-5.578581841587137</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.651426147788003</v>
+        <v>1.507559435601677</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8994572332931917</v>
+        <v>0.5769227063028682</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.250070921458687</v>
+        <v>4.085502220332001</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677823</v>
+        <v>3.730590658677826</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.809567581055676</v>
+        <v>3.838519596123184</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.99350963133927</v>
+        <v>-5.425556449473852</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.811807304206221</v>
+        <v>1.667940592019896</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.052482625406476</v>
+        <v>0.7299480984161524</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.441057156299562</v>
+        <v>4.276488455172876</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073886</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.997033805963969</v>
+        <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.021816945212541</v>
+        <v>-5.453863763347123</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.987950603565205</v>
+        <v>1.84408389137888</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.052482625406476</v>
+        <v>0.7299480984161524</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.628523381207854</v>
+        <v>4.463954680081168</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.966436757318051</v>
+        <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.188410170326063</v>
+        <v>-5.620456988460645</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.890716264873878</v>
+        <v>1.746849552687553</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8858894002929534</v>
+        <v>0.5633548733026299</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.497970397493823</v>
+        <v>4.333401696367137</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568385</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.970113159979769</v>
+        <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.015345790943763</v>
+        <v>-5.447392609078345</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.963618419288516</v>
+        <v>1.819751707102191</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8858894002929534</v>
+        <v>0.5633548733026299</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.501646800155541</v>
+        <v>4.337078099028854</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682203</v>
+        <v>3.740601586682207</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.967731215103264</v>
+        <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.986099810488066</v>
+        <v>-5.418146628622648</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.97293486659429</v>
+        <v>1.829068154407965</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8858894002929534</v>
+        <v>0.5633548733026299</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.499264855279036</v>
+        <v>4.33469615415235</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539106</v>
+        <v>3.69942482753911</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.965024454260899</v>
+        <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.093025358365917</v>
+        <v>-5.525072176500499</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.927457886600785</v>
+        <v>1.783591174414459</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.778963852415102</v>
+        <v>0.4564293254247785</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.43240276570996</v>
+        <v>4.267834064583274</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983736</v>
+        <v>3.68996278598374</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.966453256404133</v>
+        <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.238043916873166</v>
+        <v>-5.670090735007748</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.870879265341119</v>
+        <v>1.727012553154794</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6339452939078535</v>
+        <v>0.31141076691753</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.346820432748846</v>
+        <v>4.182251731622159</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969748</v>
+        <v>3.711872614969751</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.066384495661886</v>
+        <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.356385682657884</v>
+        <v>-5.788432500792466</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.923473798284985</v>
+        <v>1.77960708609866</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6446313324707436</v>
+        <v>0.3220968054804201</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.453163295144332</v>
+        <v>4.288594594017646</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073537</v>
+        <v>3.71489923707354</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.064170192787825</v>
+        <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.407796104978591</v>
+        <v>-5.839842923113173</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.900695326482641</v>
+        <v>1.756828614296316</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6446313324707436</v>
+        <v>0.3220968054804201</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.450948992270271</v>
+        <v>4.286380291143584</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.704778134720067</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.064073320862114</v>
+        <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.487215556186343</v>
+        <v>-5.919262374320925</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.86883067407383</v>
+        <v>1.724963961887505</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6446313324707436</v>
+        <v>0.3220968054804201</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.45085212034456</v>
+        <v>4.286283419217874</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.736825137581135</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.064067214420158</v>
+        <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.582678554103561</v>
+        <v>-6.014725372238143</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.830639368464986</v>
+        <v>1.686772656278661</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6446313324707436</v>
+        <v>0.3220968054804201</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.450846013902604</v>
+        <v>4.286277312775917</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500737</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.062163610982768</v>
+        <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.622698552147344</v>
+        <v>-6.054745370281926</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.812727765810083</v>
+        <v>1.668861053623758</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6046113344269597</v>
+        <v>0.2820768074366363</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.424930411638944</v>
+        <v>4.260361710512258</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.736109598636272</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.067897428730495</v>
+        <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.678067714279538</v>
+        <v>-6.11011453241412</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.796313918704933</v>
+        <v>1.652447206518607</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6046113344269597</v>
+        <v>0.2820768074366363</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.430664229386671</v>
+        <v>4.266095528259984</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396012</v>
+        <v>3.736843055396015</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.067435792073427</v>
+        <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.723505494110365</v>
+        <v>-6.155552312244947</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.777677170115533</v>
+        <v>1.633810457929209</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5617663437488001</v>
+        <v>0.2392318167584766</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.404495598322708</v>
+        <v>4.239926897196022</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.790292685396424</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.087310184923746</v>
+        <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.640280037262701</v>
+        <v>-6.072326855397283</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.830841745704918</v>
+        <v>1.686975033518594</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5617663437488001</v>
+        <v>0.2392318167584766</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.424369991173027</v>
+        <v>4.259801290046341</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299175</v>
+        <v>3.794507029299178</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.071010885448474</v>
+        <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.463989812657394</v>
+        <v>-5.896036630791976</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.885058536071769</v>
+        <v>1.741191823885445</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5617663437488001</v>
+        <v>0.2392318167584766</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.408070691697755</v>
+        <v>4.243501990571069</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590409</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.073441834912519</v>
+        <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.280778149524298</v>
+        <v>-5.71282496765888</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.960774150789053</v>
+        <v>1.816907438602728</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5617663437488001</v>
+        <v>0.2392318167584766</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.4105016411618</v>
+        <v>4.245932940035114</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146285</v>
+        <v>3.776866743146289</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.039233020760409</v>
+        <v>4.068185035827917</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.209056702510448</v>
+        <v>-5.64110352064503</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.955253915442483</v>
+        <v>1.811387203256158</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6334877907626507</v>
+        <v>0.3109532637723272</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.419325695217999</v>
+        <v>4.254756994091314</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.886133536857576</v>
+        <v>3.744367298966522</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.221340149804842</v>
+        <v>3.989099762470332</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.209056702510448</v>
+        <v>-5.64110352064503</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.955253915442483</v>
+        <v>1.811387203256158</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6334877907626507</v>
+        <v>0.3109532637723272</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.21440394679121</v>
+        <v>3.9821635594567</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240827.xlsx
+++ b/tame_output/ON/bt/strategyON_20240827.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>108.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.2%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.6%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-639.0%</t>
+          <t>-616.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>415.5%</t>
+          <t>423.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-725.7%</t>
+          <t>-673.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-256.0%</t>
+          <t>-247.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-109.7%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-195.1%</t>
+          <t>-174.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-250.9%</t>
+          <t>-228.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-65.1%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-134.8%</t>
+          <t>-292.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-192.9%</t>
+          <t>-158.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-151.0%</t>
+          <t>-137.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-26.7%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.677857997786343</v>
+        <v>-1.455994000230163</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.44542064401358</v>
+        <v>2.534166243036052</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.032009333063663</v>
+        <v>1.253873330619843</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.736125867280062</v>
+        <v>3.86924426581377</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.043926724930996</v>
+        <v>-1.822062727374816</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.292077452462168</v>
+        <v>2.38082305148464</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.6659406059190102</v>
+        <v>0.88780460347519</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.50956893029972</v>
+        <v>3.642687328833428</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.252417506382681</v>
+        <v>-2.0305535088265</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.229019429620263</v>
+        <v>2.317765028642734</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4574498244673257</v>
+        <v>0.6793138220235055</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.404812751167478</v>
+        <v>3.537931149701186</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.499618691147902</v>
+        <v>-2.277754693591722</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.138237706122742</v>
+        <v>2.226983305145214</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4776031779661382</v>
+        <v>0.699467175522318</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.425003513675334</v>
+        <v>3.558121912209042</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.992003719171999</v>
+        <v>-2.770139721615819</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.942390086956836</v>
+        <v>2.031135685979308</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.01478185005795857</v>
+        <v>0.2070821474982212</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.130678888904608</v>
+        <v>3.263797287438316</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495497</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.377184110102072</v>
+        <v>-3.155320112545891</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.78686046939767</v>
+        <v>1.875606068420142</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.01478185005795857</v>
+        <v>0.2070821474982212</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.129221427717471</v>
+        <v>3.262339826251179</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.627054790116653</v>
+        <v>-3.405190792560473</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.688681320846454</v>
+        <v>1.777426919868925</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.02148086977250468</v>
+        <v>0.2433448673286845</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.152748183070365</v>
+        <v>3.285866581604073</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.833566567003674</v>
+        <v>-3.611702569447494</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.602182668747903</v>
+        <v>1.690928267770375</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.1850309071145168</v>
+        <v>0.036833090441663</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.02494717559441</v>
+        <v>3.158065574128118</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.152910642084176</v>
+        <v>-3.931046644527996</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.476217965415962</v>
+        <v>1.564963564438434</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.1850309071145168</v>
+        <v>0.036833090441663</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.02672010229467</v>
+        <v>3.159838500828378</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.539120473359952</v>
+        <v>-4.31725647580377</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.308066920373056</v>
+        <v>1.396812519395528</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.2758038468319601</v>
+        <v>-0.05393984927578033</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.958589225931608</v>
+        <v>3.091707624465316</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.773814467492504</v>
+        <v>-4.551950469936322</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.202474097722126</v>
+        <v>1.291219696744598</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.269467579602705</v>
+        <v>-0.04760358204652515</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.950675761271252</v>
+        <v>3.08379415980496</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.109477114722957</v>
+        <v>-4.887613117166775</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.06678963048591</v>
+        <v>1.155535229508382</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.3373985650916098</v>
+        <v>-0.11553456753543</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.908497761633874</v>
+        <v>3.041616160167582</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.185921444925828</v>
+        <v>-4.964057447369647</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.042699458639003</v>
+        <v>1.131445057661475</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.2569530559979479</v>
+        <v>-0.03508905844176807</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.963252627324313</v>
+        <v>3.096371025858021</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.551048827564575</v>
+        <v>-5.329184830008393</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8959030205893352</v>
+        <v>0.9846486196118076</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.5532638402969604</v>
+        <v>-0.3313998427407806</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.784720671750737</v>
+        <v>2.917839070284444</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.959637604745254</v>
+        <v>-5.737773607189072</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7312290537318229</v>
+        <v>0.8199746527542953</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.9618526174776388</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.538328949457089</v>
+        <v>2.671447347990797</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.073398016768119</v>
+        <v>-5.851534019211937</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6809103213941374</v>
+        <v>0.7696559204166098</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.9618526174776388</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.533514381928549</v>
+        <v>2.666632780462257</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.489789891055116</v>
+        <v>-6.267925893498934</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5123476222882157</v>
+        <v>0.6010932213106881</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.9618526174776388</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.531508432537427</v>
+        <v>2.664626831071135</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.850963520872104</v>
+        <v>-6.629099523315922</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3781368610300997</v>
+        <v>0.4668824600525721</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.9618526174776388</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.541767123206106</v>
+        <v>2.674885521739814</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.194222040515123</v>
+        <v>-6.972358042958941</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2369330183185876</v>
+        <v>0.3256786173410595</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.9618526174776388</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.537866688351801</v>
+        <v>2.670985086885509</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.242424857757467</v>
+        <v>-7.020560860201285</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2160568114766508</v>
+        <v>0.3048024104991232</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.9618526174776388</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.536271608406802</v>
+        <v>2.669390006940509</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.539086199567664</v>
+        <v>-7.317222202011482</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1011712506817801</v>
+        <v>0.1899168497042525</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.030595753211518</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.498804702895683</v>
+        <v>2.631923101429391</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.725805907876967</v>
+        <v>-7.503941910320785</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.02245706282365578</v>
+        <v>0.1112026618461281</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.030595753211518</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.49477839836128</v>
+        <v>2.627896796894988</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.108807296619597</v>
+        <v>-7.886943299063416</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1308455939949802</v>
+        <v>-0.04209999497250827</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.030595753211518</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.494676297039696</v>
+        <v>2.627794695573404</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.113293741820986</v>
+        <v>-7.891429744264805</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1300686561041058</v>
+        <v>-0.04132305708163386</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.035082198412906</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.494555945890292</v>
+        <v>2.627674344424</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.472824064324987</v>
+        <v>-8.250960066768808</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2685304818076562</v>
+        <v>-0.1797848827851847</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.035082198412906</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.499906249188343</v>
+        <v>2.63302464772205</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.523173127779209</v>
+        <v>-8.30130913022303</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2807540872321677</v>
+        <v>-0.1920084882096957</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.085431261867128</v>
+        <v>-0.8635672643109484</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.477612831072987</v>
+        <v>2.610731229606695</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.620792405200605</v>
+        <v>-8.398928407644426</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3167600475789571</v>
+        <v>-0.2280144485564857</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.183050539288525</v>
+        <v>-0.9611865417323451</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.422083015241918</v>
+        <v>2.555201413775626</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.674863904708964</v>
+        <v>-8.452999907152785</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3354950910607282</v>
+        <v>-0.2467494920382567</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.237122038796884</v>
+        <v>-1.015258041240704</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.392533671858474</v>
+        <v>2.525652070392182</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.879122080038828</v>
+        <v>-8.657258082482649</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4116851640740316</v>
+        <v>-0.3229395650515601</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.364760983410873</v>
+        <v>-1.142896985854693</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.321463502208724</v>
+        <v>2.454581900742431</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.912774918547301</v>
+        <v>-8.690910920991122</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4206637449929849</v>
+        <v>-0.3319181459705134</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.465174351327911</v>
+        <v>-1.243310353771731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.265698035942937</v>
+        <v>2.398816434476645</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.051861033166158</v>
+        <v>-8.82999703560998</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.4609264893471066</v>
+        <v>-0.3721808903246351</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.604260465946767</v>
+        <v>-1.382396468390588</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.197618068665044</v>
+        <v>2.330736467198752</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.226985450552702</v>
+        <v>-9.005121452996523</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.5164210355542069</v>
+        <v>-0.4276754365317355</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.779384883333311</v>
+        <v>-1.557520885777131</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.107098638980634</v>
+        <v>2.240217037514342</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.461437544567191</v>
+        <v>-9.239573547011013</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.617421038061599</v>
+        <v>-0.5286754390391275</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.779384883333311</v>
+        <v>-1.557520885777131</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.099879474079039</v>
+        <v>2.232997872612747</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.565812275593638</v>
+        <v>-9.343948278037459</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6658431212461537</v>
+        <v>-0.5770975222236823</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.883759614359757</v>
+        <v>-1.661895616803577</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.030582444689195</v>
+        <v>2.163700843222903</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.728325741292222</v>
+        <v>-9.506461743736043</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.729732717687031</v>
+        <v>-0.6409871186645595</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.981393044778444</v>
+        <v>-1.759529047222264</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.973118176276539</v>
+        <v>2.106236574810247</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.854362534660511</v>
+        <v>-9.632498537104333</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.777453706405232</v>
+        <v>-0.6887081073827606</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.956141421968701</v>
+        <v>-1.734277424412522</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.990962878591499</v>
+        <v>2.124081277125207</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.797290762764581</v>
+        <v>-9.575426765208402</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.7506346619604591</v>
+        <v>-0.6618890629379877</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.956141421968701</v>
+        <v>-1.734277424412522</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.9949532142779</v>
+        <v>2.128071612811608</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.938962604488701</v>
+        <v>-9.717098606932522</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.8087786255488489</v>
+        <v>-0.7200330265263775</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.956141421968701</v>
+        <v>-1.734277424412522</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.993477987379158</v>
+        <v>2.126596385912866</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.889371760063867</v>
+        <v>-9.667507762507688</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7738888776140427</v>
+        <v>-0.6851432785915712</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.906550577543868</v>
+        <v>-1.684686579987688</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.038285904198931</v>
+        <v>2.171404302732639</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.74045342559201</v>
+        <v>-9.518589428035831</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.7273726774719833</v>
+        <v>-0.6386270784495118</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.875300986808695</v>
+        <v>-1.653436989252515</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.043984524993352</v>
+        <v>2.17710292352706</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.5146082728726</v>
+        <v>-9.292744275316419</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.6274555433480105</v>
+        <v>-0.5387099443255381</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.833374311221531</v>
+        <v>-1.611510313665351</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.078719603381859</v>
+        <v>2.211838001915567</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.390029616535008</v>
+        <v>-9.168165618978827</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5764849362569149</v>
+        <v>-0.4877393372344425</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.833374311221531</v>
+        <v>-1.611510313665351</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.079858747937918</v>
+        <v>2.212977146471625</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.442924904579295</v>
+        <v>-9.221060907023114</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.595009277312522</v>
+        <v>-0.5062636782900496</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.828418965133085</v>
+        <v>-1.606554967576905</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.085465729753093</v>
+        <v>2.218584128286801</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.370791729291414</v>
+        <v>-9.148927731735233</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5604223029587327</v>
+        <v>-0.4716767039362608</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.828418965133085</v>
+        <v>-1.606554967576905</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.091199433991729</v>
+        <v>2.224317832525437</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.299425336681766</v>
+        <v>-9.077561339125586</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.5416130083087394</v>
+        <v>-0.452867409286267</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.757052572523437</v>
+        <v>-1.535188574967257</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.124282007163653</v>
+        <v>2.257400405697361</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.205966302696542</v>
+        <v>-8.984102305140361</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5141128760275571</v>
+        <v>-0.4253672770050847</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.757052572523437</v>
+        <v>-1.535188574967257</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.114398525850746</v>
+        <v>2.247516924384453</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.19531312114311</v>
+        <v>-8.97344912358693</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.5116861639055581</v>
+        <v>-0.4229405648830857</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.757052572523437</v>
+        <v>-1.535188574967257</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.112563965351372</v>
+        <v>2.24568236388508</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.09740608246662</v>
+        <v>-8.875542084910439</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.4728236634084229</v>
+        <v>-0.3840780643859505</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.68906682266288</v>
+        <v>-1.467202825106701</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.153055100294245</v>
+        <v>2.286173498827953</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.073452541490662</v>
+        <v>-8.851588543934481</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.4625737408725459</v>
+        <v>-0.3738281418500735</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.665113281686923</v>
+        <v>-1.443249284130743</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.168095731025313</v>
+        <v>2.301214129559021</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.809392603167865</v>
+        <v>-8.587528605611684</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.3702100817051792</v>
+        <v>-0.2814644826827069</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.401053343364127</v>
+        <v>-1.179189345807947</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.313271377857238</v>
+        <v>2.446389776390946</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.102312979663028</v>
+        <v>-7.880448982106846</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.09016526596354524</v>
+        <v>-0.001419666941072428</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.401053343364127</v>
+        <v>-1.179189345807947</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.310484344196937</v>
+        <v>2.443602742730645</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.062128681296837</v>
+        <v>-7.840264683740656</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.0737479227292277</v>
+        <v>0.01499767629324511</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.360869044997936</v>
+        <v>-1.139005047441756</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.334938547104493</v>
+        <v>2.468056945638201</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.898728810357475</v>
+        <v>-7.676864812801293</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.009021153132725779</v>
+        <v>0.07972444588974703</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.197469174058573</v>
+        <v>-0.9756051765023934</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.432345290888868</v>
+        <v>2.565463689422576</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.665247588127876</v>
+        <v>-7.443383590571695</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.0922957645969662</v>
+        <v>0.1810413636194386</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9639879518289747</v>
+        <v>-0.7421239542727949</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.580358453064479</v>
+        <v>2.713476851598187</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.515581197120361</v>
+        <v>-7.293717199564179</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.1492701106870129</v>
+        <v>0.2380157097094857</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8710844605864387</v>
+        <v>-0.6492204630302589</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.633208337497042</v>
+        <v>2.76632673603075</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.383305723489475</v>
+        <v>-7.161441725933293</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.103441086146522</v>
+        <v>0.1921866851689948</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7388089869555521</v>
+        <v>-0.5169449893993723</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.613834407682728</v>
+        <v>2.746952806216436</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.227567390929733</v>
+        <v>-7.005703393373551</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1685514798580554</v>
+        <v>0.2572970788805282</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5830706543958105</v>
+        <v>-0.3612066568396307</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.71009246790621</v>
+        <v>2.843210866439918</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.142602724200414</v>
+        <v>-6.920738726644231</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2154436877734418</v>
+        <v>0.3041892867959151</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4981059876664909</v>
+        <v>-0.2762419901103111</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.77397760916746</v>
+        <v>2.907096007701168</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.248192713973518</v>
+        <v>-7.026328716417336</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.0452317622649816</v>
+        <v>0.1339773612874544</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6036959774395954</v>
+        <v>-0.3818319798834155</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.582647685704379</v>
+        <v>2.715766084238087</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987904</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.179958129348091</v>
+        <v>-6.958094131791908</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1210699379922389</v>
+        <v>0.2098155370147117</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.5852806545670594</v>
+        <v>-0.3634166570108795</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.642241221304987</v>
+        <v>2.775359619838695</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.873530691357055</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.032018087940491</v>
+        <v>-6.810154090384309</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.06036703186711101</v>
+        <v>0.1491126308895838</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5649597386585018</v>
+        <v>-0.3430957411023219</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.534554848161954</v>
+        <v>2.667673246695662</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.864816705103577</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.979048565686503</v>
+        <v>-6.75718456813032</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.07284085451522815</v>
+        <v>0.1615864535377014</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5119902164045129</v>
+        <v>-0.2901262188483331</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.557622575260869</v>
+        <v>2.690740973794577</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098113</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.857856093008484</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.813260369726212</v>
+        <v>-6.591396372170029</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1321955208042516</v>
+        <v>0.2209411198267244</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5119902164045129</v>
+        <v>-0.2901262188483331</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.550661963165776</v>
+        <v>2.683780361699484</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493424</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.872318447389627</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.779897163247443</v>
+        <v>-6.558033165691261</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1600031577769019</v>
+        <v>0.2487487567993751</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5119902164045129</v>
+        <v>-0.2901262188483331</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.565124317546919</v>
+        <v>2.698242716080627</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722821</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.866850567848822</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.671638026124922</v>
+        <v>-6.449774028568739</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1978389330851056</v>
+        <v>0.2865845321075788</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5119902164045129</v>
+        <v>-0.2901262188483331</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.559656438006114</v>
+        <v>2.692774836539822</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.82805292879205</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.864348661859399</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.548346891307791</v>
+        <v>-6.326482893751608</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2446534810225347</v>
+        <v>0.333399080045008</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3886990815873824</v>
+        <v>-0.1668350840312026</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.631129212906969</v>
+        <v>2.764247611440677</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.872049640096724</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.495650024176499</v>
+        <v>-6.273786026620317</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2734332061123768</v>
+        <v>0.3621788051348496</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3360022144560912</v>
+        <v>-0.1141382168999114</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.670448311423069</v>
+        <v>2.803566709956777</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.867830348443774</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.251884582193055</v>
+        <v>-6.030020584636873</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3667200912528048</v>
+        <v>0.4554656902752781</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3360022144560912</v>
+        <v>-0.1141382168999114</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.66622901977012</v>
+        <v>2.799347418303828</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057529</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.86995466236379</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.162108909816583</v>
+        <v>-5.9402449122604</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.40475467412341</v>
+        <v>0.4935002731458829</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.2744027695417812</v>
+        <v>-0.05253877198560136</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.705313000638722</v>
+        <v>2.83843139917243</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.862696737347493</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.091035878529391</v>
+        <v>-5.690394518311326</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4259259616219886</v>
+        <v>0.5861825057092149</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.2744027695417812</v>
+        <v>-0.05253877198560136</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.698055075622424</v>
+        <v>2.831173474156132</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011501</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.866295860868141</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.915143786061959</v>
+        <v>-5.514502425843894</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4998819221296102</v>
+        <v>0.6601384662168366</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.2744027695417812</v>
+        <v>-0.05253877198560136</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.701654199143073</v>
+        <v>2.834772597676781</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.879623366922695</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.743697323039496</v>
+        <v>-5.34305596282143</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5817880133931492</v>
+        <v>0.7420445574803756</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.1029563065193181</v>
+        <v>0.1189076910368618</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.817849583011105</v>
+        <v>2.950967981544812</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.878643844538992</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.663675035930375</v>
+        <v>-5.263033675712309</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6128174058530949</v>
+        <v>0.7730739499403207</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.02293401941019713</v>
+        <v>0.1989299781459827</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.864883432892874</v>
+        <v>2.998001831426582</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883076</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.883338645593309</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.60003929369644</v>
+        <v>-5.199397933478375</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6429665038009857</v>
+        <v>0.8032230478882121</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.04070172282373741</v>
+        <v>0.2625657203799173</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.907759679287552</v>
+        <v>3.04087807782126</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.864532904377105</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.506341975480045</v>
+        <v>-5.10570061526198</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6616396898713397</v>
+        <v>0.8218962339585656</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.04070172282373741</v>
+        <v>0.2625657203799173</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.888953938071348</v>
+        <v>3.022072336605055</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.866275981001982</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.516844598545334</v>
+        <v>-5.116203238327269</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6591817172701013</v>
+        <v>0.8194382613573277</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.03019909975844853</v>
+        <v>0.2520630973146284</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.884395440857052</v>
+        <v>3.01751383939076</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.870205294836802</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.444602030374139</v>
+        <v>-5.043960670156074</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6920080583733994</v>
+        <v>0.8522646024606257</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.03019909975844853</v>
+        <v>0.2520630973146284</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.888324754691872</v>
+        <v>3.02144315322558</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.870883878754142</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.426888343496274</v>
+        <v>-5.026246983278209</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6997721170418854</v>
+        <v>0.8600286611291117</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.03338042865536534</v>
+        <v>0.2552444262115452</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.890912135947362</v>
+        <v>3.02403053448107</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.867881949974136</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.318083458016547</v>
+        <v>-4.917442097798482</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7402921424537698</v>
+        <v>0.900548686540996</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.03338042865536534</v>
+        <v>0.2552444262115452</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.887910207167355</v>
+        <v>3.021028605701063</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675941</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.86946098698475</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.098062659979536</v>
+        <v>-4.697421299761471</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8298794986791882</v>
+        <v>0.9901360427664143</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.1746002737233456</v>
+        <v>0.3964642712795254</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.974221151218758</v>
+        <v>3.107339549752465</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539953</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.885355169786573</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.965194970916259</v>
+        <v>-4.564553610698193</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8989207571063225</v>
+        <v>1.059177301193549</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.1746002737233456</v>
+        <v>0.3964642712795254</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.990115334020581</v>
+        <v>3.123233732554289</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496266</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.886501014226875</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.84502188755176</v>
+        <v>-4.444380527333695</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9481358348924238</v>
+        <v>1.10839237897965</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.2947733570878445</v>
+        <v>0.5166373546440244</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.063365028479582</v>
+        <v>3.19648342701329</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577003</v>
+        <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
         <v>2.896589116788315</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.709768526221783</v>
+        <v>-4.309127166003718</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.012325281985855</v>
+        <v>1.172581826073081</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4300267184178216</v>
+        <v>0.6518907159740015</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.154605147839008</v>
+        <v>3.287723546372716</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942109</v>
+        <v>3.735839222942107</v>
       </c>
       <c r="C1933" t="n">
         <v>2.882626608189741</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.769643353579475</v>
+        <v>-4.36900199336141</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9744128424442036</v>
+        <v>1.13466938653143</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3701518910601295</v>
+        <v>0.5920158886163094</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.104717742825819</v>
+        <v>3.237836141359527</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.897915777423949</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.649823122668638</v>
+        <v>-4.249181762450573</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.037630104042747</v>
+        <v>1.197886648129973</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3701518910601295</v>
+        <v>0.5920158886163094</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.120006912060028</v>
+        <v>3.253125310593735</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.805559976746391</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.652292829130444</v>
+        <v>-4.251651468912379</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.944286420780466</v>
+        <v>1.104542964867692</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.3676821845983234</v>
+        <v>0.5895461821545032</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.026169287505385</v>
+        <v>3.159287686039093</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.724821838231692</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.720663015454455</v>
+        <v>-4.320021655236389</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.8362002077361632</v>
+        <v>0.9964567518233896</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.3769578836345383</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.950996568412416</v>
+        <v>3.084114966946124</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.715258546863584</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.734451068301501</v>
+        <v>-4.333809708083436</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8211216952292359</v>
+        <v>0.9813782393164621</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.3769578836345383</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.941433277044307</v>
+        <v>3.074551675578015</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417708</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.852289383555786</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.789971144194091</v>
+        <v>-4.389329783976025</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9359445015644026</v>
+        <v>1.096201045651629</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.3769578836345383</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.078464113736509</v>
+        <v>3.211582512270217</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.856856615547574</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.614496884401621</v>
+        <v>-4.213855524183556</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.010701437473178</v>
+        <v>1.170957981560404</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.3769578836345383</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.083031345728297</v>
+        <v>3.216149744262005</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225447</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.832598644308781</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.606572509816707</v>
+        <v>-4.205931149598642</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9896132160683508</v>
+        <v>1.149869760155577</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.3769578836345383</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.058773374489504</v>
+        <v>3.191891773023212</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111301</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.761136957710231</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.600294307246858</v>
+        <v>-4.199652947028793</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9206628104977401</v>
+        <v>1.080919354584966</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3832360862043874</v>
+        <v>0.6051000837605671</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.991078609432863</v>
+        <v>3.124197007966571</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226417</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.771309344142363</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.540441688043135</v>
+        <v>-4.139800327825069</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9547762446113619</v>
+        <v>1.115032788698588</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3832360862043874</v>
+        <v>0.6051000837605671</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.001250995864996</v>
+        <v>3.134369394398703</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742306</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.766255614716223</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.454198225016757</v>
+        <v>-4.053556864798692</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9842199003957732</v>
+        <v>1.144476444482999</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3832360862043874</v>
+        <v>0.6051000837605671</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.996197266438856</v>
+        <v>3.129315664972564</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316053</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.758031390160749</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.499505044415737</v>
+        <v>-4.098863684197672</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9578729480807069</v>
+        <v>1.118129492167933</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3424259231951566</v>
+        <v>0.5642899207513363</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.963486944077843</v>
+        <v>3.096605342611551</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803198</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.528538149118038</v>
+        <v>-4.127896788899973</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9468115792328879</v>
+        <v>1.107068123320114</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3424259231951566</v>
+        <v>0.5642899207513363</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.964038817110945</v>
+        <v>3.097157215644653</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809505</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.435727667667178</v>
+        <v>-4.035086307449113</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9132084637045974</v>
+        <v>1.073465007791824</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4352364046460159</v>
+        <v>0.6571004022021957</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.948997797872826</v>
+        <v>3.082116196406534</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560432</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.480117136996606</v>
+        <v>-4.079475776778541</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8973261518974274</v>
+        <v>1.057582695984653</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3908469353165883</v>
+        <v>0.612710932872768</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.92423759219977</v>
+        <v>3.057355990733478</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472743</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.596658742101948</v>
+        <v>-4.196017381883883</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8457852183670134</v>
+        <v>1.006041762454239</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.2743053302112455</v>
+        <v>0.4961693277674253</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.849388337648287</v>
+        <v>2.982506736181995</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.636582836684521</v>
+        <v>-4.235941476466455</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8353068763646516</v>
+        <v>0.995563420451878</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.2743053302112455</v>
+        <v>0.4961693277674253</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.854879633478955</v>
+        <v>2.987998032012662</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049887</v>
+        <v>3.689597840498866</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.664363234585873</v>
+        <v>-4.263721874367808</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8356919189726497</v>
+        <v>0.9959484630598758</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.2465249323098924</v>
+        <v>0.4683889298660722</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.849708596506682</v>
+        <v>2.98282699504039</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170533</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.782743907316012</v>
+        <v>-4.366632412571029</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6266953698812476</v>
+        <v>0.7931399677792408</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.1793070801589162</v>
+        <v>0.4342330351271303</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.64773360521675</v>
+        <v>2.800689178197678</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729274</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.891357985759343</v>
+        <v>-4.47524649101436</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7033993992231209</v>
+        <v>0.8698439971211138</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.1793070801589162</v>
+        <v>0.4342330351271303</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.767883265935955</v>
+        <v>2.920838838916884</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190773</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.8559489475112</v>
+        <v>-4.439837452766217</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7320760406247009</v>
+        <v>0.898520638522694</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.1793070801589162</v>
+        <v>0.4342330351271303</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.782396292038278</v>
+        <v>2.935351865019207</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913431</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.817565284953049</v>
+        <v>-4.401453790208066</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7448489469903301</v>
+        <v>0.911293544888323</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.2176907427170674</v>
+        <v>0.4726166976852815</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.802845930915538</v>
+        <v>2.955801503896466</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532491</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.640448954917883</v>
+        <v>-4.2243374601729</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8124245078496983</v>
+        <v>0.9788691057476915</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.2176907427170674</v>
+        <v>0.4726166976852815</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.799574959760839</v>
+        <v>2.952530532741768</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793908</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.685541199751428</v>
+        <v>-4.269429705006446</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7950710016781932</v>
+        <v>0.9615155995761864</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.1557946995476776</v>
+        <v>0.4107206545158917</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.763120725621119</v>
+        <v>2.916076298602047</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072937701124</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.506165778512661</v>
+        <v>-4.090054283767678</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8606081454801147</v>
+        <v>1.027052743378108</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3125714577183963</v>
+        <v>0.5674974126866104</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.850973755829964</v>
+        <v>3.003929328810893</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982234</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.551179992033267</v>
+        <v>-4.135068497288284</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8234099154034618</v>
+        <v>0.9898545133014551</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.2822225624037917</v>
+        <v>0.5371485173720058</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.813571873972791</v>
+        <v>2.96652744695372</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.818184502305702</v>
+        <v>-4.402073007560719</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7222996736334335</v>
+        <v>0.8887442715314269</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.0878595243608431</v>
+        <v>0.3427854793290572</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.702645613485968</v>
+        <v>2.855601186466896</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760819</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.919382283742875</v>
+        <v>-4.503270788997892</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6810244829550658</v>
+        <v>0.8474690808530592</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.01945071081552391</v>
+        <v>0.274376665783738</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.660804247255278</v>
+        <v>2.813759820236206</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815464</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.912871317128563</v>
+        <v>-4.496759822383579</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6812288311551076</v>
+        <v>0.8476734290531009</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.01945071081552391</v>
+        <v>0.274376665783738</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.658404208809594</v>
+        <v>2.811359781790523</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378109</v>
+        <v>3.709510443378106</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.893833189421265</v>
+        <v>-4.477721694676282</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6853688014462715</v>
+        <v>0.8518133993442649</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.03873290051567063</v>
+        <v>0.2161930544525434</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.620018761219123</v>
+        <v>2.772974334200051</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131257</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.946348991696086</v>
+        <v>-4.530237496951102</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7836568821705336</v>
+        <v>0.950101480068527</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.03873290051567063</v>
+        <v>0.2161930544525434</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.739313162853313</v>
+        <v>2.892268735834242</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067872</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.960215753030004</v>
+        <v>-4.54410425828502</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7789435066231001</v>
+        <v>0.9453881045210935</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.07659081724949357</v>
+        <v>0.1783351377187205</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.717431741799153</v>
+        <v>2.870387314780081</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789129</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.915411581490074</v>
+        <v>-4.49930008674509</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.802873705635998</v>
+        <v>0.9693183035339914</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.07659081724949357</v>
+        <v>0.1783351377187205</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.723440272196079</v>
+        <v>2.876395845177007</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519915</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.767668611255071</v>
+        <v>-4.351557116510087</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7599211150071985</v>
+        <v>0.9263657129051919</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.09121653998538959</v>
+        <v>0.3461424949536037</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.722074907814208</v>
+        <v>2.875030480795137</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181176</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.85148983252977</v>
+        <v>-4.435378337784786</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7291862480288001</v>
+        <v>0.8956308459267934</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.09121653998538959</v>
+        <v>0.3461424949536037</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.724868529345689</v>
+        <v>2.877824102326618</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394735</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.845337126476985</v>
+        <v>-4.429225631732002</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7323096788415722</v>
+        <v>0.8987542767395655</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.09736924603817387</v>
+        <v>0.3522952010063879</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.729222501369018</v>
+        <v>2.882178074349946</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890619</v>
+        <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.862146424627487</v>
+        <v>-4.446034929882503</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7246664363214816</v>
+        <v>0.891111034219475</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.08055994788767223</v>
+        <v>0.3354859028558863</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.718217399218827</v>
+        <v>2.871172972199756</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798432</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.799848425851365</v>
+        <v>-4.383736931106381</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8159211896287515</v>
+        <v>0.9823657875267449</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1258542121621143</v>
+        <v>0.3807801671303284</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.811729511580313</v>
+        <v>2.964685084561242</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992197</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.598058228186207</v>
+        <v>-4.181946733441223</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6989292704089416</v>
+        <v>0.8653738683069352</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3238724043312687</v>
+        <v>0.5787983592994828</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.732832428595933</v>
+        <v>2.885788001576862</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785243</v>
+        <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.648944940872402</v>
+        <v>-4.232833446127418</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.748864817656639</v>
+        <v>0.9153094155546324</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.2729856916450741</v>
+        <v>0.5279116466132883</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.772590633306391</v>
+        <v>2.92554620628732</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319549</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.562334198222595</v>
+        <v>-4.146222703477611</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7981368508326054</v>
+        <v>0.9645814487305988</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3516114228502324</v>
+        <v>0.6065373778184465</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.83439380814553</v>
+        <v>2.987349381126459</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.62254349622788</v>
+        <v>-4.206432001482896</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7725891124551632</v>
+        <v>0.9390337103531565</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2914021248449479</v>
+        <v>0.546328079813162</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.796804210167031</v>
+        <v>2.94975978314796</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.546121449795953</v>
+        <v>-4.130009955050969</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8016495490678623</v>
+        <v>0.9680941469658557</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2914021248449479</v>
+        <v>0.546328079813162</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.79529582820696</v>
+        <v>2.948251401187888</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316253</v>
+        <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.501748318157384</v>
+        <v>-4.085636823412401</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.819261669158726</v>
+        <v>0.9857062670567194</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3357752564835165</v>
+        <v>0.5907012114517306</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.821782574625537</v>
+        <v>2.974738147606466</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105971</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.524228669016269</v>
+        <v>-4.108117174271285</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8046633229537625</v>
+        <v>0.9711079208517561</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3357752564835165</v>
+        <v>0.5907012114517306</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.816176368764128</v>
+        <v>2.969131941745056</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190329</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.476572938455213</v>
+        <v>-4.06046144371023</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8301073722059895</v>
+        <v>0.9965519701039831</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3834309870445721</v>
+        <v>0.6383569420127863</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.851151564128566</v>
+        <v>3.004107137109494</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569622</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.376054779956458</v>
+        <v>-3.959943285211475</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8752070089802162</v>
+        <v>1.04165160687821</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4839491455433267</v>
+        <v>0.7388751005115408</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.916354832602543</v>
+        <v>3.069310405583471</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557298</v>
+        <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.360149450524106</v>
+        <v>-3.944037955779122</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8683238132290296</v>
+        <v>1.034768411127023</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4048364848340878</v>
+        <v>0.6597624398023019</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.855641908652872</v>
+        <v>3.0085974816338</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932774</v>
+        <v>3.816837033932772</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.315311048915707</v>
+        <v>-3.899199554170724</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8903568764830174</v>
+        <v>1.056801474381011</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4093799177789573</v>
+        <v>0.6643058727471713</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.862465671030423</v>
+        <v>3.015421244011351</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917056</v>
+        <v>3.817932354917054</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.334809505157716</v>
+        <v>-3.918698010412732</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8867184336172922</v>
+        <v>1.053163031515286</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.361295276499053</v>
+        <v>0.616221231467267</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.837775825893558</v>
+        <v>2.990731398874486</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405964</v>
+        <v>3.826684745405962</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.290606668071815</v>
+        <v>-3.874495173326832</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9102791709794895</v>
+        <v>1.076723768877483</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4054981135849534</v>
+        <v>0.6604240685531675</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.870177130672935</v>
+        <v>3.023132703653864</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265649</v>
+        <v>3.838199629265647</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.316930804748654</v>
+        <v>-3.882054839163879</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8981595167780017</v>
+        <v>1.072109903011912</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4514027950162582</v>
+        <v>0.7152274725629868</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.896129940000966</v>
+        <v>3.054424746529003</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284883</v>
+        <v>3.863895080284881</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.158639387209382</v>
+        <v>-3.723763421624607</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.01272384897675</v>
+        <v>1.18667423521066</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4514027950162582</v>
+        <v>0.7152274725629868</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.947377705184005</v>
+        <v>3.105672511712042</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321027</v>
+        <v>3.865338681321025</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.950997383574906</v>
+        <v>-3.516121417990131</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.094221355024794</v>
+        <v>1.268171741258704</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6590447986507344</v>
+        <v>0.922869476197463</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.070403611958944</v>
+        <v>3.228698418486981</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475143</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.899965290852378</v>
+        <v>-3.465089325267602</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.109582420352075</v>
+        <v>1.283532806585985</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7100768913732624</v>
+        <v>0.9739015689199909</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.095971095830731</v>
+        <v>3.254265902358768</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404857</v>
+        <v>3.842547360404855</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.834741109725172</v>
+        <v>-3.399865144140397</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.152859496895662</v>
+        <v>1.326809883129572</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.775301072500468</v>
+        <v>1.039125750047197</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.152293008599759</v>
+        <v>3.310587815127796</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.797314089654038</v>
+        <v>-3.362438124069263</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.163791277223396</v>
+        <v>1.337741663457306</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.7805526105296496</v>
+        <v>1.044377288076378</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.151404903716549</v>
+        <v>3.309699710244586</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992663</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.817425745688747</v>
+        <v>-3.382549780103971</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.157003407140753</v>
+        <v>1.330953793374663</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.7915799555270688</v>
+        <v>1.055404633073797</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.15927810304624</v>
+        <v>3.317572909574277</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82866144563629</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.789012482588863</v>
+        <v>-3.354136517004088</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.328926483401917</v>
+        <v>1.502876869635827</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.73260439278064</v>
+        <v>0.9964290703273686</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.284450536419594</v>
+        <v>3.442745342947631</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957628</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.714230221563851</v>
+        <v>-3.279354255979075</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.478952297029739</v>
+        <v>1.65290268326365</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.8073866538056527</v>
+        <v>1.071211331352381</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.449432802252419</v>
+        <v>3.607727608780456</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.688146137300043</v>
+        <v>-3.253270171715267</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.481093906749122</v>
+        <v>1.655044292983032</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.8073866538056527</v>
+        <v>1.071211331352381</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.441140778266278</v>
+        <v>3.599435584794315</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896933</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.600268224190922</v>
+        <v>-3.165392258606146</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.514438267576549</v>
+        <v>1.688388653810459</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9233122962290038</v>
+        <v>1.187136973775732</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.508889359304068</v>
+        <v>3.667184165832105</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959861</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.591375762797639</v>
+        <v>-3.156499797212863</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.535549657860654</v>
+        <v>1.709500044094564</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9233122962290038</v>
+        <v>1.187136973775732</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.526443765030859</v>
+        <v>3.684738571558896</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945369</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.759851879767516</v>
+        <v>-3.324975914182741</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.460014258477287</v>
+        <v>1.633964644711197</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.895364460512423</v>
+        <v>1.159189138059151</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.501530111005494</v>
+        <v>3.659824917533532</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782712</v>
+        <v>3.79557406678271</v>
       </c>
       <c r="C1997" t="n">
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.313595687138077</v>
+        <v>-2.878719721553301</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.619786432716924</v>
+        <v>1.793736818950835</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8006457908427903</v>
+        <v>1.064470468389519</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.425968606391577</v>
+        <v>3.584263412919614</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563264</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.290874583454924</v>
+        <v>-2.855998617870148</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.61953889668709</v>
+        <v>1.793489282921</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8006457908427903</v>
+        <v>1.064470468389519</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.416632628888482</v>
+        <v>3.574927435416519</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777677</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.420076396748966</v>
+        <v>-2.985200431164191</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.726764297220642</v>
+        <v>1.900714683454553</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.671443977548748</v>
+        <v>0.9352686550954765</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.498017666763225</v>
+        <v>3.656312473291262</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644416</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.445950795222992</v>
+        <v>-3.011074829638217</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.753492360324678</v>
+        <v>1.927442746558588</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7163555862604891</v>
+        <v>0.9801802638072177</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.562042454483916</v>
+        <v>3.720337261011953</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799969</v>
+        <v>3.769443619799967</v>
       </c>
       <c r="C2001" t="n">
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.438896105007819</v>
+        <v>-3.004020139423043</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.752989592400293</v>
+        <v>1.926939978634203</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7234102764756629</v>
+        <v>0.9872349540223915</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.562950624602566</v>
+        <v>3.721245431130603</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633112</v>
+        <v>3.766673496331118</v>
       </c>
       <c r="C2002" t="n">
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.411944880681331</v>
+        <v>-2.977068915096555</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.77377623577563</v>
+        <v>1.94772662200954</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7382906225033821</v>
+        <v>1.002115300050111</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.581884985863939</v>
+        <v>3.740179792391976</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784112</v>
+        <v>3.768052067784111</v>
       </c>
       <c r="C2003" t="n">
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.547897888737647</v>
+        <v>-3.113021923152871</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.903498164698063</v>
+        <v>2.077448550931973</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7382906225033821</v>
+        <v>1.002115300050111</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.765988118008899</v>
+        <v>3.924282924536936</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.570306006542519</v>
+        <v>-3.135430040957743</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.886651612479107</v>
+        <v>2.060601998713017</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7382906225033821</v>
+        <v>1.002115300050111</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.758104812911892</v>
+        <v>3.916399619439929</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.598530242120119</v>
+        <v>-3.163654276535344</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.877415917797705</v>
+        <v>2.051366304031615</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7562673749546907</v>
+        <v>1.020092052501419</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.770944863932314</v>
+        <v>3.929239670460351</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.607971168008649</v>
+        <v>-3.173095202423874</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.92989326516414</v>
+        <v>2.10384365139805</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8786944924980821</v>
+        <v>1.142519170044811</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.900654852180196</v>
+        <v>4.058949658708233</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.660244775344291</v>
+        <v>-3.225368809759515</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.911874916775184</v>
+        <v>2.085825303009094</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8264208851624408</v>
+        <v>1.090245562709169</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.872181782324112</v>
+        <v>4.030476588852149</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347706</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.736574752945196</v>
+        <v>-3.301698787360421</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.879454738628597</v>
+        <v>2.053405124862507</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8264208851624408</v>
+        <v>1.090245562709169</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.870293595217888</v>
+        <v>4.028588401745925</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887751</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.93882847326955</v>
+        <v>-3.503952507684774</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.793373480101718</v>
+        <v>1.967323866335628</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6241671648380873</v>
+        <v>0.8879918423848159</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.743761592626138</v>
+        <v>3.902056399154175</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-4.100396898796805</v>
+        <v>-3.665520933212029</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.727180120100968</v>
+        <v>1.901130506334878</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.497384241040208</v>
+        <v>0.7612089185869365</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.666125848557563</v>
+        <v>3.824420655085599</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389351</v>
       </c>
       <c r="C2011" t="n">
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.208697560666924</v>
+        <v>-3.773821595082149</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.696933262218839</v>
+        <v>1.870883648452749</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.497384241040208</v>
+        <v>0.7612089185869365</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.679199255423481</v>
+        <v>3.837494061951518</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378396</v>
+        <v>3.749882691378395</v>
       </c>
       <c r="C2012" t="n">
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.301845031970291</v>
+        <v>-3.866969066385515</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.651679470480432</v>
+        <v>1.825629856714343</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3745550297576752</v>
+        <v>0.6383797073044037</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.597506925436901</v>
+        <v>3.755801731964938</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.329745819079764</v>
+        <v>-3.894869853494988</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.639043196763645</v>
+        <v>1.812993582997555</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3399581056147404</v>
+        <v>0.6037827831614689</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.575272812078143</v>
+        <v>3.733567618606179</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.452271921782658</v>
+        <v>-4.017395956197882</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.586797199659686</v>
+        <v>1.760747585893597</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2174320029118465</v>
+        <v>0.4812566804585751</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.498521594433605</v>
+        <v>3.656816400961642</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585942</v>
+        <v>3.619348081585941</v>
       </c>
       <c r="C2015" t="n">
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.682786417968247</v>
+        <v>-4.247910452383471</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.561297360775955</v>
+        <v>1.735247747009865</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.01308249327374222</v>
+        <v>0.2507421842729863</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.426918856312756</v>
+        <v>3.585213662840792</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814669</v>
+        <v>3.640750087814668</v>
       </c>
       <c r="C2016" t="n">
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-5.03153150319269</v>
+        <v>-4.596655537607915</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.562111045688024</v>
+        <v>1.736061431921934</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.12183044719264</v>
+        <v>0.1419942303540885</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.501981802963264</v>
+        <v>3.660276609491301</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237099</v>
+        <v>3.668289004237098</v>
       </c>
       <c r="C2017" t="n">
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-5.185517920968831</v>
+        <v>-4.750641955384055</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.569496747723208</v>
+        <v>1.743447133957118</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.12183044719264</v>
+        <v>0.1419942303540885</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.570962072108903</v>
+        <v>3.729256878636941</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423392</v>
+        <v>3.619923016423391</v>
       </c>
       <c r="C2018" t="n">
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-5.134996017141165</v>
+        <v>-4.700120051556389</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.575756711374395</v>
+        <v>1.749707097608305</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.12183044719264</v>
+        <v>0.1419942303540885</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.557013274229024</v>
+        <v>3.715308080757062</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609758</v>
+        <v>3.656332733609757</v>
       </c>
       <c r="C2019" t="n">
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.387471171148889</v>
+        <v>-4.952595205564114</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.486637138826719</v>
+        <v>1.660587525060629</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.12183044719264</v>
+        <v>0.1419942303540885</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.568883763284438</v>
+        <v>3.727178569812476</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973162</v>
+        <v>3.674028535973161</v>
       </c>
       <c r="C2020" t="n">
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.680366927628302</v>
+        <v>-5.245490962043526</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.370689370753898</v>
+        <v>1.544639756987808</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.12183044719264</v>
+        <v>0.1419942303540885</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.570094297803382</v>
+        <v>3.728389104331419</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725195</v>
+        <v>3.663509457251949</v>
       </c>
       <c r="C2021" t="n">
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.86703105576311</v>
+        <v>-5.432155090178334</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.300145461727296</v>
+        <v>1.474095847961206</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1485694180171999</v>
+        <v>0.1152552595295286</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.558172657535968</v>
+        <v>3.716467464064005</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916205</v>
       </c>
       <c r="C2022" t="n">
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-6.013051742677072</v>
+        <v>-5.578175777092296</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.236815039697901</v>
+        <v>1.410765425931811</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.1576525098110569</v>
+        <v>0.1061721677356717</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.547800655195843</v>
+        <v>3.70609546172388</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-6.104765751786656</v>
+        <v>-5.669889786201882</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.362333492753111</v>
+        <v>1.536283878987021</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.1576525098110569</v>
+        <v>0.1061721677356717</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.710004711894887</v>
+        <v>3.868299518422924</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.136417410846626</v>
+        <v>-5.701541445261851</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.344519467092937</v>
+        <v>1.518469853326847</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1628209670554971</v>
+        <v>0.1010037104912315</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.701750275512037</v>
+        <v>3.860045082040074</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.218352229115509</v>
+        <v>-5.783476263530734</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.321974957353875</v>
+        <v>1.495925343587785</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1727557126425773</v>
+        <v>0.09106896490415128</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.70601884572828</v>
+        <v>3.864313652256317</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.320328351363917</v>
+        <v>-5.885452385779142</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.290110146910415</v>
+        <v>1.464060533144325</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2747318348909848</v>
+        <v>-0.01090715734425629</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.653758810835138</v>
+        <v>3.812053617363175</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.210322067886695</v>
+        <v>-5.77544610230192</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.326265547545479</v>
+        <v>1.500215933779389</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2515272629737096</v>
+        <v>0.01229741457301892</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.659834441229679</v>
+        <v>3.818129247757716</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.067262492145769</v>
+        <v>-5.632386526560994</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.387739388563823</v>
+        <v>1.561689774797733</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2435138363837304</v>
+        <v>0.02031084116299819</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.66889250790564</v>
+        <v>3.827187314433678</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.765815766673931</v>
+        <v>-5.330939801089157</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.515578961635094</v>
+        <v>1.689529347869005</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.0579328890881069</v>
+        <v>0.3217575666348355</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.857021426071279</v>
+        <v>4.015316232599316</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679629</v>
+        <v>3.812635940679628</v>
       </c>
       <c r="C2030" t="n">
         <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.790406010909115</v>
+        <v>-5.355530045324341</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.506714041693732</v>
+        <v>1.680664427927641</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.0579328890881069</v>
+        <v>0.3217575666348355</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.857992603823989</v>
+        <v>4.016287410352026</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.82407577475088</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.739367634902595</v>
+        <v>-5.30449166931782</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.527972296476095</v>
+        <v>1.701922682710005</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.0579328890881069</v>
+        <v>0.3217575666348355</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.858835508203745</v>
+        <v>4.017130314731782</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.843113873625026</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.698228340035964</v>
+        <v>-5.263352374451189</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.563466113296893</v>
+        <v>1.737416499530803</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.09907218395473771</v>
+        <v>0.3628968615014663</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.902557183997869</v>
+        <v>4.060851990525906</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.65929786974896</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.601593428017324</v>
+        <v>-5.166717462432549</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.418304074228284</v>
+        <v>1.592254460462193</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1957070959733777</v>
+        <v>0.4595317735201062</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.776722127332987</v>
+        <v>3.935016933861024</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.662799913822925</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.732174162548167</v>
+        <v>-5.297298196963392</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.36957382448991</v>
+        <v>1.543524210723821</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.06512636144253514</v>
+        <v>0.3289510389892637</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.701875730688446</v>
+        <v>3.860170537216483</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.647226732899007</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.567677828357205</v>
+        <v>-5.13280186277243</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.419799177242378</v>
+        <v>1.593749563476288</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.229622695633497</v>
+        <v>0.4934473731802256</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.785000350279105</v>
+        <v>3.943295156807142</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.646414443335437</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.595047761041637</v>
+        <v>-5.160171795456862</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.408038914605035</v>
+        <v>1.581989300838945</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.229622695633497</v>
+        <v>0.4934473731802256</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.784188060715535</v>
+        <v>3.942482867243572</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.656283222460509</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.605432955931526</v>
+        <v>-5.170556990346752</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.413753615774151</v>
+        <v>1.587704002008061</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2192375007436077</v>
+        <v>0.4830621782903363</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.787825722906674</v>
+        <v>3.946120529434712</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.727120228236934</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.624021114653751</v>
+        <v>-5.189145149068977</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.477155358061687</v>
+        <v>1.651105744295597</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2006493420213823</v>
+        <v>0.4644740195681109</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.847509833449764</v>
+        <v>4.005804639977801</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.723989239055233</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.624319661349787</v>
+        <v>-5.189443695765013</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.473904950201571</v>
+        <v>1.647855336435481</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2003507953253464</v>
+        <v>0.464175472872075</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.844199716250441</v>
+        <v>4.002494522778478</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.728520133994624</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.52349652765936</v>
+        <v>-5.088620562074585</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.518765098617133</v>
+        <v>1.692715484851043</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2128150108097003</v>
+        <v>0.4766396883564288</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.856209140480445</v>
+        <v>4.014503947008482</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.728649387473168</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.332715166906953</v>
+        <v>-4.897839201322178</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.595206896396639</v>
+        <v>1.769157282630549</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4035963715621076</v>
+        <v>0.6674210491088362</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.970807210410433</v>
+        <v>4.12910201693847</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.708486233210764</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.314198312865132</v>
+        <v>-4.879322347280358</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.582450483750964</v>
+        <v>1.756400869984874</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4165265009873159</v>
+        <v>0.6803511785340444</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.958402133803154</v>
+        <v>4.116696940331191</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.743453169822823</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.25886772496337</v>
+        <v>-4.823991759378595</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.639549655523727</v>
+        <v>1.813500041757637</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.471857088889078</v>
+        <v>0.7356817664358065</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.02656742315627</v>
+        <v>4.184862229684307</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.73713973772426</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.246813598050407</v>
+        <v>-4.811937632465632</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.63805787419035</v>
+        <v>1.81200826042426</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4839112158020408</v>
+        <v>0.7477358933487693</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.027486467205485</v>
+        <v>4.185781273733522</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.739020367908396</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.287968717618628</v>
+        <v>-4.853092752033853</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.623476456547198</v>
+        <v>1.797426842781108</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4427560962338199</v>
+        <v>0.7065807737805484</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.004674025648688</v>
+        <v>4.162968832176725</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.751871393786279</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.185088128090035</v>
+        <v>-4.75021216250526</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.677479718236517</v>
+        <v>1.851430104470427</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5456366857624129</v>
+        <v>0.8094613633091413</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.079253405243727</v>
+        <v>4.237548211771764</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.772074063959873</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.416688521259536</v>
+        <v>-4.981812555674761</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.605042231142311</v>
+        <v>1.778992617376221</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5456366857624129</v>
+        <v>0.8094613633091413</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.099456075417321</v>
+        <v>4.257750881945358</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.772074063959873</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.434761029551147</v>
+        <v>-4.999885063966373</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.597813227825667</v>
+        <v>1.771763614059576</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5456366857624129</v>
+        <v>0.8094613633091413</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.099456075417321</v>
+        <v>4.257750881945358</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.73232597755334</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.609867862127592</v>
+        <v>-5.174991896542817</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.488022408388555</v>
+        <v>1.661972794622465</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5456366857624129</v>
+        <v>0.8094613633091413</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.059707989010787</v>
+        <v>4.218002795538824</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.73934859655028</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.578581841587137</v>
+        <v>-5.143705876002362</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.507559435601677</v>
+        <v>1.681509821835587</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.5769227063028682</v>
+        <v>0.8407473838495967</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.085502220332001</v>
+        <v>4.243797026860038</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.838519596123184</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.425556449473852</v>
+        <v>-4.990680483889077</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.667940592019896</v>
+        <v>1.841890978253806</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.7299480984161524</v>
+        <v>0.9937727759628809</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.276488455172876</v>
+        <v>4.434783261700913</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.453863763347123</v>
+        <v>-5.018987797762348</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.84408389137888</v>
+        <v>2.01803427761279</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.7299480984161524</v>
+        <v>0.9937727759628809</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.463954680081168</v>
+        <v>4.622249486609205</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.620456988460645</v>
+        <v>-5.102587325561637</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.746849552687553</v>
+        <v>1.953997417847156</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.5633548733026299</v>
+        <v>0.910173248163592</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.333401696367137</v>
+        <v>4.541492721283714</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568385</v>
+        <v>3.708202704568384</v>
       </c>
       <c r="C2054" t="n">
         <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.447392609078345</v>
+        <v>-4.929522946179337</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.819751707102191</v>
+        <v>2.026899572261794</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.5633548733026299</v>
+        <v>0.910173248163592</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.337078099028854</v>
+        <v>4.545169123945431</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682207</v>
+        <v>3.740601586682206</v>
       </c>
       <c r="C2055" t="n">
         <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.418146628622648</v>
+        <v>-4.90027696572364</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.829068154407965</v>
+        <v>2.036216019567568</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.5633548733026299</v>
+        <v>0.910173248163592</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.33469615415235</v>
+        <v>4.542787179068926</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69942482753911</v>
+        <v>3.699424827539109</v>
       </c>
       <c r="C2056" t="n">
         <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.525072176500499</v>
+        <v>-5.007202513601491</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.783591174414459</v>
+        <v>1.990739039574063</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.4564293254247785</v>
+        <v>0.8032477002857407</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.267834064583274</v>
+        <v>4.475925089499851</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.68996278598374</v>
+        <v>3.689962785983739</v>
       </c>
       <c r="C2057" t="n">
         <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.670090735007748</v>
+        <v>-5.15222107210874</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.727012553154794</v>
+        <v>1.934160418314397</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.31141076691753</v>
+        <v>0.6582291417784921</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.182251731622159</v>
+        <v>4.390342756538736</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969751</v>
+        <v>3.71187261496975</v>
       </c>
       <c r="C2058" t="n">
         <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.788432500792466</v>
+        <v>-5.270562837893458</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.77960708609866</v>
+        <v>1.986754951258263</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.3220968054804201</v>
+        <v>0.6689151803413822</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.288594594017646</v>
+        <v>4.496685618934223</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.839842923113173</v>
+        <v>-5.321973260214166</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.756828614296316</v>
+        <v>1.963976479455919</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.3220968054804201</v>
+        <v>0.6689151803413822</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.286380291143584</v>
+        <v>4.494471316060162</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.919262374320925</v>
+        <v>-5.401392711421917</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.724963961887505</v>
+        <v>1.932111827047108</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.3220968054804201</v>
+        <v>0.6689151803413822</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.286283419217874</v>
+        <v>4.494374444134452</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-6.014725372238143</v>
+        <v>-5.496855709339135</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.686772656278661</v>
+        <v>1.893920521438264</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.3220968054804201</v>
+        <v>0.6689151803413822</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.286277312775917</v>
+        <v>4.494368337692495</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-6.054745370281926</v>
+        <v>-5.536875707382919</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.668861053623758</v>
+        <v>1.876008918783361</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.2820768074366363</v>
+        <v>0.6288951822975983</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.260361710512258</v>
+        <v>4.468452735428835</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-6.11011453241412</v>
+        <v>-5.592244869515112</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.652447206518607</v>
+        <v>1.85959507167821</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.2820768074366363</v>
+        <v>0.6288951822975983</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.266095528259984</v>
+        <v>4.474186553176562</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-6.155552312244947</v>
+        <v>-5.63768264934594</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.633810457929209</v>
+        <v>1.840958323088812</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.2392318167584766</v>
+        <v>0.5860501916194387</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.239926897196022</v>
+        <v>4.448017922112599</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-6.072326855397283</v>
+        <v>-5.554457192498275</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.686975033518594</v>
+        <v>1.894122898678197</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.2392318167584766</v>
+        <v>0.5860501916194387</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.259801290046341</v>
+        <v>4.467892314962918</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.896036630791976</v>
+        <v>-5.378166967892968</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.741191823885445</v>
+        <v>1.948339689045048</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.2392318167584766</v>
+        <v>0.5860501916194387</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.243501990571069</v>
+        <v>4.451593015487646</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.71282496765888</v>
+        <v>-5.194955304759873</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.816907438602728</v>
+        <v>2.024055303762331</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.2392318167584766</v>
+        <v>0.5860501916194387</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.245932940035114</v>
+        <v>4.454023964951691</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.068185035827917</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.64110352064503</v>
+        <v>-5.123233857746022</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.811387203256158</v>
+        <v>2.018535068415761</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.3109532637723272</v>
+        <v>0.6577716386332894</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.254756994091314</v>
+        <v>4.462848019007891</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.744367298966522</v>
+        <v>3.835466234967791</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.989099762470332</v>
+        <v>4.200626506124215</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.64110352064503</v>
+        <v>-5.123233857746022</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.811387203256158</v>
+        <v>2.018535068415761</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.3109532637723272</v>
+        <v>0.6577716386332894</v>
       </c>
       <c r="G2069" t="n">
-        <v>3.9821635594567</v>
+        <v>4.193690303110583</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240827.xlsx
+++ b/tame_output/ON/bt/strategyON_20240827.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>13.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>79.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-48.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.5%</t>
+          <t>419.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-673.9%</t>
+          <t>-687.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-174.4%</t>
+          <t>-195.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-292.6%</t>
+          <t>-964.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-158.2%</t>
+          <t>-175.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-26.2%</t>
         </is>
       </c>
     </row>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382325</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178241</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.292744275316419</v>
+        <v>-9.530782948247117</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5387099443255381</v>
+        <v>-0.6339254134978174</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.611510313665351</v>
+        <v>-1.672714665325319</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.211838001915567</v>
+        <v>2.175115390919586</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.168165618978827</v>
+        <v>-9.406204291909525</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4877393372344425</v>
+        <v>-0.5829548064067214</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.611510313665351</v>
+        <v>-1.672714665325319</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.212977146471625</v>
+        <v>2.176254535475645</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.221060907023114</v>
+        <v>-9.459099579953811</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.5062636782900496</v>
+        <v>-0.6014791474623284</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.606554967576905</v>
+        <v>-1.667759319236873</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.218584128286801</v>
+        <v>2.18186151729082</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.148927731735233</v>
+        <v>-9.38696640466593</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4716767039362608</v>
+        <v>-0.5668921731085397</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.606554967576905</v>
+        <v>-1.667759319236873</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.224317832525437</v>
+        <v>2.187595221529457</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.077561339125586</v>
+        <v>-9.315600012056283</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.452867409286267</v>
+        <v>-0.5480828784585459</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.535188574967257</v>
+        <v>-1.596392926627225</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.257400405697361</v>
+        <v>2.22067779470138</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.984102305140361</v>
+        <v>-9.222140978071058</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.4253672770050847</v>
+        <v>-0.5205827461773636</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.535188574967257</v>
+        <v>-1.596392926627225</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.247516924384453</v>
+        <v>2.210794313388472</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.97344912358693</v>
+        <v>-9.211487796517627</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4229405648830857</v>
+        <v>-0.5181560340553646</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.535188574967257</v>
+        <v>-1.596392926627225</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.24568236388508</v>
+        <v>2.208959752889099</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.875542084910439</v>
+        <v>-9.113580757841136</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3840780643859505</v>
+        <v>-0.4792935335582293</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.467202825106701</v>
+        <v>-1.528407176766668</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.286173498827953</v>
+        <v>2.249450887831972</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.851588543934481</v>
+        <v>-9.089627216865178</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3738281418500735</v>
+        <v>-0.4690436110223524</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.443249284130743</v>
+        <v>-1.504453635790711</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.301214129559021</v>
+        <v>2.26449151856304</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.587528605611684</v>
+        <v>-8.825567278542382</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2814644826827069</v>
+        <v>-0.3766799518549862</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.179189345807947</v>
+        <v>-1.240393697467915</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.446389776390946</v>
+        <v>2.409667165394966</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.880448982106846</v>
+        <v>-8.118487655037544</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.001419666941072428</v>
+        <v>-0.09663513611335173</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.179189345807947</v>
+        <v>-1.240393697467915</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.443602742730645</v>
+        <v>2.406880131734665</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.840264683740656</v>
+        <v>-8.078303356671354</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.01499767629324511</v>
+        <v>-0.08021779287903419</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.139005047441756</v>
+        <v>-1.200209399101724</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.468056945638201</v>
+        <v>2.431334334642221</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.676864812801293</v>
+        <v>-7.914903485731991</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.07972444588974703</v>
+        <v>-0.01549102328253227</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9756051765023934</v>
+        <v>-1.036809528162361</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.565463689422576</v>
+        <v>2.528741078426595</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.443383590571695</v>
+        <v>-7.681422263502393</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1810413636194386</v>
+        <v>0.08582589444715927</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7421239542727949</v>
+        <v>-0.8033283059327627</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.713476851598187</v>
+        <v>2.676754240602206</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.293717199564179</v>
+        <v>-7.531755872494878</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2380157097094857</v>
+        <v>0.1428002405372064</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6492204630302589</v>
+        <v>-0.7104248146902268</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.76632673603075</v>
+        <v>2.729604125034769</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.161441725933293</v>
+        <v>-7.399480398863991</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.1921866851689948</v>
+        <v>0.09697121599671554</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5169449893993723</v>
+        <v>-0.5781493410593401</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.746952806216436</v>
+        <v>2.710230195220455</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105956</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.005703393373551</v>
+        <v>-7.243742066304249</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2572970788805282</v>
+        <v>0.1620816097082489</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3612066568396307</v>
+        <v>-0.4224110084995986</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.843210866439918</v>
+        <v>2.806488255443937</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.920738726644231</v>
+        <v>-7.15877739957493</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3041892867959151</v>
+        <v>0.2089738176236353</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2762419901103111</v>
+        <v>-0.337446341770279</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.907096007701168</v>
+        <v>2.870373396705188</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.026328716417336</v>
+        <v>-7.264367389348035</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1339773612874544</v>
+        <v>0.03876189211517467</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3818319798834155</v>
+        <v>-0.4430363315433833</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.715766084238087</v>
+        <v>2.679043473242106</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.958094131791908</v>
+        <v>-7.196132804722607</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2098155370147117</v>
+        <v>0.1146000678424324</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3634166570108795</v>
+        <v>-0.4246210086708473</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.775359619838695</v>
+        <v>2.738637008842714</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.873530691357055</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.810154090384309</v>
+        <v>-7.048192763315008</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1491126308895838</v>
+        <v>0.05389716171730452</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3430957411023219</v>
+        <v>-0.4043000927622898</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.667673246695662</v>
+        <v>2.630950635699681</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.864816705103577</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.75718456813032</v>
+        <v>-6.995223241061019</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1615864535377014</v>
+        <v>0.06637098436542166</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2901262188483331</v>
+        <v>-0.3513305705083009</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.690740973794577</v>
+        <v>2.654018362798596</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.857856093008484</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.591396372170029</v>
+        <v>-6.829435045100729</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2209411198267244</v>
+        <v>0.1257256506544446</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2901262188483331</v>
+        <v>-0.3513305705083009</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.683780361699484</v>
+        <v>2.647057750703503</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.872318447389627</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.558033165691261</v>
+        <v>-6.79607183862196</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2487487567993751</v>
+        <v>0.1535332876270954</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2901262188483331</v>
+        <v>-0.3513305705083009</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.698242716080627</v>
+        <v>2.661520105084646</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.866850567848822</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.449774028568739</v>
+        <v>-6.687812701499438</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2865845321075788</v>
+        <v>0.1913690629352991</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2901262188483331</v>
+        <v>-0.3513305705083009</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.692774836539822</v>
+        <v>2.656052225543841</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.864348661859399</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.326482893751608</v>
+        <v>-6.564521566682307</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.333399080045008</v>
+        <v>0.2381836108727282</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1668350840312026</v>
+        <v>-0.2280394356911704</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.764247611440677</v>
+        <v>2.727525000444697</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.872049640096724</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.273786026620317</v>
+        <v>-6.511824699551016</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3621788051348496</v>
+        <v>0.2669633359625698</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1141382168999114</v>
+        <v>-0.1753425685598792</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.803566709956777</v>
+        <v>2.766844098960796</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.867830348443774</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.030020584636873</v>
+        <v>-6.268059257567572</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4554656902752781</v>
+        <v>0.3602502211029983</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1141382168999114</v>
+        <v>-0.1753425685598792</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.799347418303828</v>
+        <v>2.762624807307847</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.86995466236379</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.9402449122604</v>
+        <v>-6.1782835851911</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4935002731458829</v>
+        <v>0.3982848039736031</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.05253877198560136</v>
+        <v>-0.1137431236455692</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.83843139917243</v>
+        <v>2.801708788176449</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.862696737347493</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.690394518311326</v>
+        <v>-5.928433191242025</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5861825057092149</v>
+        <v>0.4909670365369352</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.05253877198560136</v>
+        <v>-0.1137431236455692</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.831173474156132</v>
+        <v>2.794450863160151</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.866295860868141</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.514502425843894</v>
+        <v>-5.752541098774593</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6601384662168366</v>
+        <v>0.5649229970445568</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.05253877198560136</v>
+        <v>-0.1137431236455692</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.834772597676781</v>
+        <v>2.7980499866808</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.879623366922695</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.34305596282143</v>
+        <v>-5.581094635752129</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7420445574803756</v>
+        <v>0.6468290883080958</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1189076910368618</v>
+        <v>0.05770333937689393</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.950967981544812</v>
+        <v>2.914245370548831</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.878643844538992</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.263033675712309</v>
+        <v>-5.501072348643008</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7730739499403207</v>
+        <v>0.6778584807680414</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1989299781459827</v>
+        <v>0.1377256264860149</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.998001831426582</v>
+        <v>2.961279220430601</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.883338645593309</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.199397933478375</v>
+        <v>-5.437436606409074</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8032230478882121</v>
+        <v>0.7080075787159323</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2625657203799173</v>
+        <v>0.2013613687199494</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.04087807782126</v>
+        <v>3.004155466825279</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.864532904377105</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.10570061526198</v>
+        <v>-5.343739288192679</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8218962339585656</v>
+        <v>0.7266807647862858</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2625657203799173</v>
+        <v>0.2013613687199494</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.022072336605055</v>
+        <v>2.985349725609075</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242295</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.866275981001982</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.116203238327269</v>
+        <v>-5.354241911257968</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8194382613573277</v>
+        <v>0.7242227921850479</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2520630973146284</v>
+        <v>0.1908587456546605</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.01751383939076</v>
+        <v>2.980791228394779</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.870205294836802</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.043960670156074</v>
+        <v>-5.281999343086773</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8522646024606257</v>
+        <v>0.757049133288346</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2520630973146284</v>
+        <v>0.1908587456546605</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.02144315322558</v>
+        <v>2.984720542229599</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.870883878754142</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.026246983278209</v>
+        <v>-5.264285656208908</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8600286611291117</v>
+        <v>0.764813191956832</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2552444262115452</v>
+        <v>0.1940400745515773</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.02403053448107</v>
+        <v>2.987307923485089</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.867881949974136</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.917442097798482</v>
+        <v>-5.155480770729181</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.900548686540996</v>
+        <v>0.8053332173687164</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2552444262115452</v>
+        <v>0.1940400745515773</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.021028605701063</v>
+        <v>2.984305994705083</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.86946098698475</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.697421299761471</v>
+        <v>-4.93545997269217</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9901360427664143</v>
+        <v>0.8949205735941348</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3964642712795254</v>
+        <v>0.3352599196195576</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.107339549752465</v>
+        <v>3.070616938756485</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539951</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.885355169786573</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.564553610698193</v>
+        <v>-4.802592283628893</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.059177301193549</v>
+        <v>0.9639618320212691</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3964642712795254</v>
+        <v>0.3352599196195576</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.123233732554289</v>
+        <v>3.086511121558308</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.886501014226875</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.444380527333695</v>
+        <v>-4.682419200264394</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.10839237897965</v>
+        <v>1.01317690980737</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5166373546440244</v>
+        <v>0.4554330029840565</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.19648342701329</v>
+        <v>3.159760816017309</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577001</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.896589116788315</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.309127166003718</v>
+        <v>-4.547165838934417</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.172581826073081</v>
+        <v>1.077366356900801</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6518907159740015</v>
+        <v>0.5906863643140337</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.287723546372716</v>
+        <v>3.251000935376736</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942107</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.882626608189741</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.36900199336141</v>
+        <v>-4.607040666292109</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.13466938653143</v>
+        <v>1.03945391735915</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5920158886163094</v>
+        <v>0.5308115369563415</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.237836141359527</v>
+        <v>3.201113530363546</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.897915777423949</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.249181762450573</v>
+        <v>-4.487220435381272</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.197886648129973</v>
+        <v>1.102671178957693</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5920158886163094</v>
+        <v>0.5308115369563415</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.253125310593735</v>
+        <v>3.216402699597755</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.805559976746391</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.251651468912379</v>
+        <v>-4.489690141843078</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.104542964867692</v>
+        <v>1.009327495695413</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5895461821545032</v>
+        <v>0.5283418304945353</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.159287686039093</v>
+        <v>3.122565075043112</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003597</v>
       </c>
       <c r="C1936" t="n">
         <v>2.724821838231692</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.320021655236389</v>
+        <v>-4.558060328167088</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9964567518233896</v>
+        <v>0.9012412826511098</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.5376175295307503</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.084114966946124</v>
+        <v>3.047392355950143</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.715258546863584</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.333809708083436</v>
+        <v>-4.571848381014135</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9813782393164621</v>
+        <v>0.8861627701441823</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.5376175295307503</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.074551675578015</v>
+        <v>3.037829064582034</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.852289383555786</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.389329783976025</v>
+        <v>-4.627368456906725</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.096201045651629</v>
+        <v>1.000985576479349</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.5376175295307503</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.211582512270217</v>
+        <v>3.174859901274237</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.856856615547574</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.213855524183556</v>
+        <v>-4.451894197114255</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.170957981560404</v>
+        <v>1.075742512388125</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.5376175295307503</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.216149744262005</v>
+        <v>3.179427133266024</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.832598644308781</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.205931149598642</v>
+        <v>-4.443969822529341</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.149869760155577</v>
+        <v>1.054654290983297</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.5376175295307503</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.191891773023212</v>
+        <v>3.155169162027232</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.761136957710231</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.199652947028793</v>
+        <v>-4.437691619959492</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.080919354584966</v>
+        <v>0.9857038854126867</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6051000837605671</v>
+        <v>0.5438957321005993</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.124197007966571</v>
+        <v>3.08747439697059</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.771309344142363</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.139800327825069</v>
+        <v>-4.377839000755769</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.115032788698588</v>
+        <v>1.019817319526308</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6051000837605671</v>
+        <v>0.5438957321005993</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.134369394398703</v>
+        <v>3.097646783402723</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.766255614716223</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.053556864798692</v>
+        <v>-4.291595537729391</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.144476444482999</v>
+        <v>1.04926097531072</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6051000837605671</v>
+        <v>0.5438957321005993</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.129315664972564</v>
+        <v>3.092593053976583</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.758031390160749</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.098863684197672</v>
+        <v>-4.336902357128371</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.118129492167933</v>
+        <v>1.022914022995653</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5642899207513363</v>
+        <v>0.5030855690913685</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.096605342611551</v>
+        <v>3.05988273161557</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.127896788899973</v>
+        <v>-4.365935461830672</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.107068123320114</v>
+        <v>1.011852654147835</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5642899207513363</v>
+        <v>0.5030855690913685</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.097157215644653</v>
+        <v>3.060434604648672</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.035086307449113</v>
+        <v>-4.273124980379812</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.073465007791824</v>
+        <v>0.978249538619544</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6571004022021957</v>
+        <v>0.5958960505422278</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.082116196406534</v>
+        <v>3.045393585410553</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.079475776778541</v>
+        <v>-4.31751444970924</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.057582695984653</v>
+        <v>0.9623672268123737</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.612710932872768</v>
+        <v>0.5515065812128002</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.057355990733478</v>
+        <v>3.020633379737498</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.196017381883883</v>
+        <v>-4.434056054814582</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.006041762454239</v>
+        <v>0.9108262932819597</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4961693277674253</v>
+        <v>0.4349649761074574</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.982506736181995</v>
+        <v>2.945784125186015</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.235941476466455</v>
+        <v>-4.473980149397154</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.995563420451878</v>
+        <v>0.9003479512795982</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4961693277674253</v>
+        <v>0.4349649761074574</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.987998032012662</v>
+        <v>2.951275421016682</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498866</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.263721874367808</v>
+        <v>-4.501760547298507</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9959484630598758</v>
+        <v>0.9007329938875963</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4683889298660722</v>
+        <v>0.4071845782061043</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.98282699504039</v>
+        <v>2.946104384044409</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.366632412571029</v>
+        <v>-4.620141220028645</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7931399677792408</v>
+        <v>0.6917364447961942</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4342330351271303</v>
+        <v>0.3399667260551281</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.800689178197678</v>
+        <v>2.744129392754477</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.47524649101436</v>
+        <v>-4.728755298471977</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8698439971211138</v>
+        <v>0.7684404741380673</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4342330351271303</v>
+        <v>0.3399667260551281</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.920838838916884</v>
+        <v>2.864279053473682</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.439837452766217</v>
+        <v>-4.693346260223834</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.898520638522694</v>
+        <v>0.7971171155396475</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4342330351271303</v>
+        <v>0.3399667260551281</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.935351865019207</v>
+        <v>2.878792079576005</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.401453790208066</v>
+        <v>-4.654962597665683</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.911293544888323</v>
+        <v>0.8098900219052765</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4726166976852815</v>
+        <v>0.3783503886132793</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.955801503896466</v>
+        <v>2.899241718453265</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.2243374601729</v>
+        <v>-4.477846267630516</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9788691057476915</v>
+        <v>0.8774655827646449</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4726166976852815</v>
+        <v>0.3783503886132793</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.952530532741768</v>
+        <v>2.895970747298567</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.269429705006446</v>
+        <v>-4.522938512464062</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9615155995761864</v>
+        <v>0.8601120765931398</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4107206545158917</v>
+        <v>0.3164543454438895</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.916076298602047</v>
+        <v>2.859516513158846</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.090054283767678</v>
+        <v>-4.343563091225294</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.027052743378108</v>
+        <v>0.9256492203950613</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5674974126866104</v>
+        <v>0.4732311036146082</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.003929328810893</v>
+        <v>2.947369543367691</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.135068497288284</v>
+        <v>-4.388577304745901</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9898545133014551</v>
+        <v>0.8884509903184084</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5371485173720058</v>
+        <v>0.4428822083000036</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.96652744695372</v>
+        <v>2.909967661510518</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.402073007560719</v>
+        <v>-4.655581815018336</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8887442715314269</v>
+        <v>0.7873407485483801</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3427854793290572</v>
+        <v>0.248519170257055</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.855601186466896</v>
+        <v>2.799041401023695</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.503270788997892</v>
+        <v>-4.756779596455509</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8474690808530592</v>
+        <v>0.7460655578700124</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.274376665783738</v>
+        <v>0.1801103567117358</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.813759820236206</v>
+        <v>2.757200034793005</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70557166181546</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.496759822383579</v>
+        <v>-4.750268629841196</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8476734290531009</v>
+        <v>0.7462699060700542</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.274376665783738</v>
+        <v>0.1801103567117358</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.811359781790523</v>
+        <v>2.754799996347322</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378106</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.477721694676282</v>
+        <v>-4.731230502133899</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8518133993442649</v>
+        <v>0.7504098763612179</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2161930544525434</v>
+        <v>0.1219267453805413</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.772974334200051</v>
+        <v>2.71641454875685</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.530237496951102</v>
+        <v>-4.783746304408719</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.950101480068527</v>
+        <v>0.8486979570854802</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2161930544525434</v>
+        <v>0.1219267453805413</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.892268735834242</v>
+        <v>2.83570895039104</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.54410425828502</v>
+        <v>-4.797613065742637</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9453881045210935</v>
+        <v>0.8439845815380465</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1783351377187205</v>
+        <v>0.08406882864671833</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.870387314780081</v>
+        <v>2.81382752933688</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.49930008674509</v>
+        <v>-4.752808894202707</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9693183035339914</v>
+        <v>0.8679147805509444</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1783351377187205</v>
+        <v>0.08406882864671833</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.876395845177007</v>
+        <v>2.819836059733806</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.351557116510087</v>
+        <v>-4.605065923967705</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9263657129051919</v>
+        <v>0.8249621899221449</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3461424949536037</v>
+        <v>0.2518761858816015</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.875030480795137</v>
+        <v>2.818470695351935</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.435378337784786</v>
+        <v>-4.688887145242403</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8956308459267934</v>
+        <v>0.7942273229437466</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3461424949536037</v>
+        <v>0.2518761858816015</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.877824102326618</v>
+        <v>2.821264316883416</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.429225631732002</v>
+        <v>-4.682734439189619</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8987542767395655</v>
+        <v>0.7973507537565188</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3522952010063879</v>
+        <v>0.2580288919343858</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.882178074349946</v>
+        <v>2.825618288906745</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890615</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.446034929882503</v>
+        <v>-4.699543737340121</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.891111034219475</v>
+        <v>0.7897075112364282</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3354859028558863</v>
+        <v>0.2412195937838841</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.871172972199756</v>
+        <v>2.814613186756555</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.383736931106381</v>
+        <v>-4.637245738563998</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9823657875267449</v>
+        <v>0.8809622645436979</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3807801671303284</v>
+        <v>0.2865138580583262</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.964685084561242</v>
+        <v>2.908125299118041</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.181946733441223</v>
+        <v>-4.435455540898841</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8653738683069352</v>
+        <v>0.7639703453238882</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5787983592994828</v>
+        <v>0.4845320502274806</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.885788001576862</v>
+        <v>2.82922821613366</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852429</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.232833446127418</v>
+        <v>-4.486342253585035</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9153094155546324</v>
+        <v>0.8139058925715856</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5279116466132883</v>
+        <v>0.433645337541286</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.92554620628732</v>
+        <v>2.868986420844119</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.146222703477611</v>
+        <v>-4.399731510935228</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9645814487305988</v>
+        <v>0.8631779257475518</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6065373778184465</v>
+        <v>0.5122710687464442</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.987349381126459</v>
+        <v>2.930789595683257</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.206432001482896</v>
+        <v>-4.459940808940513</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9390337103531565</v>
+        <v>0.8376301873701095</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.546328079813162</v>
+        <v>0.4520617707411597</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.94975978314796</v>
+        <v>2.893199997704758</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.130009955050969</v>
+        <v>-4.383518762508587</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9680941469658557</v>
+        <v>0.8666906239828089</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.546328079813162</v>
+        <v>0.4520617707411597</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.948251401187888</v>
+        <v>2.891691615744687</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316251</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.085636823412401</v>
+        <v>-4.339145630870018</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9857062670567194</v>
+        <v>0.8843027440736726</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5907012114517306</v>
+        <v>0.4964349023797283</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.974738147606466</v>
+        <v>2.918178362163264</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.108117174271285</v>
+        <v>-4.361625981728903</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9711079208517561</v>
+        <v>0.8697043978687091</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5907012114517306</v>
+        <v>0.4964349023797283</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.969131941745056</v>
+        <v>2.912572156301855</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190328</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.06046144371023</v>
+        <v>-4.313970251167847</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9965519701039831</v>
+        <v>0.8951484471209361</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6383569420127863</v>
+        <v>0.544090632940784</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.004107137109494</v>
+        <v>2.947547351666293</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056962</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.959943285211475</v>
+        <v>-4.213452092669092</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.04165160687821</v>
+        <v>0.9402480838951628</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7388751005115408</v>
+        <v>0.6446087914395385</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.069310405583471</v>
+        <v>3.01275062014027</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557297</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.944037955779122</v>
+        <v>-4.19754676323674</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.034768411127023</v>
+        <v>0.933364888143976</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6597624398023019</v>
+        <v>0.5654961307302997</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.0085974816338</v>
+        <v>2.952037696190599</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932772</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.899199554170724</v>
+        <v>-4.152708361628341</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.056801474381011</v>
+        <v>0.955397951397964</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6643058727471713</v>
+        <v>0.5700395636751692</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.015421244011351</v>
+        <v>2.958861458568149</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917054</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.918698010412732</v>
+        <v>-4.172206817870349</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.053163031515286</v>
+        <v>0.9517595085322388</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.616221231467267</v>
+        <v>0.5219549223952649</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.990731398874486</v>
+        <v>2.934171613431285</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405962</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.874495173326832</v>
+        <v>-4.128003980784449</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.076723768877483</v>
+        <v>0.9753202458944361</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6604240685531675</v>
+        <v>0.5661577594811653</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.023132703653864</v>
+        <v>2.966572918210662</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265647</v>
+        <v>3.83819962926564</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.882054839163879</v>
+        <v>-4.135563646621495</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.072109903011912</v>
+        <v>0.9707063800288651</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7152274725629868</v>
+        <v>0.6209611634909846</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.054424746529003</v>
+        <v>2.997864961085801</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284881</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.723763421624607</v>
+        <v>-3.977272229082223</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.18667423521066</v>
+        <v>1.085270712227614</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7152274725629868</v>
+        <v>0.6209611634909846</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.105672511712042</v>
+        <v>3.049112726268841</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321025</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.516121417990131</v>
+        <v>-3.769630225447747</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.268171741258704</v>
+        <v>1.166768218275657</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.922869476197463</v>
+        <v>0.8286031671254608</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.228698418486981</v>
+        <v>3.17213863304378</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.465089325267602</v>
+        <v>-3.718598132725219</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.283532806585985</v>
+        <v>1.182129283602938</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9739015689199909</v>
+        <v>0.8796352598479887</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.254265902358768</v>
+        <v>3.197706116915567</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404855</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.399865144140397</v>
+        <v>-3.653373951598013</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.326809883129572</v>
+        <v>1.225406360146526</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.039125750047197</v>
+        <v>0.9448594409751944</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.310587815127796</v>
+        <v>3.254028029684595</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.362438124069263</v>
+        <v>-3.615946931526879</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.337741663457306</v>
+        <v>1.236338140474259</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.044377288076378</v>
+        <v>0.950110979004376</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.309699710244586</v>
+        <v>3.253139924801384</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.382549780103971</v>
+        <v>-3.636058587561588</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.330953793374663</v>
+        <v>1.229550270391617</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.055404633073797</v>
+        <v>0.9611383240017952</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.317572909574277</v>
+        <v>3.261013124131076</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.354136517004088</v>
+        <v>-3.607645324461704</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.502876869635827</v>
+        <v>1.401473346652781</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9964290703273686</v>
+        <v>0.9021627612553664</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.442745342947631</v>
+        <v>3.38618555750443</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.279354255979075</v>
+        <v>-3.532863063436691</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.65290268326365</v>
+        <v>1.551499160280603</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.071211331352381</v>
+        <v>0.976945022280379</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.607727608780456</v>
+        <v>3.551167823337254</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.253270171715267</v>
+        <v>-3.506778979172883</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.655044292983032</v>
+        <v>1.553640769999985</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.071211331352381</v>
+        <v>0.976945022280379</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.599435584794315</v>
+        <v>3.542875799351113</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.165392258606146</v>
+        <v>-3.418901066063763</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.688388653810459</v>
+        <v>1.586985130827413</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.187136973775732</v>
+        <v>1.09287066470373</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.667184165832105</v>
+        <v>3.610624380388904</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.156499797212863</v>
+        <v>-3.410008604670479</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.709500044094564</v>
+        <v>1.608096521111518</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.187136973775732</v>
+        <v>1.09287066470373</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.684738571558896</v>
+        <v>3.628178786115695</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.324975914182741</v>
+        <v>-3.578484721640357</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.633964644711197</v>
+        <v>1.532561121728151</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.159189138059151</v>
+        <v>1.06492282898715</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.659824917533532</v>
+        <v>3.603265132090331</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.79557406678271</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.878719721553301</v>
+        <v>-3.132228529010917</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.793736818950835</v>
+        <v>1.692333295967788</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.064470468389519</v>
+        <v>0.9702041593175168</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.584263412919614</v>
+        <v>3.527703627476413</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.855998617870148</v>
+        <v>-3.109507425327765</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.793489282921</v>
+        <v>1.692085759937954</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.064470468389519</v>
+        <v>0.9702041593175168</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.574927435416519</v>
+        <v>3.518367649973317</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.985200431164191</v>
+        <v>-3.238709238621807</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.900714683454553</v>
+        <v>1.799311160471506</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9352686550954765</v>
+        <v>0.8410023460234746</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.656312473291262</v>
+        <v>3.599752687848061</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.011074829638217</v>
+        <v>-3.264583637095833</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.927442746558588</v>
+        <v>1.826039223575542</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9801802638072177</v>
+        <v>0.8859139547352157</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.720337261011953</v>
+        <v>3.663777475568752</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799967</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.004020139423043</v>
+        <v>-3.257528946880659</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.926939978634203</v>
+        <v>1.825536455651157</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9872349540223915</v>
+        <v>0.8929686449503895</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.721245431130603</v>
+        <v>3.664685645687402</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331118</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.977068915096555</v>
+        <v>-3.230577722554171</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.94772662200954</v>
+        <v>1.846323099026493</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.002115300050111</v>
+        <v>0.9078489909781087</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.740179792391976</v>
+        <v>3.683620006948775</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784111</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.113021923152871</v>
+        <v>-3.366530730610488</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.077448550931973</v>
+        <v>1.976045027948927</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.002115300050111</v>
+        <v>0.9078489909781087</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.924282924536936</v>
+        <v>3.867723139093735</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.135430040957743</v>
+        <v>-3.38893884841536</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.060601998713017</v>
+        <v>1.959198475729971</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.002115300050111</v>
+        <v>0.9078489909781087</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.916399619439929</v>
+        <v>3.859839833996728</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.163654276535344</v>
+        <v>-3.41716308399296</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.051366304031615</v>
+        <v>1.949962781048568</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.020092052501419</v>
+        <v>0.9258257434294173</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.929239670460351</v>
+        <v>3.87267988501715</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.173095202423874</v>
+        <v>-3.42660400988149</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.10384365139805</v>
+        <v>2.002440128415004</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.142519170044811</v>
+        <v>1.048252860972809</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.058949658708233</v>
+        <v>4.002389873265033</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.225368809759515</v>
+        <v>-3.478877617217131</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.085825303009094</v>
+        <v>1.984421780026048</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.090245562709169</v>
+        <v>0.9959792536371674</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.030476588852149</v>
+        <v>3.973916803408948</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.301698787360421</v>
+        <v>-3.555207594818037</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.053405124862507</v>
+        <v>1.952001601879461</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.090245562709169</v>
+        <v>0.9959792536371674</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.028588401745925</v>
+        <v>3.972028616302723</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.503952507684774</v>
+        <v>-3.757461315142391</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.967323866335628</v>
+        <v>1.865920343352582</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8879918423848159</v>
+        <v>0.7937255333128139</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.902056399154175</v>
+        <v>3.845496613710974</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.665520933212029</v>
+        <v>-3.919029740669646</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.901130506334878</v>
+        <v>1.799726983351832</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7612089185869365</v>
+        <v>0.6669426095149346</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.824420655085599</v>
+        <v>3.767860869642398</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389351</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.773821595082149</v>
+        <v>-4.027330402539765</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.870883648452749</v>
+        <v>1.769480125469703</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7612089185869365</v>
+        <v>0.6669426095149346</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.837494061951518</v>
+        <v>3.780934276508317</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378395</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.866969066385515</v>
+        <v>-4.120477873843132</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.825629856714343</v>
+        <v>1.724226333731296</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6383797073044037</v>
+        <v>0.5441133982324018</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.755801731964938</v>
+        <v>3.699241946521737</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006979</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.894869853494988</v>
+        <v>-4.148378660952605</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.812993582997555</v>
+        <v>1.711590060014509</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6037827831614689</v>
+        <v>0.509516474089467</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.733567618606179</v>
+        <v>3.677007833162978</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787391</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.017395956197882</v>
+        <v>-4.270904763655499</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.760747585893597</v>
+        <v>1.65934406291055</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4812566804585751</v>
+        <v>0.3869903713865731</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.656816400961642</v>
+        <v>3.600256615518441</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585941</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.247910452383471</v>
+        <v>-4.501419259841088</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.735247747009865</v>
+        <v>1.633844224026818</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2507421842729863</v>
+        <v>0.1564758752009844</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.585213662840792</v>
+        <v>3.528653877397591</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814668</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.596655537607915</v>
+        <v>-4.850164345065531</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.736061431921934</v>
+        <v>1.634657908938888</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1419942303540885</v>
+        <v>0.04772792128208658</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.660276609491301</v>
+        <v>3.6037168240481</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237098</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.750641955384055</v>
+        <v>-5.004150762841672</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.743447133957118</v>
+        <v>1.642043610974071</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1419942303540885</v>
+        <v>0.04772792128208658</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.729256878636941</v>
+        <v>3.67269709319374</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423391</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.700120051556389</v>
+        <v>-4.953628859014006</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.749707097608305</v>
+        <v>1.648303574625259</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1419942303540885</v>
+        <v>0.04772792128208658</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.715308080757062</v>
+        <v>3.658748295313861</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609757</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.952595205564114</v>
+        <v>-5.20610401302173</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.660587525060629</v>
+        <v>1.559184002077583</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1419942303540885</v>
+        <v>0.04772792128208658</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.727178569812476</v>
+        <v>3.670618784369275</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973161</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.245490962043526</v>
+        <v>-5.498999769501142</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.544639756987808</v>
+        <v>1.443236234004762</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1419942303540885</v>
+        <v>0.04772792128208658</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.728389104331419</v>
+        <v>3.671829318888218</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251949</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.432155090178334</v>
+        <v>-5.68566389763595</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.474095847961206</v>
+        <v>1.37269232497816</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1152552595295286</v>
+        <v>0.02098895045752669</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.716467464064005</v>
+        <v>3.659907678620804</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916205</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.578175777092296</v>
+        <v>-5.831684584549913</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.410765425931811</v>
+        <v>1.309361902948765</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1061721677356717</v>
+        <v>0.01190585866366972</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.70609546172388</v>
+        <v>3.649535676280679</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830332</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.669889786201882</v>
+        <v>-5.923398593659497</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.536283878987021</v>
+        <v>1.434880356003975</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1061721677356717</v>
+        <v>0.01190585866366972</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.868299518422924</v>
+        <v>3.811739732979723</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.701541445261851</v>
+        <v>-5.955050252719467</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.518469853326847</v>
+        <v>1.417066330343801</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1010037104912315</v>
+        <v>0.006737401419229516</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.860045082040074</v>
+        <v>3.803485296596873</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.783476263530734</v>
+        <v>-6.03698507098835</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.495925343587785</v>
+        <v>1.394521820604739</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.09106896490415128</v>
+        <v>-0.003197344167850669</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.864313652256317</v>
+        <v>3.807753866813116</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.885452385779142</v>
+        <v>-6.138961193236757</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.464060533144325</v>
+        <v>1.362657010161278</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.01090715734425629</v>
+        <v>-0.1051734664162582</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.812053617363175</v>
+        <v>3.755493831919974</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.77544610230192</v>
+        <v>-6.028954909759536</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.500215933779389</v>
+        <v>1.398812410796342</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.01229741457301892</v>
+        <v>-0.08196889449898304</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.818129247757716</v>
+        <v>3.761569462314514</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818526</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.632386526560994</v>
+        <v>-5.88589533401861</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.561689774797733</v>
+        <v>1.460286251814687</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.02031084116299819</v>
+        <v>-0.07395546790900376</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.827187314433678</v>
+        <v>3.770627528990476</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051791</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.330939801089157</v>
+        <v>-5.584448608546772</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.689529347869005</v>
+        <v>1.588125824885958</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3217575666348355</v>
+        <v>0.2274912575628335</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.015316232599316</v>
+        <v>3.958756447156115</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679628</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.355530045324341</v>
+        <v>-5.609038852781956</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.680664427927641</v>
+        <v>1.579260904944595</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3217575666348355</v>
+        <v>0.2274912575628335</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.016287410352026</v>
+        <v>3.959727624908825</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474163</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.82407577475088</v>
+        <v>3.718989340645655</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.30449166931782</v>
+        <v>-5.558000476775436</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.701922682710005</v>
+        <v>1.495432725621733</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3217575666348355</v>
+        <v>0.2274912575628335</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.017130314731782</v>
+        <v>3.855484095183355</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969546</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.843113873625026</v>
+        <v>3.7380274395198</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.263352374451189</v>
+        <v>-5.516861181908805</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.737416499530803</v>
+        <v>1.530926542442531</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3628968615014663</v>
+        <v>0.2686305524294643</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.060851990525906</v>
+        <v>3.899205770977479</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700482</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.65929786974896</v>
+        <v>3.554211435643735</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.166717462432549</v>
+        <v>-5.420226269890165</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.592254460462193</v>
+        <v>1.385764503373922</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4595317735201062</v>
+        <v>0.3652654644481043</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.935016933861024</v>
+        <v>3.773370714312598</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077643</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.662799913822925</v>
+        <v>3.557713479717699</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.297298196963392</v>
+        <v>-5.550807004421007</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.543524210723821</v>
+        <v>1.337034253635549</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3289510389892637</v>
+        <v>0.2346847299172617</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.860170537216483</v>
+        <v>3.698524317668056</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083346</v>
+        <v>3.775028860833454</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.647226732899007</v>
+        <v>3.542140298793782</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.13280186277243</v>
+        <v>-5.386310670230046</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.593749563476288</v>
+        <v>1.387259606388016</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4934473731802256</v>
+        <v>0.3991810641082236</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.943295156807142</v>
+        <v>3.781648937258716</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077632</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.646414443335437</v>
+        <v>3.541328009230211</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.160171795456862</v>
+        <v>-5.413680602914478</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.581989300838945</v>
+        <v>1.375499343750673</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4934473731802256</v>
+        <v>0.3991810641082236</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.942482867243572</v>
+        <v>3.780836647695146</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147913</v>
+        <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.656283222460509</v>
+        <v>3.551196788355284</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.170556990346752</v>
+        <v>-5.424065797804367</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.587704002008061</v>
+        <v>1.38121404491979</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4830621782903363</v>
+        <v>0.3887958692183343</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.946120529434712</v>
+        <v>3.784474309886285</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735284</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.727120228236934</v>
+        <v>3.622033794131709</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.189145149068977</v>
+        <v>-5.442653956526592</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.651105744295597</v>
+        <v>1.444615787207325</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4644740195681109</v>
+        <v>0.370207710496109</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.005804639977801</v>
+        <v>3.844158420429375</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496557</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.723989239055233</v>
+        <v>3.618902804950007</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.189443695765013</v>
+        <v>-5.442952503222628</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.647855336435481</v>
+        <v>1.441365379347209</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.464175472872075</v>
+        <v>0.369909163800073</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.002494522778478</v>
+        <v>3.840848303230052</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108859</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.728520133994624</v>
+        <v>3.623433699889399</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.088620562074585</v>
+        <v>-5.3421293695322</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.692715484851043</v>
+        <v>1.486225527762771</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4766396883564288</v>
+        <v>0.3823733792844269</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.014503947008482</v>
+        <v>3.852857727460055</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121468</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.728649387473168</v>
+        <v>3.623562953367942</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.897839201322178</v>
+        <v>-5.151348008779793</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.769157282630549</v>
+        <v>1.562667325542277</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6674210491088362</v>
+        <v>0.5731547400368342</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.12910201693847</v>
+        <v>3.967455797390043</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.708486233210764</v>
+        <v>3.603399799105539</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.879322347280358</v>
+        <v>-5.132831154737973</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.756400869984874</v>
+        <v>1.549910912896602</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6803511785340444</v>
+        <v>0.5860848694620424</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.116696940331191</v>
+        <v>3.955050720782764</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912987</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.743453169822823</v>
+        <v>3.638366735717597</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.823991759378595</v>
+        <v>-5.077500566836211</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.813500041757637</v>
+        <v>1.607010084669366</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7356817664358065</v>
+        <v>0.6414154573638046</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.184862229684307</v>
+        <v>4.02321601013588</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539896</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.73713973772426</v>
+        <v>3.632053303619035</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.811937632465632</v>
+        <v>-5.065446439923248</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.81200826042426</v>
+        <v>1.605518303335988</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7477358933487693</v>
+        <v>0.6534695842767674</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.185781273733522</v>
+        <v>4.024135054185096</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811011</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.739020367908396</v>
+        <v>3.633933933803171</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.853092752033853</v>
+        <v>-5.106601559491469</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.797426842781108</v>
+        <v>1.590936885692836</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7065807737805484</v>
+        <v>0.6123144647085464</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.162968832176725</v>
+        <v>4.001322612628298</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382921</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.751871393786279</v>
+        <v>3.646784959681053</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.75021216250526</v>
+        <v>-5.003720969962876</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.851430104470427</v>
+        <v>1.644940147382155</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8094613633091413</v>
+        <v>0.7151950542371394</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.237548211771764</v>
+        <v>4.075901992223337</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.772074063959873</v>
+        <v>3.666987629854647</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.981812555674761</v>
+        <v>-5.235321363132377</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.778992617376221</v>
+        <v>1.572502660287949</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8094613633091413</v>
+        <v>0.7151950542371394</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.257750881945358</v>
+        <v>4.096104662396931</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781708</v>
+        <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.772074063959873</v>
+        <v>3.666987629854647</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.999885063966373</v>
+        <v>-5.253393871423988</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.771763614059576</v>
+        <v>1.565273656971305</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8094613633091413</v>
+        <v>0.7151950542371394</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.257750881945358</v>
+        <v>4.096104662396931</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082837</v>
+        <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.73232597755334</v>
+        <v>3.627239543448114</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.174991896542817</v>
+        <v>-5.428500704000433</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.661972794622465</v>
+        <v>1.455482837534193</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8094613633091413</v>
+        <v>0.7151950542371394</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.218002795538824</v>
+        <v>4.056356575990398</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943589</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.73934859655028</v>
+        <v>3.634262162445054</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.143705876002362</v>
+        <v>-5.397214683459977</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.681509821835587</v>
+        <v>1.475019864747316</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8407473838495967</v>
+        <v>0.7464810747775947</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.243797026860038</v>
+        <v>4.082150807311611</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677826</v>
+        <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.838519596123184</v>
+        <v>3.733433162017958</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.990680483889077</v>
+        <v>-5.244189291346693</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.841890978253806</v>
+        <v>1.635401021165534</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9937727759628809</v>
+        <v>0.8995064668908789</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.434783261700913</v>
+        <v>4.273137042152486</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073886</v>
+        <v>3.741298518073879</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.025985821031476</v>
+        <v>3.920899386926251</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.018987797762348</v>
+        <v>-5.272496605219963</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.01803427761279</v>
+        <v>1.811544320524518</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9937727759628809</v>
+        <v>0.8995064668908789</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.622249486609205</v>
+        <v>4.460603267060778</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903171</v>
+        <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.995388772385558</v>
+        <v>3.890302338280333</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.102587325561637</v>
+        <v>-5.439089830333486</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.953997417847156</v>
+        <v>1.714309981833192</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.910173248163592</v>
+        <v>0.7329132417773565</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.541492721283714</v>
+        <v>4.330050283346748</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568384</v>
+        <v>3.708202704568379</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.999065175047276</v>
+        <v>3.893978740942051</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.929522946179337</v>
+        <v>-5.266025450951186</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.026899572261794</v>
+        <v>1.787212136247829</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.910173248163592</v>
+        <v>0.7329132417773565</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.545169123945431</v>
+        <v>4.333726686008466</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682206</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.996683230170771</v>
+        <v>3.891596796065546</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.90027696572364</v>
+        <v>-5.236779470495489</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.036216019567568</v>
+        <v>1.796528583553603</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.910173248163592</v>
+        <v>0.7329132417773565</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.542787179068926</v>
+        <v>4.331344741131961</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539109</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.993976469328406</v>
+        <v>3.888890035223181</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.007202513601491</v>
+        <v>-5.34370501837334</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.990739039574063</v>
+        <v>1.751051603560098</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8032477002857407</v>
+        <v>0.6259876938995051</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.475925089499851</v>
+        <v>4.264482651562885</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983739</v>
+        <v>3.689962785983734</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.995405271471641</v>
+        <v>3.890318837366415</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.15222107210874</v>
+        <v>-5.488723576880589</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.934160418314397</v>
+        <v>1.694472982300433</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6582291417784921</v>
+        <v>0.4809691353922566</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.390342756538736</v>
+        <v>4.178900318601769</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71187261496975</v>
+        <v>3.711872614969745</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.095336510729394</v>
+        <v>3.990250076624168</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.270562837893458</v>
+        <v>-5.607065342665306</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.986754951258263</v>
+        <v>1.747067515244298</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6689151803413822</v>
+        <v>0.4916551739551467</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.496685618934223</v>
+        <v>4.285243180997257</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.71489923707354</v>
+        <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.093122207855332</v>
+        <v>3.988035773750107</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.321973260214166</v>
+        <v>-5.658475764986014</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.963976479455919</v>
+        <v>1.724289043441954</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6689151803413822</v>
+        <v>0.4916551739551467</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.494471316060162</v>
+        <v>4.283028878123195</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720067</v>
+        <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.093025335929622</v>
+        <v>3.987938901824396</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.401392711421917</v>
+        <v>-5.737895216193766</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.932111827047108</v>
+        <v>1.692424391033143</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6689151803413822</v>
+        <v>0.4916551739551467</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.494374444134452</v>
+        <v>4.282932006197485</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581135</v>
+        <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.093019229487665</v>
+        <v>3.98793279538244</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.496855709339135</v>
+        <v>-5.833358214110984</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.893920521438264</v>
+        <v>1.654233085424299</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6689151803413822</v>
+        <v>0.4916551739551467</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.494368337692495</v>
+        <v>4.282925899755528</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500737</v>
+        <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.091115626050276</v>
+        <v>3.98602919194505</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.536875707382919</v>
+        <v>-5.873378212154767</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.876008918783361</v>
+        <v>1.636321482769396</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6288951822975983</v>
+        <v>0.4516351759113629</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.468452735428835</v>
+        <v>4.257010297491869</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636272</v>
+        <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.096849443798003</v>
+        <v>3.991763009692777</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.592244869515112</v>
+        <v>-5.928747374286961</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.85959507167821</v>
+        <v>1.619907635664245</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6288951822975983</v>
+        <v>0.4516351759113629</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.474186553176562</v>
+        <v>4.262744115239595</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396015</v>
+        <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.096387807140935</v>
+        <v>3.991301373035709</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.63768264934594</v>
+        <v>-5.974185154117788</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.840958323088812</v>
+        <v>1.601270887074846</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5860501916194387</v>
+        <v>0.4087901852332032</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.448017922112599</v>
+        <v>4.236575484175631</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396424</v>
+        <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.116262199991255</v>
+        <v>4.011175765886028</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.554457192498275</v>
+        <v>-5.890959697270124</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.894122898678197</v>
+        <v>1.654435462664231</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5860501916194387</v>
+        <v>0.4087901852332032</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.467892314962918</v>
+        <v>4.25644987702595</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299178</v>
+        <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.099962900515982</v>
+        <v>3.994876466410756</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.378166967892968</v>
+        <v>-5.714669472664816</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.948339689045048</v>
+        <v>1.708652253031082</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5860501916194387</v>
+        <v>0.4087901852332032</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.451593015487646</v>
+        <v>4.240150577550678</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590409</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.102393849980028</v>
+        <v>3.997307415874801</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.194955304759873</v>
+        <v>-5.531457809531721</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.024055303762331</v>
+        <v>1.784367867748366</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5860501916194387</v>
+        <v>0.4087901852332032</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.454023964951691</v>
+        <v>4.242581527014724</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146289</v>
+        <v>3.776866743146283</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.068185035827917</v>
+        <v>3.963098601722691</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.123233857746022</v>
+        <v>-5.45973636251787</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.018535068415761</v>
+        <v>1.778847632401795</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6577716386332894</v>
+        <v>0.4805116322470538</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.462848019007891</v>
+        <v>4.251405581070923</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.835466234967791</v>
+        <v>3.410463535269516</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.200626506124215</v>
+        <v>3.910014347643862</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.123233857746022</v>
+        <v>-5.259012820377008</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.018535068415761</v>
+        <v>1.806052795179312</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6577716386332894</v>
+        <v>0.4805116322470538</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.193690303110583</v>
+        <v>4.198321326992095</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240827.xlsx
+++ b/tame_output/ON/bt/strategyON_20240827.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>89.9%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>-49.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.5%</t>
+          <t>423.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-687.5%</t>
+          <t>-690.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-195.6%</t>
+          <t>-186.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-964.3%</t>
+          <t>-281.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-175.9%</t>
+          <t>-174.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-14.6%</t>
         </is>
       </c>
     </row>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382325</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.530782948247117</v>
+        <v>-9.292744275316419</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.6339254134978174</v>
+        <v>-0.5387099443255381</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.672714665325319</v>
+        <v>-1.611510313665351</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.175115390919586</v>
+        <v>2.211838001915567</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.406204291909525</v>
+        <v>-9.168165618978827</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5829548064067214</v>
+        <v>-0.4877393372344425</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.672714665325319</v>
+        <v>-1.611510313665351</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.176254535475645</v>
+        <v>2.212977146471625</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.459099579953811</v>
+        <v>-9.221060907023114</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.6014791474623284</v>
+        <v>-0.5062636782900496</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.667759319236873</v>
+        <v>-1.606554967576905</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.18186151729082</v>
+        <v>2.218584128286801</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.38696640466593</v>
+        <v>-9.148927731735233</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5668921731085397</v>
+        <v>-0.4716767039362608</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.667759319236873</v>
+        <v>-1.606554967576905</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.187595221529457</v>
+        <v>2.224317832525437</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.315600012056283</v>
+        <v>-9.077561339125586</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.5480828784585459</v>
+        <v>-0.452867409286267</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.596392926627225</v>
+        <v>-1.535188574967257</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.22067779470138</v>
+        <v>2.257400405697361</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.222140978071058</v>
+        <v>-8.984102305140361</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5205827461773636</v>
+        <v>-0.4253672770050847</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.596392926627225</v>
+        <v>-1.535188574967257</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.210794313388472</v>
+        <v>2.247516924384453</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.211487796517627</v>
+        <v>-8.97344912358693</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.5181560340553646</v>
+        <v>-0.4229405648830857</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.596392926627225</v>
+        <v>-1.535188574967257</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.208959752889099</v>
+        <v>2.24568236388508</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.113580757841136</v>
+        <v>-8.875542084910439</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.4792935335582293</v>
+        <v>-0.3840780643859505</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.528407176766668</v>
+        <v>-1.467202825106701</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.249450887831972</v>
+        <v>2.286173498827953</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.089627216865178</v>
+        <v>-8.851588543934481</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.4690436110223524</v>
+        <v>-0.3738281418500735</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.504453635790711</v>
+        <v>-1.443249284130743</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.26449151856304</v>
+        <v>2.301214129559021</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.825567278542382</v>
+        <v>-8.587528605611684</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.3766799518549862</v>
+        <v>-0.2814644826827069</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.240393697467915</v>
+        <v>-1.179189345807947</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.409667165394966</v>
+        <v>2.446389776390946</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.118487655037544</v>
+        <v>-7.880448982106846</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.09663513611335173</v>
+        <v>-0.001419666941072428</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.240393697467915</v>
+        <v>-1.179189345807947</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.406880131734665</v>
+        <v>2.443602742730645</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.078303356671354</v>
+        <v>-7.840264683740656</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.08021779287903419</v>
+        <v>0.01499767629324511</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.200209399101724</v>
+        <v>-1.139005047441756</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.431334334642221</v>
+        <v>2.468056945638201</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.914903485731991</v>
+        <v>-7.676864812801293</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.01549102328253227</v>
+        <v>0.07972444588974703</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.036809528162361</v>
+        <v>-0.9756051765023934</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.528741078426595</v>
+        <v>2.565463689422576</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.681422263502393</v>
+        <v>-7.443383590571695</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.08582589444715927</v>
+        <v>0.1810413636194386</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8033283059327627</v>
+        <v>-0.7421239542727949</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.676754240602206</v>
+        <v>2.713476851598187</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.531755872494878</v>
+        <v>-7.293717199564179</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.1428002405372064</v>
+        <v>0.2380157097094857</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7104248146902268</v>
+        <v>-0.6492204630302589</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.729604125034769</v>
+        <v>2.76632673603075</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.399480398863991</v>
+        <v>-7.161441725933293</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.09697121599671554</v>
+        <v>0.1921866851689948</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5781493410593401</v>
+        <v>-0.5169449893993723</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.710230195220455</v>
+        <v>2.746952806216436</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.243742066304249</v>
+        <v>-7.005703393373551</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1620816097082489</v>
+        <v>0.2572970788805282</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4224110084995986</v>
+        <v>-0.3612066568396307</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.806488255443937</v>
+        <v>2.843210866439918</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.15877739957493</v>
+        <v>-6.920738726644231</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2089738176236353</v>
+        <v>0.3041892867959151</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.337446341770279</v>
+        <v>-0.2762419901103111</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.870373396705188</v>
+        <v>2.907096007701168</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.264367389348035</v>
+        <v>-7.026328716417336</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.03876189211517467</v>
+        <v>0.1339773612874544</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4430363315433833</v>
+        <v>-0.3818319798834155</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.679043473242106</v>
+        <v>2.715766084238087</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.196132804722607</v>
+        <v>-6.958094131791908</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1146000678424324</v>
+        <v>0.2098155370147117</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4246210086708473</v>
+        <v>-0.3634166570108795</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.738637008842714</v>
+        <v>2.775359619838695</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.873530691357055</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.048192763315008</v>
+        <v>-6.810154090384309</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.05389716171730452</v>
+        <v>0.1491126308895838</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.4043000927622898</v>
+        <v>-0.3430957411023219</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.630950635699681</v>
+        <v>2.667673246695662</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.864816705103577</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.995223241061019</v>
+        <v>-6.75718456813032</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.06637098436542166</v>
+        <v>0.1615864535377014</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3513305705083009</v>
+        <v>-0.2901262188483331</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.654018362798596</v>
+        <v>2.690740973794577</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.857856093008484</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.829435045100729</v>
+        <v>-6.591396372170029</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.1257256506544446</v>
+        <v>0.2209411198267244</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3513305705083009</v>
+        <v>-0.2901262188483331</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.647057750703503</v>
+        <v>2.683780361699484</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.872318447389627</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.79607183862196</v>
+        <v>-6.558033165691261</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1535332876270954</v>
+        <v>0.2487487567993751</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3513305705083009</v>
+        <v>-0.2901262188483331</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.661520105084646</v>
+        <v>2.698242716080627</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.866850567848822</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.687812701499438</v>
+        <v>-6.449774028568739</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1913690629352991</v>
+        <v>0.2865845321075788</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3513305705083009</v>
+        <v>-0.2901262188483331</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.656052225543841</v>
+        <v>2.692774836539822</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.864348661859399</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.564521566682307</v>
+        <v>-6.326482893751608</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2381836108727282</v>
+        <v>0.333399080045008</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2280394356911704</v>
+        <v>-0.1668350840312026</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.727525000444697</v>
+        <v>2.764247611440677</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.872049640096724</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.511824699551016</v>
+        <v>-6.273786026620317</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2669633359625698</v>
+        <v>0.3621788051348496</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1753425685598792</v>
+        <v>-0.1141382168999114</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.766844098960796</v>
+        <v>2.803566709956777</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.867830348443774</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.268059257567572</v>
+        <v>-6.030020584636873</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3602502211029983</v>
+        <v>0.4554656902752781</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1753425685598792</v>
+        <v>-0.1141382168999114</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.762624807307847</v>
+        <v>2.799347418303828</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.86995466236379</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.1782835851911</v>
+        <v>-5.9402449122604</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3982848039736031</v>
+        <v>0.4935002731458829</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1137431236455692</v>
+        <v>-0.05253877198560136</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.801708788176449</v>
+        <v>2.83843139917243</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.862696737347493</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.928433191242025</v>
+        <v>-5.690394518311326</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4909670365369352</v>
+        <v>0.5861825057092149</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1137431236455692</v>
+        <v>-0.05253877198560136</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.794450863160151</v>
+        <v>2.831173474156132</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.866295860868141</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.752541098774593</v>
+        <v>-5.514502425843894</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5649229970445568</v>
+        <v>0.6601384662168366</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1137431236455692</v>
+        <v>-0.05253877198560136</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.7980499866808</v>
+        <v>2.834772597676781</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.879623366922695</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.581094635752129</v>
+        <v>-5.34305596282143</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6468290883080958</v>
+        <v>0.7420445574803756</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.05770333937689393</v>
+        <v>0.1189076910368618</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.914245370548831</v>
+        <v>2.950967981544812</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.878643844538992</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.501072348643008</v>
+        <v>-5.263033675712309</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6778584807680414</v>
+        <v>0.7730739499403207</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1377256264860149</v>
+        <v>0.1989299781459827</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.961279220430601</v>
+        <v>2.998001831426582</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.883338645593309</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.437436606409074</v>
+        <v>-5.199397933478375</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7080075787159323</v>
+        <v>0.8032230478882121</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2013613687199494</v>
+        <v>0.2625657203799173</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.004155466825279</v>
+        <v>3.04087807782126</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.864532904377105</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.343739288192679</v>
+        <v>-5.10570061526198</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7266807647862858</v>
+        <v>0.8218962339585656</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2013613687199494</v>
+        <v>0.2625657203799173</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.985349725609075</v>
+        <v>3.022072336605055</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.866275981001982</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.354241911257968</v>
+        <v>-5.116203238327269</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7242227921850479</v>
+        <v>0.8194382613573277</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1908587456546605</v>
+        <v>0.2520630973146284</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.980791228394779</v>
+        <v>3.01751383939076</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.870205294836802</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.281999343086773</v>
+        <v>-5.043960670156074</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.757049133288346</v>
+        <v>0.8522646024606257</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1908587456546605</v>
+        <v>0.2520630973146284</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.984720542229599</v>
+        <v>3.02144315322558</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.870883878754142</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.264285656208908</v>
+        <v>-5.026246983278209</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.764813191956832</v>
+        <v>0.8600286611291117</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1940400745515773</v>
+        <v>0.2552444262115452</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.987307923485089</v>
+        <v>3.02403053448107</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.867881949974136</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.155480770729181</v>
+        <v>-4.917442097798482</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8053332173687164</v>
+        <v>0.900548686540996</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1940400745515773</v>
+        <v>0.2552444262115452</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.984305994705083</v>
+        <v>3.021028605701063</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.86946098698475</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.93545997269217</v>
+        <v>-4.697421299761471</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8949205735941348</v>
+        <v>0.9901360427664143</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3352599196195576</v>
+        <v>0.3964642712795254</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.070616938756485</v>
+        <v>3.107339549752465</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.885355169786573</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.802592283628893</v>
+        <v>-4.564553610698193</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9639618320212691</v>
+        <v>1.059177301193549</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3352599196195576</v>
+        <v>0.3964642712795254</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.086511121558308</v>
+        <v>3.123233732554289</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.886501014226875</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.682419200264394</v>
+        <v>-4.444380527333695</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.01317690980737</v>
+        <v>1.10839237897965</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4554330029840565</v>
+        <v>0.5166373546440244</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.159760816017309</v>
+        <v>3.19648342701329</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.896589116788315</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.547165838934417</v>
+        <v>-4.309127166003718</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.077366356900801</v>
+        <v>1.172581826073081</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5906863643140337</v>
+        <v>0.6518907159740015</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.251000935376736</v>
+        <v>3.287723546372716</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.882626608189741</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.607040666292109</v>
+        <v>-4.36900199336141</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.03945391735915</v>
+        <v>1.13466938653143</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5308115369563415</v>
+        <v>0.5920158886163094</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.201113530363546</v>
+        <v>3.237836141359527</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.897915777423949</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.487220435381272</v>
+        <v>-4.249181762450573</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.102671178957693</v>
+        <v>1.197886648129973</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5308115369563415</v>
+        <v>0.5920158886163094</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.216402699597755</v>
+        <v>3.253125310593735</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.805559976746391</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.489690141843078</v>
+        <v>-4.251651468912379</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.009327495695413</v>
+        <v>1.104542964867692</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5283418304945353</v>
+        <v>0.5895461821545032</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.122565075043112</v>
+        <v>3.159287686039093</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.724821838231692</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.558060328167088</v>
+        <v>-4.320021655236389</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9012412826511098</v>
+        <v>0.9964567518233896</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5376175295307503</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.047392355950143</v>
+        <v>3.084114966946124</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.715258546863584</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.571848381014135</v>
+        <v>-4.333809708083436</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8861627701441823</v>
+        <v>0.9813782393164621</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5376175295307503</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.037829064582034</v>
+        <v>3.074551675578015</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.852289383555786</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.627368456906725</v>
+        <v>-4.389329783976025</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.000985576479349</v>
+        <v>1.096201045651629</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5376175295307503</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.174859901274237</v>
+        <v>3.211582512270217</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.856856615547574</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.451894197114255</v>
+        <v>-4.213855524183556</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.075742512388125</v>
+        <v>1.170957981560404</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5376175295307503</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.179427133266024</v>
+        <v>3.216149744262005</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.832598644308781</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.443969822529341</v>
+        <v>-4.205931149598642</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.054654290983297</v>
+        <v>1.149869760155577</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5376175295307503</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.155169162027232</v>
+        <v>3.191891773023212</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.761136957710231</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.437691619959492</v>
+        <v>-4.199652947028793</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9857038854126867</v>
+        <v>1.080919354584966</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5438957321005993</v>
+        <v>0.6051000837605671</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.08747439697059</v>
+        <v>3.124197007966571</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.771309344142363</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.377839000755769</v>
+        <v>-4.139800327825069</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.019817319526308</v>
+        <v>1.115032788698588</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5438957321005993</v>
+        <v>0.6051000837605671</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.097646783402723</v>
+        <v>3.134369394398703</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.766255614716223</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.291595537729391</v>
+        <v>-4.053556864798692</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.04926097531072</v>
+        <v>1.144476444482999</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5438957321005993</v>
+        <v>0.6051000837605671</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.092593053976583</v>
+        <v>3.129315664972564</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.758031390160749</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.336902357128371</v>
+        <v>-4.098863684197672</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.022914022995653</v>
+        <v>1.118129492167933</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5030855690913685</v>
+        <v>0.5642899207513363</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.05988273161557</v>
+        <v>3.096605342611551</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.75858326319385</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.365935461830672</v>
+        <v>-4.127896788899973</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.011852654147835</v>
+        <v>1.107068123320114</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5030855690913685</v>
+        <v>0.5642899207513363</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.060434604648672</v>
+        <v>3.097157215644653</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.687855955085216</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.273124980379812</v>
+        <v>-4.035086307449113</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.978249538619544</v>
+        <v>1.073465007791824</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5958960505422278</v>
+        <v>0.6571004022021957</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.045393585410553</v>
+        <v>3.082116196406534</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.689729431009817</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.31751444970924</v>
+        <v>-4.079475776778541</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9623672268123737</v>
+        <v>1.057582695984653</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5515065812128002</v>
+        <v>0.612710932872768</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.020633379737498</v>
+        <v>3.057355990733478</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.68480513952154</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.434056054814582</v>
+        <v>-4.196017381883883</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9108262932819597</v>
+        <v>1.006041762454239</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4349649761074574</v>
+        <v>0.4961693277674253</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.945784125186015</v>
+        <v>2.982506736181995</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.473980149397154</v>
+        <v>-4.235941476466455</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9003479512795982</v>
+        <v>0.995563420451878</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4349649761074574</v>
+        <v>0.4961693277674253</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.951275421016682</v>
+        <v>2.987998032012662</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.501760547298507</v>
+        <v>-4.263721874367808</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9007329938875963</v>
+        <v>0.9959484630598758</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4071845782061043</v>
+        <v>0.4683889298660722</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.946104384044409</v>
+        <v>2.98282699504039</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.620141220028645</v>
+        <v>-4.382102547097946</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6917364447961942</v>
+        <v>0.7869519139684737</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3399667260551281</v>
+        <v>0.401171077715096</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.744129392754477</v>
+        <v>2.780852003750458</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.728755298471977</v>
+        <v>-4.490716625541277</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7684404741380673</v>
+        <v>0.863655943310347</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3399667260551281</v>
+        <v>0.401171077715096</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.864279053473682</v>
+        <v>2.901001664469663</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.693346260223834</v>
+        <v>-4.455307587293134</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7971171155396475</v>
+        <v>0.892332584711927</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3399667260551281</v>
+        <v>0.401171077715096</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.878792079576005</v>
+        <v>2.915514690571986</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.654962597665683</v>
+        <v>-4.416923924734983</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8098900219052765</v>
+        <v>0.9051054910775562</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3783503886132793</v>
+        <v>0.4395547402732472</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.899241718453265</v>
+        <v>2.935964329449245</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.477846267630516</v>
+        <v>-4.239807594699817</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8774655827646449</v>
+        <v>0.9726810519369247</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3783503886132793</v>
+        <v>0.4395547402732472</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.895970747298567</v>
+        <v>2.932693358294547</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.522938512464062</v>
+        <v>-4.284899839533363</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8601120765931398</v>
+        <v>0.9553275457654193</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3164543454438895</v>
+        <v>0.3776586971038574</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.859516513158846</v>
+        <v>2.896239124154826</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.343563091225294</v>
+        <v>-4.105524418294595</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9256492203950613</v>
+        <v>1.020864689567341</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4732311036146082</v>
+        <v>0.534435455274576</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.947369543367691</v>
+        <v>2.984092154363672</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.388577304745901</v>
+        <v>-4.150538631815202</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8884509903184084</v>
+        <v>0.9836664594906879</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4428822083000036</v>
+        <v>0.5040865599599714</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.909967661510518</v>
+        <v>2.946690272506499</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.655581815018336</v>
+        <v>-4.417543142087637</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7873407485483801</v>
+        <v>0.8825562177206596</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.248519170257055</v>
+        <v>0.3097235219170228</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.799041401023695</v>
+        <v>2.835764012019676</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.756779596455509</v>
+        <v>-4.51874092352481</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7460655578700124</v>
+        <v>0.8412810270422919</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1801103567117358</v>
+        <v>0.2413147083717037</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.757200034793005</v>
+        <v>2.793922645788986</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.750268629841196</v>
+        <v>-4.512229956910497</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7462699060700542</v>
+        <v>0.8414853752423337</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1801103567117358</v>
+        <v>0.2413147083717037</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.754799996347322</v>
+        <v>2.791522607343302</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.731230502133899</v>
+        <v>-4.4931918292032</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7504098763612179</v>
+        <v>0.8456253455334977</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1219267453805413</v>
+        <v>0.1831310970405091</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.71641454875685</v>
+        <v>2.753137159752831</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.783746304408719</v>
+        <v>-4.54570763147802</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8486979570854802</v>
+        <v>0.9439134262577598</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1219267453805413</v>
+        <v>0.1831310970405091</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.83570895039104</v>
+        <v>2.872431561387021</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.797613065742637</v>
+        <v>-4.559574392811938</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8439845815380465</v>
+        <v>0.9392000507103262</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.08406882864671833</v>
+        <v>0.1452731803066862</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.81382752933688</v>
+        <v>2.850550140332861</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.752808894202707</v>
+        <v>-4.599664694570697</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8679147805509444</v>
+        <v>0.9291724604037488</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.08406882864671833</v>
+        <v>0.1452731803066862</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.819836059733806</v>
+        <v>2.856558670729787</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.605065923967705</v>
+        <v>-4.451921724335694</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8249621899221449</v>
+        <v>0.8862198697749493</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2518761858816015</v>
+        <v>0.3130805375415693</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.818470695351935</v>
+        <v>2.855193306347916</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.688887145242403</v>
+        <v>-4.535742945610393</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7942273229437466</v>
+        <v>0.8554850027965508</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2518761858816015</v>
+        <v>0.3130805375415693</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.821264316883416</v>
+        <v>2.857986927879397</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.682734439189619</v>
+        <v>-4.529590239557608</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7973507537565188</v>
+        <v>0.8586084336093229</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2580288919343858</v>
+        <v>0.3192332435943536</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.825618288906745</v>
+        <v>2.862340899902726</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.699543737340121</v>
+        <v>-4.54639953770811</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7897075112364282</v>
+        <v>0.8509651910892324</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2412195937838841</v>
+        <v>0.302423945443852</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.814613186756555</v>
+        <v>2.851335797752535</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.637245738563998</v>
+        <v>-4.484101538931988</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8809622645436979</v>
+        <v>0.9422199443965023</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2865138580583262</v>
+        <v>0.347718209718294</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.908125299118041</v>
+        <v>2.944847910114021</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.435455540898841</v>
+        <v>-4.28231134126683</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7639703453238882</v>
+        <v>0.8252280251766924</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4845320502274806</v>
+        <v>0.5457364018874484</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.82922821613366</v>
+        <v>2.865950827129641</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.486342253585035</v>
+        <v>-4.333198053953025</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8139058925715856</v>
+        <v>0.8751635724243898</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.433645337541286</v>
+        <v>0.4948496892012539</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.868986420844119</v>
+        <v>2.905709031840099</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.399731510935228</v>
+        <v>-4.246587311303218</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8631779257475518</v>
+        <v>0.9244356056003562</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5122710687464442</v>
+        <v>0.5734754204064122</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.930789595683257</v>
+        <v>2.967512206679238</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.459940808940513</v>
+        <v>-4.306796609308503</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8376301873701095</v>
+        <v>0.8988878672229139</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4520617707411597</v>
+        <v>0.5132661224011277</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.893199997704758</v>
+        <v>2.929922608700739</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.383518762508587</v>
+        <v>-4.230374562876576</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8666906239828089</v>
+        <v>0.9279483038356131</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4520617707411597</v>
+        <v>0.5132661224011277</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.891691615744687</v>
+        <v>2.928414226740668</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.339145630870018</v>
+        <v>-4.186001431238007</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8843027440736726</v>
+        <v>0.9455604239264768</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4964349023797283</v>
+        <v>0.5576392540396963</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.918178362163264</v>
+        <v>2.954900973159245</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.361625981728903</v>
+        <v>-4.208481782096892</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8697043978687091</v>
+        <v>0.9309620777215133</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4964349023797283</v>
+        <v>0.5576392540396963</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.912572156301855</v>
+        <v>2.949294767297836</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.313970251167847</v>
+        <v>-4.160826051535836</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8951484471209361</v>
+        <v>0.9564061269737403</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.544090632940784</v>
+        <v>0.6052949846007519</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.947547351666293</v>
+        <v>2.984269962662274</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.213452092669092</v>
+        <v>-4.060307893037082</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9402480838951628</v>
+        <v>1.001505763747967</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6446087914395385</v>
+        <v>0.7058131430995065</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.01275062014027</v>
+        <v>3.049473231136251</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.19754676323674</v>
+        <v>-4.044402563604729</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.933364888143976</v>
+        <v>0.9946225679967804</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5654961307302997</v>
+        <v>0.6267004823902675</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.952037696190599</v>
+        <v>2.98876030718658</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.152708361628341</v>
+        <v>-3.999564161996331</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.955397951397964</v>
+        <v>1.016655631250768</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5700395636751692</v>
+        <v>0.631243915335137</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.958861458568149</v>
+        <v>2.99558406956413</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.172206817870349</v>
+        <v>-4.01906261823834</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9517595085322388</v>
+        <v>1.013017188385043</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5219549223952649</v>
+        <v>0.5831592740552327</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.934171613431285</v>
+        <v>2.970894224427266</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.128003980784449</v>
+        <v>-3.974859781152439</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9753202458944361</v>
+        <v>1.03657792574724</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5661577594811653</v>
+        <v>0.6273621111411332</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.966572918210662</v>
+        <v>3.003295529206643</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.135563646621495</v>
+        <v>-3.982419446989486</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9707063800288651</v>
+        <v>1.031964059881669</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6209611634909846</v>
+        <v>0.6821655151509525</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.997864961085801</v>
+        <v>3.034587572081782</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.977272229082223</v>
+        <v>-3.824128029450214</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.085270712227614</v>
+        <v>1.146528392080417</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6209611634909846</v>
+        <v>0.6821655151509525</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.049112726268841</v>
+        <v>3.085835337264822</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.769630225447747</v>
+        <v>-3.616486025815738</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.166768218275657</v>
+        <v>1.228025898128461</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8286031671254608</v>
+        <v>0.8898075187854286</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.17213863304378</v>
+        <v>3.208861244039761</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.718598132725219</v>
+        <v>-3.56545393309321</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.182129283602938</v>
+        <v>1.243386963455742</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8796352598479887</v>
+        <v>0.9408396115079566</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.197706116915567</v>
+        <v>3.234428727911547</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.653373951598013</v>
+        <v>-3.500229751966004</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.225406360146526</v>
+        <v>1.286664039999329</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9448594409751944</v>
+        <v>1.006063792635162</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.254028029684595</v>
+        <v>3.290750640680576</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.615946931526879</v>
+        <v>-3.46280273189487</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.236338140474259</v>
+        <v>1.297595820327063</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.950110979004376</v>
+        <v>1.011315330664344</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.253139924801384</v>
+        <v>3.289862535797365</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.636058587561588</v>
+        <v>-3.482914387929579</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.229550270391617</v>
+        <v>1.29080795024442</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9611383240017952</v>
+        <v>1.022342675661763</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.261013124131076</v>
+        <v>3.297735735127057</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.607645324461704</v>
+        <v>-3.454501124829695</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.401473346652781</v>
+        <v>1.462731026505584</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9021627612553664</v>
+        <v>0.9633671129153341</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.38618555750443</v>
+        <v>3.42290816850041</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.532863063436691</v>
+        <v>-3.379718863804682</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.551499160280603</v>
+        <v>1.612756840133406</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.976945022280379</v>
+        <v>1.038149373940347</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.551167823337254</v>
+        <v>3.587890434333235</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.506778979172883</v>
+        <v>-3.353634779540875</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.553640769999985</v>
+        <v>1.614898449852789</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.976945022280379</v>
+        <v>1.038149373940347</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.542875799351113</v>
+        <v>3.579598410347094</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.418901066063763</v>
+        <v>-3.265756866431754</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.586985130827413</v>
+        <v>1.648242810680216</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.09287066470373</v>
+        <v>1.154075016363698</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.610624380388904</v>
+        <v>3.647346991384884</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.410008604670479</v>
+        <v>-3.256864405038471</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.608096521111518</v>
+        <v>1.669354200964321</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.09287066470373</v>
+        <v>1.154075016363698</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.628178786115695</v>
+        <v>3.664901397111676</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.578484721640357</v>
+        <v>-3.425340522008348</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.532561121728151</v>
+        <v>1.593818801580954</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.06492282898715</v>
+        <v>1.126127180647117</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.603265132090331</v>
+        <v>3.639987743086311</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.132228529010917</v>
+        <v>-2.979084329378908</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.692333295967788</v>
+        <v>1.753590975820592</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9702041593175168</v>
+        <v>1.031408510977484</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.527703627476413</v>
+        <v>3.564426238472393</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.109507425327765</v>
+        <v>-2.956363225695756</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.692085759937954</v>
+        <v>1.753343439790757</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9702041593175168</v>
+        <v>1.031408510977484</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.518367649973317</v>
+        <v>3.555090260969298</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.238709238621807</v>
+        <v>-3.085565038989798</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.799311160471506</v>
+        <v>1.860568840324309</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8410023460234746</v>
+        <v>0.902206697683442</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.599752687848061</v>
+        <v>3.636475298844041</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.264583637095833</v>
+        <v>-3.111439437463824</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.826039223575542</v>
+        <v>1.887296903428346</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8859139547352157</v>
+        <v>0.9471183063951831</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.663777475568752</v>
+        <v>3.700500086564733</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.257528946880659</v>
+        <v>-3.104384747248651</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.825536455651157</v>
+        <v>1.88679413550396</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8929686449503895</v>
+        <v>0.9541729966103569</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.664685645687402</v>
+        <v>3.701408256683382</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.230577722554171</v>
+        <v>-3.077433522922163</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.846323099026493</v>
+        <v>1.907580778879297</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9078489909781087</v>
+        <v>0.9690533426380761</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.683620006948775</v>
+        <v>3.720342617944755</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.366530730610488</v>
+        <v>-3.213386530978479</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.976045027948927</v>
+        <v>2.037302707801731</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9078489909781087</v>
+        <v>0.9690533426380761</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.867723139093735</v>
+        <v>3.904445750089715</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.38893884841536</v>
+        <v>-3.235794648783351</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.959198475729971</v>
+        <v>2.020456155582774</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9078489909781087</v>
+        <v>0.9690533426380761</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.859839833996728</v>
+        <v>3.896562444992708</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.41716308399296</v>
+        <v>-3.264018884360951</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.949962781048568</v>
+        <v>2.011220460901372</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9258257434294173</v>
+        <v>0.9870300950893847</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.87267988501715</v>
+        <v>3.909402496013131</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.42660400988149</v>
+        <v>-3.273459810249481</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.002440128415004</v>
+        <v>2.063697808267807</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.048252860972809</v>
+        <v>1.109457212632776</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.002389873265033</v>
+        <v>4.039112484261013</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.478877617217131</v>
+        <v>-3.325733417585123</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.984421780026048</v>
+        <v>2.045679459878851</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9959792536371674</v>
+        <v>1.057183605297135</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.973916803408948</v>
+        <v>4.010639414404928</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.555207594818037</v>
+        <v>-3.402063395186028</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.952001601879461</v>
+        <v>2.013259281732264</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9959792536371674</v>
+        <v>1.057183605297135</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.972028616302723</v>
+        <v>4.008751227298704</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.757461315142391</v>
+        <v>-3.604317115510382</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.865920343352582</v>
+        <v>1.927178023205385</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7937255333128139</v>
+        <v>0.8549298849727813</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.845496613710974</v>
+        <v>3.882219224706954</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.919029740669646</v>
+        <v>-3.765885541037637</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.799726983351832</v>
+        <v>1.860984663204635</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6669426095149346</v>
+        <v>0.728146961174902</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.767860869642398</v>
+        <v>3.804583480638379</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.027330402539765</v>
+        <v>-3.874186202907756</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.769480125469703</v>
+        <v>1.830737805322506</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6669426095149346</v>
+        <v>0.728146961174902</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.780934276508317</v>
+        <v>3.817656887504298</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.120477873843132</v>
+        <v>-3.967333674211123</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.724226333731296</v>
+        <v>1.785484013584099</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5441133982324018</v>
+        <v>0.6053177498923692</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.699241946521737</v>
+        <v>3.735964557517718</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.148378660952605</v>
+        <v>-3.995234461320596</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.711590060014509</v>
+        <v>1.772847739867312</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.509516474089467</v>
+        <v>0.5707208257494344</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.677007833162978</v>
+        <v>3.713730444158959</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.270904763655499</v>
+        <v>-4.11776056402349</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.65934406291055</v>
+        <v>1.720601742763354</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3869903713865731</v>
+        <v>0.4481947230465405</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.600256615518441</v>
+        <v>3.636979226514421</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.501419259841088</v>
+        <v>-4.348275060209079</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.633844224026818</v>
+        <v>1.695101903879622</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1564758752009844</v>
+        <v>0.2176802268609518</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.528653877397591</v>
+        <v>3.565376488393572</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.850164345065531</v>
+        <v>-4.697020145433522</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.634657908938888</v>
+        <v>1.695915588791691</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.04772792128208658</v>
+        <v>0.108932272942054</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.6037168240481</v>
+        <v>3.64043943504408</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-5.004150762841672</v>
+        <v>-4.851006563209663</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.642043610974071</v>
+        <v>1.703301290826875</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.04772792128208658</v>
+        <v>0.108932272942054</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.67269709319374</v>
+        <v>3.70941970418972</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.953628859014006</v>
+        <v>-4.800484659381997</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.648303574625259</v>
+        <v>1.709561254478062</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.04772792128208658</v>
+        <v>0.108932272942054</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.658748295313861</v>
+        <v>3.695470906309841</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.20610401302173</v>
+        <v>-5.052959813389721</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.559184002077583</v>
+        <v>1.620441681930386</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.04772792128208658</v>
+        <v>0.108932272942054</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.670618784369275</v>
+        <v>3.707341395365255</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.498999769501142</v>
+        <v>-5.345855569869133</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.443236234004762</v>
+        <v>1.504493913857565</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.04772792128208658</v>
+        <v>0.108932272942054</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.671829318888218</v>
+        <v>3.708551929884198</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.68566389763595</v>
+        <v>-5.532519698003941</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.37269232497816</v>
+        <v>1.433950004830963</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.02098895045752669</v>
+        <v>0.08219330211749409</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.659907678620804</v>
+        <v>3.696630289616784</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.831684584549913</v>
+        <v>-5.678540384917904</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.309361902948765</v>
+        <v>1.370619582801568</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.01190585866366972</v>
+        <v>0.07311021032363713</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.649535676280679</v>
+        <v>3.686258287276659</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.923398593659497</v>
+        <v>-5.770254394027489</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.434880356003975</v>
+        <v>1.496138035856778</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.01190585866366972</v>
+        <v>0.07311021032363713</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.811739732979723</v>
+        <v>3.848462343975704</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.955050252719467</v>
+        <v>-5.801906053087459</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.417066330343801</v>
+        <v>1.478324010196604</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.006737401419229516</v>
+        <v>0.06794175307919692</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.803485296596873</v>
+        <v>3.840207907592853</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.03698507098835</v>
+        <v>-5.883840871356342</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.394521820604739</v>
+        <v>1.455779500457542</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.003197344167850669</v>
+        <v>0.05800700749211674</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.807753866813116</v>
+        <v>3.844476477809097</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.138961193236757</v>
+        <v>-5.985816993604749</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.362657010161278</v>
+        <v>1.423914690014082</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1051734664162582</v>
+        <v>-0.04396911475629084</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.755493831919974</v>
+        <v>3.792216442915954</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.028954909759536</v>
+        <v>-5.875810710127528</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.398812410796342</v>
+        <v>1.460070090649146</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.08196889449898304</v>
+        <v>-0.02076454283901563</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.761569462314514</v>
+        <v>3.798292073310495</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.88589533401861</v>
+        <v>-5.732751134386602</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.460286251814687</v>
+        <v>1.52154393166749</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.07395546790900376</v>
+        <v>-0.01275111624903635</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.770627528990476</v>
+        <v>3.807350139986457</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.584448608546772</v>
+        <v>-5.431304408914764</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.588125824885958</v>
+        <v>1.649383504738761</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2274912575628335</v>
+        <v>0.2886956092228009</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.958756447156115</v>
+        <v>3.995479058152095</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.609038852781956</v>
+        <v>-5.455894653149948</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.579260904944595</v>
+        <v>1.640518584797398</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2274912575628335</v>
+        <v>0.2886956092228009</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.959727624908825</v>
+        <v>3.996450235904805</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.718989340645655</v>
+        <v>3.82407577475088</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.558000476775436</v>
+        <v>-5.404856277143428</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.495432725621733</v>
+        <v>1.661776839579762</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2274912575628335</v>
+        <v>0.2886956092228009</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.855484095183355</v>
+        <v>3.997293140284561</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.7380274395198</v>
+        <v>3.843113873625026</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.516861181908805</v>
+        <v>-5.363716982276797</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.530926542442531</v>
+        <v>1.69727065640056</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2686305524294643</v>
+        <v>0.3298349040894317</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.899205770977479</v>
+        <v>4.041014816078685</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.554211435643735</v>
+        <v>3.65929786974896</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.420226269890165</v>
+        <v>-5.267082070258157</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.385764503373922</v>
+        <v>1.55210861733195</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3652654644481043</v>
+        <v>0.4264698161080717</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.773370714312598</v>
+        <v>3.915179759413804</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.557713479717699</v>
+        <v>3.662799913822925</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.550807004421007</v>
+        <v>-5.397662804788999</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.337034253635549</v>
+        <v>1.503378367593577</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2346847299172617</v>
+        <v>0.2958890815772292</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.698524317668056</v>
+        <v>3.840333362769262</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833454</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.542140298793782</v>
+        <v>3.647226732899007</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.386310670230046</v>
+        <v>-5.233166470598038</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.387259606388016</v>
+        <v>1.553603720346045</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3991810641082236</v>
+        <v>0.460385415768191</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.781648937258716</v>
+        <v>3.923457982359922</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.541328009230211</v>
+        <v>3.646414443335437</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.413680602914478</v>
+        <v>-5.26053640328247</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.375499343750673</v>
+        <v>1.541843457708702</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3991810641082236</v>
+        <v>0.460385415768191</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.780836647695146</v>
+        <v>3.922645692796352</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.551196788355284</v>
+        <v>3.656283222460509</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.424065797804367</v>
+        <v>-5.270921598172359</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.38121404491979</v>
+        <v>1.547558158877818</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3887958692183343</v>
+        <v>0.4500002208783017</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.784474309886285</v>
+        <v>3.926283354987491</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.622033794131709</v>
+        <v>3.727120228236934</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.442653956526592</v>
+        <v>-5.289509756894584</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.444615787207325</v>
+        <v>1.610959901165354</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.370207710496109</v>
+        <v>0.4314120621560764</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.844158420429375</v>
+        <v>3.985967465530581</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.618902804950007</v>
+        <v>3.723989239055233</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.442952503222628</v>
+        <v>-5.28980830359062</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.441365379347209</v>
+        <v>1.607709493305238</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.369909163800073</v>
+        <v>0.4311135154600405</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.840848303230052</v>
+        <v>3.982657348331258</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.623433699889399</v>
+        <v>3.728520133994624</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.3421293695322</v>
+        <v>-5.188985169900192</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.486225527762771</v>
+        <v>1.6525696417208</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3823733792844269</v>
+        <v>0.4435777309443943</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.852857727460055</v>
+        <v>3.994666772561261</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.623562953367942</v>
+        <v>3.728649387473168</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.151348008779793</v>
+        <v>-4.998203809147785</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.562667325542277</v>
+        <v>1.729011439500306</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5731547400368342</v>
+        <v>0.6343590916968016</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.967455797390043</v>
+        <v>4.109264842491249</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.603399799105539</v>
+        <v>3.708486233210764</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.132831154737973</v>
+        <v>-4.979686955105965</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.549910912896602</v>
+        <v>1.716255026854631</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5860848694620424</v>
+        <v>0.6472892211220098</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.955050720782764</v>
+        <v>4.096859765883971</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.638366735717597</v>
+        <v>3.743453169822823</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.077500566836211</v>
+        <v>-4.924356367204203</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.607010084669366</v>
+        <v>1.773354198627394</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6414154573638046</v>
+        <v>0.702619809023772</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.02321601013588</v>
+        <v>4.165025055237086</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.632053303619035</v>
+        <v>3.73713973772426</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.065446439923248</v>
+        <v>-4.91230224029124</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.605518303335988</v>
+        <v>1.771862417294017</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6534695842767674</v>
+        <v>0.7146739359367348</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.024135054185096</v>
+        <v>4.165944099286301</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.633933933803171</v>
+        <v>3.739020367908396</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.106601559491469</v>
+        <v>-4.953457359859461</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.590936885692836</v>
+        <v>1.757280999650865</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6123144647085464</v>
+        <v>0.6735188163685139</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.001322612628298</v>
+        <v>4.143131657729505</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.646784959681053</v>
+        <v>3.751871393786279</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.003720969962876</v>
+        <v>-4.850576770330868</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.644940147382155</v>
+        <v>1.811284261340184</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7151950542371394</v>
+        <v>0.7763994058971068</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.075901992223337</v>
+        <v>4.217711037324543</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.666987629854647</v>
+        <v>3.772074063959873</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.235321363132377</v>
+        <v>-5.082177163500369</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.572502660287949</v>
+        <v>1.738846774245978</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7151950542371394</v>
+        <v>0.7763994058971068</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.096104662396931</v>
+        <v>4.237913707498137</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.666987629854647</v>
+        <v>3.772074063959873</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.253393871423988</v>
+        <v>-5.10024967179198</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.565273656971305</v>
+        <v>1.731617770929334</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7151950542371394</v>
+        <v>0.7763994058971068</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.096104662396931</v>
+        <v>4.237913707498137</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.627239543448114</v>
+        <v>3.73232597755334</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.428500704000433</v>
+        <v>-5.275356504368425</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.455482837534193</v>
+        <v>1.621826951492222</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7151950542371394</v>
+        <v>0.7763994058971068</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.056356575990398</v>
+        <v>4.198165621091603</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.634262162445054</v>
+        <v>3.73934859655028</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.397214683459977</v>
+        <v>-5.244070483827969</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.475019864747316</v>
+        <v>1.641363978705344</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7464810747775947</v>
+        <v>0.8076854264375621</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.082150807311611</v>
+        <v>4.223959852412817</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.733433162017958</v>
+        <v>3.838519596123184</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.244189291346693</v>
+        <v>-5.091045091714685</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.635401021165534</v>
+        <v>1.801745135123562</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8995064668908789</v>
+        <v>0.9607108185508463</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.273137042152486</v>
+        <v>4.414946087253692</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073879</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.920899386926251</v>
+        <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.272496605219963</v>
+        <v>-5.119352405587955</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.811544320524518</v>
+        <v>1.977888434482546</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8995064668908789</v>
+        <v>0.9607108185508463</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.460603267060778</v>
+        <v>4.602412312161984</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.890302338280333</v>
+        <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.439089830333486</v>
+        <v>-5.285945630701478</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.714309981833192</v>
+        <v>1.88065409579122</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7329132417773565</v>
+        <v>0.7941175934373239</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.330050283346748</v>
+        <v>4.471859328447953</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568379</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.893978740942051</v>
+        <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.266025450951186</v>
+        <v>-5.112881251319178</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.787212136247829</v>
+        <v>1.953556250205858</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7329132417773565</v>
+        <v>0.7941175934373239</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.333726686008466</v>
+        <v>4.47553573110967</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.891596796065546</v>
+        <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.236779470495489</v>
+        <v>-5.083635270863481</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.796528583553603</v>
+        <v>1.962872697511632</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7329132417773565</v>
+        <v>0.7941175934373239</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.331344741131961</v>
+        <v>4.473153786233166</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.888890035223181</v>
+        <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.34370501837334</v>
+        <v>-5.190560818741332</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.751051603560098</v>
+        <v>1.917395717518126</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6259876938995051</v>
+        <v>0.6871920455594726</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.264482651562885</v>
+        <v>4.40629169666409</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689962785983734</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.890318837366415</v>
+        <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.488723576880589</v>
+        <v>-5.335579377248581</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.694472982300433</v>
+        <v>1.860817096258461</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.4809691353922566</v>
+        <v>0.542173487052224</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.178900318601769</v>
+        <v>4.320709363702975</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711872614969745</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.990250076624168</v>
+        <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.607065342665306</v>
+        <v>-5.453921143033298</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.747067515244298</v>
+        <v>1.913411629202327</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.4916551739551467</v>
+        <v>0.5528595256151141</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.285243180997257</v>
+        <v>4.427052226098462</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.988035773750107</v>
+        <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.658475764986014</v>
+        <v>-5.505331565354006</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.724289043441954</v>
+        <v>1.890633157399983</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.4916551739551467</v>
+        <v>0.5528595256151141</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.283028878123195</v>
+        <v>4.424837923224401</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.987938901824396</v>
+        <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.737895216193766</v>
+        <v>-5.584751016561758</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.692424391033143</v>
+        <v>1.858768504991172</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.4916551739551467</v>
+        <v>0.5528595256151141</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.282932006197485</v>
+        <v>4.424741051298691</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.98793279538244</v>
+        <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.833358214110984</v>
+        <v>-5.680214014478976</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.654233085424299</v>
+        <v>1.820577199382328</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.4916551739551467</v>
+        <v>0.5528595256151141</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.282925899755528</v>
+        <v>4.424734944856734</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.98602919194505</v>
+        <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.873378212154767</v>
+        <v>-5.720234012522759</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.636321482769396</v>
+        <v>1.802665596727425</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.4516351759113629</v>
+        <v>0.5128395275713302</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.257010297491869</v>
+        <v>4.398819342593074</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.991763009692777</v>
+        <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.928747374286961</v>
+        <v>-5.775603174654953</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.619907635664245</v>
+        <v>1.786251749622274</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.4516351759113629</v>
+        <v>0.5128395275713302</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.262744115239595</v>
+        <v>4.404553160340801</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.991301373035709</v>
+        <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.974185154117788</v>
+        <v>-5.82104095448578</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.601270887074846</v>
+        <v>1.767615001032876</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4087901852332032</v>
+        <v>0.4699945368931706</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.236575484175631</v>
+        <v>4.378384529276838</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.011175765886028</v>
+        <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.890959697270124</v>
+        <v>-5.737815497638116</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.654435462664231</v>
+        <v>1.820779576622261</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4087901852332032</v>
+        <v>0.4699945368931706</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.25644987702595</v>
+        <v>4.398258922127157</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.994876466410756</v>
+        <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.714669472664816</v>
+        <v>-5.561525273032808</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.708652253031082</v>
+        <v>1.874996366989112</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4087901852332032</v>
+        <v>0.4699945368931706</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.240150577550678</v>
+        <v>4.381959622651885</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.997307415874801</v>
+        <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.531457809531721</v>
+        <v>-5.378313609899713</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.784367867748366</v>
+        <v>1.950711981706395</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4087901852332032</v>
+        <v>0.4699945368931706</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.242581527014724</v>
+        <v>4.38439057211593</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146283</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.963098601722691</v>
+        <v>4.068185035827917</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.45973636251787</v>
+        <v>-5.306592162885862</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.778847632401795</v>
+        <v>1.945191746359825</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.4805116322470538</v>
+        <v>0.5417159839070211</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.251405581070923</v>
+        <v>4.393214626172131</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.410463535269516</v>
+        <v>3.795503554326209</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.910014347643862</v>
+        <v>4.015100781749089</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.259012820377008</v>
+        <v>-5.285899851773697</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.806052795179312</v>
+        <v>1.900384416725863</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.4805116322470538</v>
+        <v>0.4985391062140451</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.198321326992095</v>
+        <v>4.314224245477516</v>
       </c>
     </row>
   </sheetData>
